--- a/receptury.xlsx
+++ b/receptury.xlsx
@@ -398,20 +398,4035 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:F3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>idRap</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nazwaReceptury</v>
+      </c>
+      <c r="C1" t="str">
+        <v>CzasOdloz</v>
+      </c>
+      <c r="D1" t="str">
+        <v>createdAt</v>
+      </c>
+      <c r="E1" t="str">
+        <v>lastUsedAt</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Usr</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1780474710119</v>
+      </c>
+      <c r="B2" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-06-03 10:18:30</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-06-03 10:18:30</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-06-03 10:22:29</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Default</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1780983779698</v>
+      </c>
+      <c r="B3" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-06-09 07:42:59</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-09 07:42:59</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-06-09 07:43:54</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Default</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:S67"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>nazwaReceptury</v>
+      </c>
+      <c r="B1" t="str">
+        <v>nazwaProduktu</v>
+      </c>
+      <c r="C1" t="str">
+        <v>TekstDoDruku</v>
+      </c>
+      <c r="D1" t="str">
+        <v>nazwaSkladowej</v>
+      </c>
+      <c r="E1" t="str">
+        <v>dlugosc</v>
+      </c>
+      <c r="F1" t="str">
+        <v>grubosc</v>
+      </c>
+      <c r="G1" t="str">
+        <v>szerokosc</v>
+      </c>
+      <c r="H1" t="str">
+        <v>material</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Klasa</v>
+      </c>
+      <c r="J1" t="str">
+        <v>klasa</v>
+      </c>
+      <c r="K1" t="str">
+        <v>idReceptury</v>
+      </c>
+      <c r="L1" t="str">
+        <v>idSkladowej</v>
+      </c>
+      <c r="M1" t="str">
+        <v>wybijak</v>
+      </c>
+      <c r="N1" t="str">
+        <v>grupa</v>
+      </c>
+      <c r="O1" t="str">
+        <v>priorytet</v>
+      </c>
+      <c r="P1" t="str">
+        <v>ilosc</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Stanowisko</v>
+      </c>
+      <c r="R1" t="str">
+        <v>iloscWykonana</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Informacje</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B2" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C2" t="str">
+        <v>BULL S 127,5 FR + KL</v>
+      </c>
+      <c r="D2" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E2">
+        <v>1275</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2" t="str">
+        <v>So</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>26</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="str">
+        <v>809</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2">
+        <v>300</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>4</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C3" t="str">
+        <v>BULL S 126</v>
+      </c>
+      <c r="D3" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E3">
+        <v>1260</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+      <c r="G3">
+        <v>60</v>
+      </c>
+      <c r="H3" t="str">
+        <v>So</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3" t="str">
+        <v>607</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3">
+        <v>150</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>3</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C4" t="str">
+        <v>BULL S 94 FR</v>
+      </c>
+      <c r="D4" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E4">
+        <v>940</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>60</v>
+      </c>
+      <c r="H4" t="str">
+        <v>So</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4" t="str">
+        <v>405</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4">
+        <v>300</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>2</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B5" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C5" t="str">
+        <v>BULL S 94</v>
+      </c>
+      <c r="D5" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E5">
+        <v>940</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>60</v>
+      </c>
+      <c r="H5" t="str">
+        <v>So</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5" t="str">
+        <v>405</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5">
+        <v>150</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B6" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C6" t="str">
+        <v>BULL S 88</v>
+      </c>
+      <c r="D6" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E6">
+        <v>880</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>60</v>
+      </c>
+      <c r="H6" t="str">
+        <v>So</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6" t="str">
+        <v>809</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6">
+        <v>300</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>4</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B7" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C7" t="str">
+        <v>BULL S 52</v>
+      </c>
+      <c r="D7" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E7">
+        <v>520</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+      <c r="H7" t="str">
+        <v>So</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+      <c r="M7" t="str">
+        <v>607</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7">
+        <v>300</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>3</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B8" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C8" t="str">
+        <v>BULL S 19</v>
+      </c>
+      <c r="D8" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E8">
+        <v>190</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8" t="str">
+        <v>So</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <v>26</v>
+      </c>
+      <c r="L8">
+        <v>6</v>
+      </c>
+      <c r="M8" t="str">
+        <v>4</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8">
+        <v>900</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>2</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B9" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C9" t="str">
+        <v>BULL S 15,1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E9">
+        <v>151</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9" t="str">
+        <v>So</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <v>26</v>
+      </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9" t="str">
+        <v>8</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9">
+        <v>300</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B10" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C10" t="str">
+        <v>BULL S 12,5</v>
+      </c>
+      <c r="D10" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E10">
+        <v>125</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>60</v>
+      </c>
+      <c r="H10" t="str">
+        <v>So</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
+        <v>26</v>
+      </c>
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10" t="str">
+        <v>6</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10">
+        <v>150</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>3</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B11" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C11" t="str">
+        <v>BULL S 9,1</v>
+      </c>
+      <c r="D11" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E11">
+        <v>91</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>60</v>
+      </c>
+      <c r="H11" t="str">
+        <v>So</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>26</v>
+      </c>
+      <c r="L11">
+        <v>9</v>
+      </c>
+      <c r="M11" t="str">
+        <v>1</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11">
+        <v>750</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>dysza</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B12" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C12" t="str">
+        <v>BULL S 22</v>
+      </c>
+      <c r="D12" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E12">
+        <v>220</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+      <c r="G12">
+        <v>80</v>
+      </c>
+      <c r="H12" t="str">
+        <v>So</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <v>26</v>
+      </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12" t="str">
+        <v>4</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12">
+        <v>900</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>2</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B13" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C13" t="str">
+        <v>BULL S 131 KL</v>
+      </c>
+      <c r="D13" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E13">
+        <v>1310</v>
+      </c>
+      <c r="F13">
+        <v>25</v>
+      </c>
+      <c r="G13">
+        <v>50</v>
+      </c>
+      <c r="H13" t="str">
+        <v>So</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>26</v>
+      </c>
+      <c r="L13">
+        <v>11</v>
+      </c>
+      <c r="M13" t="str">
+        <v>405</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13">
+        <v>300</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>2</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B14" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C14" t="str">
+        <v>BULL S 126</v>
+      </c>
+      <c r="D14" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E14">
+        <v>1260</v>
+      </c>
+      <c r="F14">
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>50</v>
+      </c>
+      <c r="H14" t="str">
+        <v>So</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>26</v>
+      </c>
+      <c r="L14">
+        <v>12</v>
+      </c>
+      <c r="M14" t="str">
+        <v>809</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14">
+        <v>300</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>4</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B15" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C15" t="str">
+        <v>BULL S 114,5</v>
+      </c>
+      <c r="D15" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E15">
+        <v>1145</v>
+      </c>
+      <c r="F15">
+        <v>25</v>
+      </c>
+      <c r="G15">
+        <v>50</v>
+      </c>
+      <c r="H15" t="str">
+        <v>So</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>26</v>
+      </c>
+      <c r="L15">
+        <v>13</v>
+      </c>
+      <c r="M15" t="str">
+        <v>607</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15">
+        <v>150</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>3</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B16" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C16" t="str">
+        <v>BULL S 99,5</v>
+      </c>
+      <c r="D16" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E16">
+        <v>995</v>
+      </c>
+      <c r="F16">
+        <v>25</v>
+      </c>
+      <c r="G16">
+        <v>50</v>
+      </c>
+      <c r="H16" t="str">
+        <v>So</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <v>26</v>
+      </c>
+      <c r="L16">
+        <v>14</v>
+      </c>
+      <c r="M16" t="str">
+        <v>405</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16">
+        <v>300</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B17" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C17" t="str">
+        <v>BULL S 92</v>
+      </c>
+      <c r="D17" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E17">
+        <v>920</v>
+      </c>
+      <c r="F17">
+        <v>25</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17" t="str">
+        <v>So</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <v>26</v>
+      </c>
+      <c r="L17">
+        <v>15</v>
+      </c>
+      <c r="M17" t="str">
+        <v>809</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17">
+        <v>450</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>4</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B18" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C18" t="str">
+        <v>BULL S 82</v>
+      </c>
+      <c r="D18" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E18">
+        <v>820</v>
+      </c>
+      <c r="F18">
+        <v>25</v>
+      </c>
+      <c r="G18">
+        <v>50</v>
+      </c>
+      <c r="H18" t="str">
+        <v>So</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <v>26</v>
+      </c>
+      <c r="L18">
+        <v>16</v>
+      </c>
+      <c r="M18" t="str">
+        <v>607</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18">
+        <v>150</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>3</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B19" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C19" t="str">
+        <v>BULL S 21</v>
+      </c>
+      <c r="D19" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E19">
+        <v>210</v>
+      </c>
+      <c r="F19">
+        <v>25</v>
+      </c>
+      <c r="G19">
+        <v>50</v>
+      </c>
+      <c r="H19" t="str">
+        <v>So</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>26</v>
+      </c>
+      <c r="L19">
+        <v>17</v>
+      </c>
+      <c r="M19" t="str">
+        <v>4</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19">
+        <v>900</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>2</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B20" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C20" t="str">
+        <v>BULL S 11,5</v>
+      </c>
+      <c r="D20" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E20">
+        <v>115</v>
+      </c>
+      <c r="F20">
+        <v>25</v>
+      </c>
+      <c r="G20">
+        <v>50</v>
+      </c>
+      <c r="H20" t="str">
+        <v>So</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <v>26</v>
+      </c>
+      <c r="L20">
+        <v>18</v>
+      </c>
+      <c r="M20" t="str">
+        <v>8</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20">
+        <v>450</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>4</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B21" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C21" t="str">
+        <v>BULL S 7,5</v>
+      </c>
+      <c r="D21" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E21">
+        <v>75</v>
+      </c>
+      <c r="F21">
+        <v>25</v>
+      </c>
+      <c r="G21">
+        <v>50</v>
+      </c>
+      <c r="H21" t="str">
+        <v>So</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <v>26</v>
+      </c>
+      <c r="L21">
+        <v>19</v>
+      </c>
+      <c r="M21" t="str">
+        <v>6</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21">
+        <v>300</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>3</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B22" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C22" t="str">
+        <v>BULL S 6,5</v>
+      </c>
+      <c r="D22" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E22">
+        <v>65</v>
+      </c>
+      <c r="F22">
+        <v>25</v>
+      </c>
+      <c r="G22">
+        <v>50</v>
+      </c>
+      <c r="H22" t="str">
+        <v>So</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>26</v>
+      </c>
+      <c r="L22">
+        <v>20</v>
+      </c>
+      <c r="M22" t="str">
+        <v>4</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22">
+        <v>300</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>2</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B23" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C23" t="str">
+        <v>BULL S 146</v>
+      </c>
+      <c r="D23" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E23">
+        <v>1460</v>
+      </c>
+      <c r="F23">
+        <v>25</v>
+      </c>
+      <c r="G23">
+        <v>25</v>
+      </c>
+      <c r="H23" t="str">
+        <v>So</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>26</v>
+      </c>
+      <c r="L23">
+        <v>21</v>
+      </c>
+      <c r="M23" t="str">
+        <v>809</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23">
+        <v>150</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>4</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B24" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C24" t="str">
+        <v>BULL S 127,5</v>
+      </c>
+      <c r="D24" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E24">
+        <v>1275</v>
+      </c>
+      <c r="F24">
+        <v>25</v>
+      </c>
+      <c r="G24">
+        <v>25</v>
+      </c>
+      <c r="H24" t="str">
+        <v>So</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>2</v>
+      </c>
+      <c r="K24">
+        <v>26</v>
+      </c>
+      <c r="L24">
+        <v>22</v>
+      </c>
+      <c r="M24" t="str">
+        <v>607</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24">
+        <v>150</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>3</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B25" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C25" t="str">
+        <v>BULL S 126</v>
+      </c>
+      <c r="D25" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E25">
+        <v>1260</v>
+      </c>
+      <c r="F25">
+        <v>25</v>
+      </c>
+      <c r="G25">
+        <v>25</v>
+      </c>
+      <c r="H25" t="str">
+        <v>So</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>26</v>
+      </c>
+      <c r="L25">
+        <v>23</v>
+      </c>
+      <c r="M25" t="str">
+        <v>405</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25">
+        <v>450</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>2</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B26" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C26" t="str">
+        <v>BULL S 92</v>
+      </c>
+      <c r="D26" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E26">
+        <v>920</v>
+      </c>
+      <c r="F26">
+        <v>25</v>
+      </c>
+      <c r="G26">
+        <v>25</v>
+      </c>
+      <c r="H26" t="str">
+        <v>So</v>
+      </c>
+      <c r="I26">
+        <v>2</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>26</v>
+      </c>
+      <c r="L26">
+        <v>24</v>
+      </c>
+      <c r="M26" t="str">
+        <v>607</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26">
+        <v>450</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>3</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B27" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C27" t="str">
+        <v>BULL S 99,5</v>
+      </c>
+      <c r="D27" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E27">
+        <v>995</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
+      </c>
+      <c r="H27" t="str">
+        <v>So</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27">
+        <v>26</v>
+      </c>
+      <c r="L27">
+        <v>25</v>
+      </c>
+      <c r="M27" t="str">
+        <v>809</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27">
+        <v>600</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>4</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B28" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C28" t="str">
+        <v>BULL S 85,5</v>
+      </c>
+      <c r="D28" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E28">
+        <v>855</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>25</v>
+      </c>
+      <c r="H28" t="str">
+        <v>So</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>26</v>
+      </c>
+      <c r="L28">
+        <v>26</v>
+      </c>
+      <c r="M28" t="str">
+        <v>405</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28">
+        <v>300</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>2</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B29" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C29" t="str">
+        <v>BULL S 82</v>
+      </c>
+      <c r="D29" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E29">
+        <v>820</v>
+      </c>
+      <c r="F29">
+        <v>25</v>
+      </c>
+      <c r="G29">
+        <v>25</v>
+      </c>
+      <c r="H29" t="str">
+        <v>So</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>26</v>
+      </c>
+      <c r="L29">
+        <v>27</v>
+      </c>
+      <c r="M29" t="str">
+        <v>809</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29">
+        <v>150</v>
+      </c>
+      <c r="Q29" t="str">
+        <v>4</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B30" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C30" t="str">
+        <v>BULL S 52,5</v>
+      </c>
+      <c r="D30" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E30">
+        <v>525</v>
+      </c>
+      <c r="F30">
+        <v>25</v>
+      </c>
+      <c r="G30">
+        <v>25</v>
+      </c>
+      <c r="H30" t="str">
+        <v>So</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>2</v>
+      </c>
+      <c r="K30">
+        <v>26</v>
+      </c>
+      <c r="L30">
+        <v>28</v>
+      </c>
+      <c r="M30" t="str">
+        <v>607</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30">
+        <v>1050</v>
+      </c>
+      <c r="Q30" t="str">
+        <v>3</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B31" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C31" t="str">
+        <v>BULL S 24</v>
+      </c>
+      <c r="D31" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E31">
+        <v>240</v>
+      </c>
+      <c r="F31">
+        <v>25</v>
+      </c>
+      <c r="G31">
+        <v>25</v>
+      </c>
+      <c r="H31" t="str">
+        <v>So</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31">
+        <v>26</v>
+      </c>
+      <c r="L31">
+        <v>29</v>
+      </c>
+      <c r="M31" t="str">
+        <v>4</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31">
+        <v>600</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>2</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B32" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C32" t="str">
+        <v>BULL S 18,5</v>
+      </c>
+      <c r="D32" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E32">
+        <v>185</v>
+      </c>
+      <c r="F32">
+        <v>25</v>
+      </c>
+      <c r="G32">
+        <v>25</v>
+      </c>
+      <c r="H32" t="str">
+        <v>So</v>
+      </c>
+      <c r="I32">
+        <v>2</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32">
+        <v>26</v>
+      </c>
+      <c r="L32">
+        <v>30</v>
+      </c>
+      <c r="M32" t="str">
+        <v>8</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32">
+        <v>300</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>4</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B33" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C33" t="str">
+        <v>BULL S 14,5</v>
+      </c>
+      <c r="D33" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E33">
+        <v>145</v>
+      </c>
+      <c r="F33">
+        <v>25</v>
+      </c>
+      <c r="G33">
+        <v>25</v>
+      </c>
+      <c r="H33" t="str">
+        <v>So</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33">
+        <v>26</v>
+      </c>
+      <c r="L33">
+        <v>31</v>
+      </c>
+      <c r="M33" t="str">
+        <v>6</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33">
+        <v>900</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>3</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>BULLS</v>
+      </c>
+      <c r="B34" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C34" t="str">
+        <v>BULL S 13,1</v>
+      </c>
+      <c r="D34" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E34">
+        <v>131</v>
+      </c>
+      <c r="F34">
+        <v>25</v>
+      </c>
+      <c r="G34">
+        <v>25</v>
+      </c>
+      <c r="H34" t="str">
+        <v>So</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34">
+        <v>26</v>
+      </c>
+      <c r="L34">
+        <v>32</v>
+      </c>
+      <c r="M34" t="str">
+        <v>4</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34">
+        <v>1050</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>2</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B35" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C35" t="str">
+        <v>BULL S 127,5 FR + KL</v>
+      </c>
+      <c r="D35" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E35">
+        <v>1275</v>
+      </c>
+      <c r="F35">
+        <v>30</v>
+      </c>
+      <c r="G35">
+        <v>60</v>
+      </c>
+      <c r="H35" t="str">
+        <v>So</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>2</v>
+      </c>
+      <c r="K35">
+        <v>26</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="str">
+        <v>405</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35">
+        <v>300</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>2</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B36" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C36" t="str">
+        <v>BULL S 126</v>
+      </c>
+      <c r="D36" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E36">
+        <v>1260</v>
+      </c>
+      <c r="F36">
+        <v>30</v>
+      </c>
+      <c r="G36">
+        <v>60</v>
+      </c>
+      <c r="H36" t="str">
+        <v>So</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>2</v>
+      </c>
+      <c r="K36">
+        <v>26</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36" t="str">
+        <v>809</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36">
+        <v>150</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>4</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B37" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C37" t="str">
+        <v>BULL S 94 FR</v>
+      </c>
+      <c r="D37" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E37">
+        <v>940</v>
+      </c>
+      <c r="F37">
+        <v>30</v>
+      </c>
+      <c r="G37">
+        <v>60</v>
+      </c>
+      <c r="H37" t="str">
+        <v>So</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37">
+        <v>26</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37" t="str">
+        <v>405</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37">
+        <v>300</v>
+      </c>
+      <c r="Q37" t="str">
+        <v>2</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B38" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C38" t="str">
+        <v>BULL S 94</v>
+      </c>
+      <c r="D38" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E38">
+        <v>940</v>
+      </c>
+      <c r="F38">
+        <v>30</v>
+      </c>
+      <c r="G38">
+        <v>60</v>
+      </c>
+      <c r="H38" t="str">
+        <v>So</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>2</v>
+      </c>
+      <c r="K38">
+        <v>26</v>
+      </c>
+      <c r="L38">
+        <v>3</v>
+      </c>
+      <c r="M38" t="str">
+        <v>607</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38">
+        <v>150</v>
+      </c>
+      <c r="Q38" t="str">
+        <v>3</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B39" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C39" t="str">
+        <v>BULL S 88</v>
+      </c>
+      <c r="D39" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E39">
+        <v>880</v>
+      </c>
+      <c r="F39">
+        <v>30</v>
+      </c>
+      <c r="G39">
+        <v>60</v>
+      </c>
+      <c r="H39" t="str">
+        <v>So</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39">
+        <v>26</v>
+      </c>
+      <c r="L39">
+        <v>4</v>
+      </c>
+      <c r="M39" t="str">
+        <v>809</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39">
+        <v>300</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>4</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B40" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C40" t="str">
+        <v>BULL S 52</v>
+      </c>
+      <c r="D40" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E40">
+        <v>520</v>
+      </c>
+      <c r="F40">
+        <v>30</v>
+      </c>
+      <c r="G40">
+        <v>60</v>
+      </c>
+      <c r="H40" t="str">
+        <v>So</v>
+      </c>
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40">
+        <v>26</v>
+      </c>
+      <c r="L40">
+        <v>5</v>
+      </c>
+      <c r="M40" t="str">
+        <v>607</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40">
+        <v>300</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>3</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B41" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C41" t="str">
+        <v>BULL S 19</v>
+      </c>
+      <c r="D41" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E41">
+        <v>190</v>
+      </c>
+      <c r="F41">
+        <v>30</v>
+      </c>
+      <c r="G41">
+        <v>60</v>
+      </c>
+      <c r="H41" t="str">
+        <v>So</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <v>26</v>
+      </c>
+      <c r="L41">
+        <v>6</v>
+      </c>
+      <c r="M41" t="str">
+        <v>4</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41">
+        <v>900</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>2</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B42" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C42" t="str">
+        <v>BULL S 15,1</v>
+      </c>
+      <c r="D42" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E42">
+        <v>151</v>
+      </c>
+      <c r="F42">
+        <v>30</v>
+      </c>
+      <c r="G42">
+        <v>60</v>
+      </c>
+      <c r="H42" t="str">
+        <v>So</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42">
+        <v>26</v>
+      </c>
+      <c r="L42">
+        <v>7</v>
+      </c>
+      <c r="M42" t="str">
+        <v>8</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42">
+        <v>300</v>
+      </c>
+      <c r="Q42" t="str">
+        <v>4</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B43" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C43" t="str">
+        <v>BULL S 12,5</v>
+      </c>
+      <c r="D43" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E43">
+        <v>125</v>
+      </c>
+      <c r="F43">
+        <v>30</v>
+      </c>
+      <c r="G43">
+        <v>60</v>
+      </c>
+      <c r="H43" t="str">
+        <v>So</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>26</v>
+      </c>
+      <c r="L43">
+        <v>8</v>
+      </c>
+      <c r="M43" t="str">
+        <v>6</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43">
+        <v>150</v>
+      </c>
+      <c r="Q43" t="str">
+        <v>3</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B44" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C44" t="str">
+        <v>BULL S 9,1</v>
+      </c>
+      <c r="D44" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E44">
+        <v>91</v>
+      </c>
+      <c r="F44">
+        <v>30</v>
+      </c>
+      <c r="G44">
+        <v>60</v>
+      </c>
+      <c r="H44" t="str">
+        <v>So</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44">
+        <v>26</v>
+      </c>
+      <c r="L44">
+        <v>9</v>
+      </c>
+      <c r="M44" t="str">
+        <v>4</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44">
+        <v>750</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>2</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B45" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C45" t="str">
+        <v>BULL S 22</v>
+      </c>
+      <c r="D45" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E45">
+        <v>220</v>
+      </c>
+      <c r="F45">
+        <v>30</v>
+      </c>
+      <c r="G45">
+        <v>80</v>
+      </c>
+      <c r="H45" t="str">
+        <v>So</v>
+      </c>
+      <c r="I45">
+        <v>2</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
+        <v>26</v>
+      </c>
+      <c r="L45">
+        <v>10</v>
+      </c>
+      <c r="M45" t="str">
+        <v>4</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45">
+        <v>900</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>2</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B46" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C46" t="str">
+        <v>BULL S 131 KL</v>
+      </c>
+      <c r="D46" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E46">
+        <v>1310</v>
+      </c>
+      <c r="F46">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>50</v>
+      </c>
+      <c r="H46" t="str">
+        <v>So</v>
+      </c>
+      <c r="I46">
+        <v>2</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46">
+        <v>26</v>
+      </c>
+      <c r="L46">
+        <v>11</v>
+      </c>
+      <c r="M46" t="str">
+        <v>405</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46">
+        <v>300</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>2</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B47" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C47" t="str">
+        <v>BULL S 126</v>
+      </c>
+      <c r="D47" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E47">
+        <v>1260</v>
+      </c>
+      <c r="F47">
+        <v>25</v>
+      </c>
+      <c r="G47">
+        <v>50</v>
+      </c>
+      <c r="H47" t="str">
+        <v>So</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>2</v>
+      </c>
+      <c r="K47">
+        <v>26</v>
+      </c>
+      <c r="L47">
+        <v>12</v>
+      </c>
+      <c r="M47" t="str">
+        <v>809</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47">
+        <v>300</v>
+      </c>
+      <c r="Q47" t="str">
+        <v>4</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B48" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C48" t="str">
+        <v>BULL S 114,5</v>
+      </c>
+      <c r="D48" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E48">
+        <v>1145</v>
+      </c>
+      <c r="F48">
+        <v>25</v>
+      </c>
+      <c r="G48">
+        <v>50</v>
+      </c>
+      <c r="H48" t="str">
+        <v>So</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48">
+        <v>2</v>
+      </c>
+      <c r="K48">
+        <v>26</v>
+      </c>
+      <c r="L48">
+        <v>13</v>
+      </c>
+      <c r="M48" t="str">
+        <v>607</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48">
+        <v>150</v>
+      </c>
+      <c r="Q48" t="str">
+        <v>3</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B49" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C49" t="str">
+        <v>BULL S 99,5</v>
+      </c>
+      <c r="D49" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E49">
+        <v>995</v>
+      </c>
+      <c r="F49">
+        <v>25</v>
+      </c>
+      <c r="G49">
+        <v>50</v>
+      </c>
+      <c r="H49" t="str">
+        <v>So</v>
+      </c>
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="K49">
+        <v>26</v>
+      </c>
+      <c r="L49">
+        <v>14</v>
+      </c>
+      <c r="M49" t="str">
+        <v>405</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49">
+        <v>300</v>
+      </c>
+      <c r="Q49" t="str">
+        <v>2</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B50" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C50" t="str">
+        <v>BULL S 92</v>
+      </c>
+      <c r="D50" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E50">
+        <v>920</v>
+      </c>
+      <c r="F50">
+        <v>25</v>
+      </c>
+      <c r="G50">
+        <v>50</v>
+      </c>
+      <c r="H50" t="str">
+        <v>So</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50">
+        <v>26</v>
+      </c>
+      <c r="L50">
+        <v>15</v>
+      </c>
+      <c r="M50" t="str">
+        <v>809</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50">
+        <v>450</v>
+      </c>
+      <c r="Q50" t="str">
+        <v>4</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B51" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C51" t="str">
+        <v>BULL S 82</v>
+      </c>
+      <c r="D51" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E51">
+        <v>820</v>
+      </c>
+      <c r="F51">
+        <v>25</v>
+      </c>
+      <c r="G51">
+        <v>50</v>
+      </c>
+      <c r="H51" t="str">
+        <v>So</v>
+      </c>
+      <c r="I51">
+        <v>2</v>
+      </c>
+      <c r="J51">
+        <v>2</v>
+      </c>
+      <c r="K51">
+        <v>26</v>
+      </c>
+      <c r="L51">
+        <v>16</v>
+      </c>
+      <c r="M51" t="str">
+        <v>607</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51">
+        <v>150</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>3</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B52" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C52" t="str">
+        <v>BULL S 21</v>
+      </c>
+      <c r="D52" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E52">
+        <v>210</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+      <c r="G52">
+        <v>50</v>
+      </c>
+      <c r="H52" t="str">
+        <v>So</v>
+      </c>
+      <c r="I52">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>26</v>
+      </c>
+      <c r="L52">
+        <v>17</v>
+      </c>
+      <c r="M52" t="str">
+        <v>4</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52">
+        <v>900</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>2</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B53" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C53" t="str">
+        <v>BULL S 11,5</v>
+      </c>
+      <c r="D53" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E53">
+        <v>115</v>
+      </c>
+      <c r="F53">
+        <v>25</v>
+      </c>
+      <c r="G53">
+        <v>50</v>
+      </c>
+      <c r="H53" t="str">
+        <v>So</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53">
+        <v>26</v>
+      </c>
+      <c r="L53">
+        <v>18</v>
+      </c>
+      <c r="M53" t="str">
+        <v>8</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53">
+        <v>450</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>4</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B54" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C54" t="str">
+        <v>BULL S 7,5</v>
+      </c>
+      <c r="D54" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E54">
+        <v>75</v>
+      </c>
+      <c r="F54">
+        <v>25</v>
+      </c>
+      <c r="G54">
+        <v>50</v>
+      </c>
+      <c r="H54" t="str">
+        <v>So</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54">
+        <v>2</v>
+      </c>
+      <c r="K54">
+        <v>26</v>
+      </c>
+      <c r="L54">
+        <v>19</v>
+      </c>
+      <c r="M54" t="str">
+        <v>6</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54">
+        <v>300</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>3</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B55" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C55" t="str">
+        <v>BULL S 6,5</v>
+      </c>
+      <c r="D55" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E55">
+        <v>65</v>
+      </c>
+      <c r="F55">
+        <v>25</v>
+      </c>
+      <c r="G55">
+        <v>50</v>
+      </c>
+      <c r="H55" t="str">
+        <v>So</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>2</v>
+      </c>
+      <c r="K55">
+        <v>26</v>
+      </c>
+      <c r="L55">
+        <v>20</v>
+      </c>
+      <c r="M55" t="str">
+        <v>4</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55">
+        <v>300</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>2</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B56" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C56" t="str">
+        <v>BULL S 146</v>
+      </c>
+      <c r="D56" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E56">
+        <v>1460</v>
+      </c>
+      <c r="F56">
+        <v>25</v>
+      </c>
+      <c r="G56">
+        <v>25</v>
+      </c>
+      <c r="H56" t="str">
+        <v>So</v>
+      </c>
+      <c r="I56">
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <v>2</v>
+      </c>
+      <c r="K56">
+        <v>26</v>
+      </c>
+      <c r="L56">
+        <v>21</v>
+      </c>
+      <c r="M56" t="str">
+        <v>809</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56">
+        <v>150</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>4</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B57" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C57" t="str">
+        <v>BULL S 127,5</v>
+      </c>
+      <c r="D57" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E57">
+        <v>1275</v>
+      </c>
+      <c r="F57">
+        <v>25</v>
+      </c>
+      <c r="G57">
+        <v>25</v>
+      </c>
+      <c r="H57" t="str">
+        <v>So</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+      <c r="J57">
+        <v>2</v>
+      </c>
+      <c r="K57">
+        <v>26</v>
+      </c>
+      <c r="L57">
+        <v>22</v>
+      </c>
+      <c r="M57" t="str">
+        <v>607</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57">
+        <v>150</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>3</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B58" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C58" t="str">
+        <v>BULL S 126</v>
+      </c>
+      <c r="D58" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E58">
+        <v>1260</v>
+      </c>
+      <c r="F58">
+        <v>25</v>
+      </c>
+      <c r="G58">
+        <v>25</v>
+      </c>
+      <c r="H58" t="str">
+        <v>So</v>
+      </c>
+      <c r="I58">
+        <v>2</v>
+      </c>
+      <c r="J58">
+        <v>2</v>
+      </c>
+      <c r="K58">
+        <v>26</v>
+      </c>
+      <c r="L58">
+        <v>23</v>
+      </c>
+      <c r="M58" t="str">
+        <v>405</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58">
+        <v>450</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>2</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B59" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C59" t="str">
+        <v>BULL S 92</v>
+      </c>
+      <c r="D59" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E59">
+        <v>920</v>
+      </c>
+      <c r="F59">
+        <v>25</v>
+      </c>
+      <c r="G59">
+        <v>25</v>
+      </c>
+      <c r="H59" t="str">
+        <v>So</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="K59">
+        <v>26</v>
+      </c>
+      <c r="L59">
+        <v>24</v>
+      </c>
+      <c r="M59" t="str">
+        <v>607</v>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59">
+        <v>450</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>3</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B60" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C60" t="str">
+        <v>BULL S 99,5</v>
+      </c>
+      <c r="D60" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E60">
+        <v>995</v>
+      </c>
+      <c r="F60">
+        <v>25</v>
+      </c>
+      <c r="G60">
+        <v>25</v>
+      </c>
+      <c r="H60" t="str">
+        <v>So</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="K60">
+        <v>26</v>
+      </c>
+      <c r="L60">
+        <v>25</v>
+      </c>
+      <c r="M60" t="str">
+        <v>809</v>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60">
+        <v>600</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>4</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B61" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C61" t="str">
+        <v>BULL S 85,5</v>
+      </c>
+      <c r="D61" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E61">
+        <v>855</v>
+      </c>
+      <c r="F61">
+        <v>25</v>
+      </c>
+      <c r="G61">
+        <v>25</v>
+      </c>
+      <c r="H61" t="str">
+        <v>So</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61">
+        <v>26</v>
+      </c>
+      <c r="L61">
+        <v>26</v>
+      </c>
+      <c r="M61" t="str">
+        <v>405</v>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61">
+        <v>300</v>
+      </c>
+      <c r="Q61" t="str">
+        <v>2</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B62" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C62" t="str">
+        <v>BULL S 82</v>
+      </c>
+      <c r="D62" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E62">
+        <v>820</v>
+      </c>
+      <c r="F62">
+        <v>25</v>
+      </c>
+      <c r="G62">
+        <v>25</v>
+      </c>
+      <c r="H62" t="str">
+        <v>So</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62">
+        <v>26</v>
+      </c>
+      <c r="L62">
+        <v>27</v>
+      </c>
+      <c r="M62" t="str">
+        <v>809</v>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62">
+        <v>150</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>4</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B63" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C63" t="str">
+        <v>BULL S 52,5</v>
+      </c>
+      <c r="D63" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E63">
+        <v>525</v>
+      </c>
+      <c r="F63">
+        <v>25</v>
+      </c>
+      <c r="G63">
+        <v>25</v>
+      </c>
+      <c r="H63" t="str">
+        <v>So</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>2</v>
+      </c>
+      <c r="K63">
+        <v>26</v>
+      </c>
+      <c r="L63">
+        <v>28</v>
+      </c>
+      <c r="M63" t="str">
+        <v>607</v>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63">
+        <v>1050</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>3</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B64" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C64" t="str">
+        <v>BULL S 24</v>
+      </c>
+      <c r="D64" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E64">
+        <v>240</v>
+      </c>
+      <c r="F64">
+        <v>25</v>
+      </c>
+      <c r="G64">
+        <v>25</v>
+      </c>
+      <c r="H64" t="str">
+        <v>So</v>
+      </c>
+      <c r="I64">
+        <v>2</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+      <c r="K64">
+        <v>26</v>
+      </c>
+      <c r="L64">
+        <v>29</v>
+      </c>
+      <c r="M64" t="str">
+        <v>4</v>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64">
+        <v>600</v>
+      </c>
+      <c r="Q64" t="str">
+        <v>2</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B65" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C65" t="str">
+        <v>BULL S 18,5</v>
+      </c>
+      <c r="D65" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E65">
+        <v>185</v>
+      </c>
+      <c r="F65">
+        <v>25</v>
+      </c>
+      <c r="G65">
+        <v>25</v>
+      </c>
+      <c r="H65" t="str">
+        <v>So</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65">
+        <v>26</v>
+      </c>
+      <c r="L65">
+        <v>30</v>
+      </c>
+      <c r="M65" t="str">
+        <v>8</v>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65">
+        <v>300</v>
+      </c>
+      <c r="Q65" t="str">
+        <v>4</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B66" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C66" t="str">
+        <v>BULL S 14,5</v>
+      </c>
+      <c r="D66" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E66">
+        <v>145</v>
+      </c>
+      <c r="F66">
+        <v>25</v>
+      </c>
+      <c r="G66">
+        <v>25</v>
+      </c>
+      <c r="H66" t="str">
+        <v>So</v>
+      </c>
+      <c r="I66">
+        <v>2</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66">
+        <v>26</v>
+      </c>
+      <c r="L66">
+        <v>31</v>
+      </c>
+      <c r="M66" t="str">
+        <v>6</v>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66">
+        <v>900</v>
+      </c>
+      <c r="Q66" t="str">
+        <v>3</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>bullsg</v>
+      </c>
+      <c r="B67" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="C67" t="str">
+        <v>BULL S 13,1</v>
+      </c>
+      <c r="D67" t="str">
+        <v>BULL S</v>
+      </c>
+      <c r="E67">
+        <v>131</v>
+      </c>
+      <c r="F67">
+        <v>25</v>
+      </c>
+      <c r="G67">
+        <v>25</v>
+      </c>
+      <c r="H67" t="str">
+        <v>So</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="K67">
+        <v>26</v>
+      </c>
+      <c r="L67">
+        <v>32</v>
+      </c>
+      <c r="M67" t="str">
+        <v>4</v>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67">
+        <v>1050</v>
+      </c>
+      <c r="Q67" t="str">
+        <v>2</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S67"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/receptury.xlsx
+++ b/receptury.xlsx
@@ -434,7 +434,7 @@
         <v>2026-06-03 10:18:30</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-03 10:22:29</v>
+        <v>2026-06-10 14:31:52</v>
       </c>
       <c r="F2" t="str">
         <v>Default</v>
@@ -2482,7 +2482,7 @@
         <v>bullsg</v>
       </c>
       <c r="B35" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C35" t="str">
         <v>BULL S 127,5 FR + KL</v>
@@ -2541,7 +2541,7 @@
         <v>bullsg</v>
       </c>
       <c r="B36" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C36" t="str">
         <v>BULL S 126</v>
@@ -2600,7 +2600,7 @@
         <v>bullsg</v>
       </c>
       <c r="B37" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C37" t="str">
         <v>BULL S 94 FR</v>
@@ -2659,7 +2659,7 @@
         <v>bullsg</v>
       </c>
       <c r="B38" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C38" t="str">
         <v>BULL S 94</v>
@@ -2718,7 +2718,7 @@
         <v>bullsg</v>
       </c>
       <c r="B39" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C39" t="str">
         <v>BULL S 88</v>
@@ -2777,7 +2777,7 @@
         <v>bullsg</v>
       </c>
       <c r="B40" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C40" t="str">
         <v>BULL S 52</v>
@@ -2836,7 +2836,7 @@
         <v>bullsg</v>
       </c>
       <c r="B41" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C41" t="str">
         <v>BULL S 19</v>
@@ -2895,7 +2895,7 @@
         <v>bullsg</v>
       </c>
       <c r="B42" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C42" t="str">
         <v>BULL S 15,1</v>
@@ -2954,7 +2954,7 @@
         <v>bullsg</v>
       </c>
       <c r="B43" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C43" t="str">
         <v>BULL S 12,5</v>
@@ -3013,7 +3013,7 @@
         <v>bullsg</v>
       </c>
       <c r="B44" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C44" t="str">
         <v>BULL S 9,1</v>
@@ -3072,7 +3072,7 @@
         <v>bullsg</v>
       </c>
       <c r="B45" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C45" t="str">
         <v>BULL S 22</v>
@@ -3131,7 +3131,7 @@
         <v>bullsg</v>
       </c>
       <c r="B46" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C46" t="str">
         <v>BULL S 131 KL</v>
@@ -3190,7 +3190,7 @@
         <v>bullsg</v>
       </c>
       <c r="B47" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C47" t="str">
         <v>BULL S 126</v>
@@ -3249,7 +3249,7 @@
         <v>bullsg</v>
       </c>
       <c r="B48" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C48" t="str">
         <v>BULL S 114,5</v>
@@ -3308,7 +3308,7 @@
         <v>bullsg</v>
       </c>
       <c r="B49" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C49" t="str">
         <v>BULL S 99,5</v>
@@ -3367,7 +3367,7 @@
         <v>bullsg</v>
       </c>
       <c r="B50" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C50" t="str">
         <v>BULL S 92</v>
@@ -3426,7 +3426,7 @@
         <v>bullsg</v>
       </c>
       <c r="B51" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C51" t="str">
         <v>BULL S 82</v>
@@ -3485,7 +3485,7 @@
         <v>bullsg</v>
       </c>
       <c r="B52" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C52" t="str">
         <v>BULL S 21</v>
@@ -3544,7 +3544,7 @@
         <v>bullsg</v>
       </c>
       <c r="B53" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C53" t="str">
         <v>BULL S 11,5</v>
@@ -3603,7 +3603,7 @@
         <v>bullsg</v>
       </c>
       <c r="B54" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C54" t="str">
         <v>BULL S 7,5</v>
@@ -3662,7 +3662,7 @@
         <v>bullsg</v>
       </c>
       <c r="B55" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C55" t="str">
         <v>BULL S 6,5</v>
@@ -3721,7 +3721,7 @@
         <v>bullsg</v>
       </c>
       <c r="B56" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C56" t="str">
         <v>BULL S 146</v>
@@ -3780,7 +3780,7 @@
         <v>bullsg</v>
       </c>
       <c r="B57" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C57" t="str">
         <v>BULL S 127,5</v>
@@ -3839,7 +3839,7 @@
         <v>bullsg</v>
       </c>
       <c r="B58" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C58" t="str">
         <v>BULL S 126</v>
@@ -3898,7 +3898,7 @@
         <v>bullsg</v>
       </c>
       <c r="B59" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C59" t="str">
         <v>BULL S 92</v>
@@ -3957,7 +3957,7 @@
         <v>bullsg</v>
       </c>
       <c r="B60" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C60" t="str">
         <v>BULL S 99,5</v>
@@ -4016,7 +4016,7 @@
         <v>bullsg</v>
       </c>
       <c r="B61" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C61" t="str">
         <v>BULL S 85,5</v>
@@ -4075,7 +4075,7 @@
         <v>bullsg</v>
       </c>
       <c r="B62" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C62" t="str">
         <v>BULL S 82</v>
@@ -4134,7 +4134,7 @@
         <v>bullsg</v>
       </c>
       <c r="B63" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C63" t="str">
         <v>BULL S 52,5</v>
@@ -4193,7 +4193,7 @@
         <v>bullsg</v>
       </c>
       <c r="B64" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C64" t="str">
         <v>BULL S 24</v>
@@ -4252,7 +4252,7 @@
         <v>bullsg</v>
       </c>
       <c r="B65" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C65" t="str">
         <v>BULL S 18,5</v>
@@ -4311,7 +4311,7 @@
         <v>bullsg</v>
       </c>
       <c r="B66" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C66" t="str">
         <v>BULL S 14,5</v>
@@ -4370,7 +4370,7 @@
         <v>bullsg</v>
       </c>
       <c r="B67" t="str">
-        <v>BULL S</v>
+        <v/>
       </c>
       <c r="C67" t="str">
         <v>BULL S 13,1</v>

--- a/receptury.xlsx
+++ b/receptury.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,7 +434,7 @@
         <v>2026-06-03 10:18:30</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-10 14:31:52</v>
+        <v>2026-06-15 11:02:12</v>
       </c>
       <c r="F2" t="str">
         <v>Default</v>
@@ -460,16 +460,36 @@
         <v>Default</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4">
+        <v>1781514156350</v>
+      </c>
+      <c r="B4" t="str">
+        <v>selval</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-06-15 11:02:36</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-15 11:02:36</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2026-06-15 11:02:52</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Default</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:S102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4424,9 +4444,2074 @@
         <v>Kopia tymczasowa</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B68" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C68" t="str">
+        <v>SELVA L 215,5 FR</v>
+      </c>
+      <c r="D68" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E68">
+        <v>2155</v>
+      </c>
+      <c r="F68">
+        <v>30</v>
+      </c>
+      <c r="G68">
+        <v>60</v>
+      </c>
+      <c r="H68" t="str">
+        <v>So</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="K68">
+        <v>26</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="str">
+        <v>203</v>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68">
+        <v>210</v>
+      </c>
+      <c r="Q68" t="str">
+        <v>1</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B69" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C69" t="str">
+        <v>SELVA L 215,5 FR+KL</v>
+      </c>
+      <c r="D69" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E69">
+        <v>2155</v>
+      </c>
+      <c r="F69">
+        <v>30</v>
+      </c>
+      <c r="G69">
+        <v>60</v>
+      </c>
+      <c r="H69" t="str">
+        <v>So</v>
+      </c>
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69">
+        <v>26</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="M69" t="str">
+        <v>405</v>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69">
+        <v>210</v>
+      </c>
+      <c r="Q69" t="str">
+        <v>2</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B70" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C70" t="str">
+        <v>SELVA L 209,5 KL</v>
+      </c>
+      <c r="D70" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E70">
+        <v>2095</v>
+      </c>
+      <c r="F70">
+        <v>30</v>
+      </c>
+      <c r="G70">
+        <v>60</v>
+      </c>
+      <c r="H70" t="str">
+        <v>So</v>
+      </c>
+      <c r="I70">
+        <v>2</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="K70">
+        <v>26</v>
+      </c>
+      <c r="L70">
+        <v>2</v>
+      </c>
+      <c r="M70" t="str">
+        <v>11110</v>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70">
+        <v>210</v>
+      </c>
+      <c r="Q70" t="str">
+        <v>5</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B71" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C71" t="str">
+        <v>SELVA L 134</v>
+      </c>
+      <c r="D71" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E71">
+        <v>1340</v>
+      </c>
+      <c r="F71">
+        <v>30</v>
+      </c>
+      <c r="G71">
+        <v>60</v>
+      </c>
+      <c r="H71" t="str">
+        <v>So</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71">
+        <v>26</v>
+      </c>
+      <c r="L71">
+        <v>3</v>
+      </c>
+      <c r="M71" t="str">
+        <v>607</v>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71">
+        <v>210</v>
+      </c>
+      <c r="Q71" t="str">
+        <v>3</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B72" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C72" t="str">
+        <v>SELVA L 134 FR+KL</v>
+      </c>
+      <c r="D72" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E72">
+        <v>1340</v>
+      </c>
+      <c r="F72">
+        <v>30</v>
+      </c>
+      <c r="G72">
+        <v>60</v>
+      </c>
+      <c r="H72" t="str">
+        <v>So</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72">
+        <v>2</v>
+      </c>
+      <c r="K72">
+        <v>26</v>
+      </c>
+      <c r="L72">
+        <v>4</v>
+      </c>
+      <c r="M72" t="str">
+        <v>809</v>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72">
+        <v>420</v>
+      </c>
+      <c r="Q72" t="str">
+        <v>4</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B73" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C73" t="str">
+        <v>SELVA L 88 FR</v>
+      </c>
+      <c r="D73" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E73">
+        <v>880</v>
+      </c>
+      <c r="F73">
+        <v>30</v>
+      </c>
+      <c r="G73">
+        <v>60</v>
+      </c>
+      <c r="H73" t="str">
+        <v>So</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73">
+        <v>2</v>
+      </c>
+      <c r="K73">
+        <v>26</v>
+      </c>
+      <c r="L73">
+        <v>5</v>
+      </c>
+      <c r="M73" t="str">
+        <v>405</v>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73">
+        <v>420</v>
+      </c>
+      <c r="Q73" t="str">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B74" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C74" t="str">
+        <v>SELVA L 63 FR</v>
+      </c>
+      <c r="D74" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E74">
+        <v>630</v>
+      </c>
+      <c r="F74">
+        <v>30</v>
+      </c>
+      <c r="G74">
+        <v>60</v>
+      </c>
+      <c r="H74" t="str">
+        <v>So</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="K74">
+        <v>26</v>
+      </c>
+      <c r="L74">
+        <v>6</v>
+      </c>
+      <c r="M74" t="str">
+        <v>10</v>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74">
+        <v>420</v>
+      </c>
+      <c r="Q74" t="str">
+        <v>5</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B75" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C75" t="str">
+        <v>SELVA L 57</v>
+      </c>
+      <c r="D75" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E75">
+        <v>570</v>
+      </c>
+      <c r="F75">
+        <v>30</v>
+      </c>
+      <c r="G75">
+        <v>60</v>
+      </c>
+      <c r="H75" t="str">
+        <v>So</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="K75">
+        <v>26</v>
+      </c>
+      <c r="L75">
+        <v>7</v>
+      </c>
+      <c r="M75" t="str">
+        <v>809</v>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75">
+        <v>1050</v>
+      </c>
+      <c r="Q75" t="str">
+        <v>4</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B76" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C76" t="str">
+        <v>SELVA L 22</v>
+      </c>
+      <c r="D76" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E76">
+        <v>220</v>
+      </c>
+      <c r="F76">
+        <v>30</v>
+      </c>
+      <c r="G76">
+        <v>60</v>
+      </c>
+      <c r="H76" t="str">
+        <v>So</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76">
+        <v>26</v>
+      </c>
+      <c r="L76">
+        <v>8</v>
+      </c>
+      <c r="M76" t="str">
+        <v>4</v>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76">
+        <v>1260</v>
+      </c>
+      <c r="Q76" t="str">
+        <v>2</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B77" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C77" t="str">
+        <v>SELVA L 86,5 SZ</v>
+      </c>
+      <c r="D77" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E77">
+        <v>865</v>
+      </c>
+      <c r="F77">
+        <v>30</v>
+      </c>
+      <c r="G77">
+        <v>60</v>
+      </c>
+      <c r="H77" t="str">
+        <v>So</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>26</v>
+      </c>
+      <c r="L77">
+        <v>9</v>
+      </c>
+      <c r="M77" t="str">
+        <v>203</v>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77">
+        <v>420</v>
+      </c>
+      <c r="Q77" t="str">
+        <v>1</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B78" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C78" t="str">
+        <v>SELVA L 11 SZ</v>
+      </c>
+      <c r="D78" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E78">
+        <v>110</v>
+      </c>
+      <c r="F78">
+        <v>30</v>
+      </c>
+      <c r="G78">
+        <v>60</v>
+      </c>
+      <c r="H78" t="str">
+        <v>So</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>26</v>
+      </c>
+      <c r="L78">
+        <v>10</v>
+      </c>
+      <c r="M78" t="str">
+        <v>2</v>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78">
+        <v>1260</v>
+      </c>
+      <c r="Q78" t="str">
+        <v>1</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B79" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C79" t="str">
+        <v>SELVA L 23</v>
+      </c>
+      <c r="D79" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E79">
+        <v>230</v>
+      </c>
+      <c r="F79">
+        <v>30</v>
+      </c>
+      <c r="G79">
+        <v>60</v>
+      </c>
+      <c r="H79" t="str">
+        <v>So</v>
+      </c>
+      <c r="I79">
+        <v>2</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79">
+        <v>26</v>
+      </c>
+      <c r="L79">
+        <v>11</v>
+      </c>
+      <c r="M79" t="str">
+        <v>6</v>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79">
+        <v>630</v>
+      </c>
+      <c r="Q79" t="str">
+        <v>3</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B80" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C80" t="str">
+        <v>SELVA L 17,9</v>
+      </c>
+      <c r="D80" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E80">
+        <v>179</v>
+      </c>
+      <c r="F80">
+        <v>30</v>
+      </c>
+      <c r="G80">
+        <v>80</v>
+      </c>
+      <c r="H80" t="str">
+        <v>So</v>
+      </c>
+      <c r="I80">
+        <v>2</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80">
+        <v>26</v>
+      </c>
+      <c r="L80">
+        <v>12</v>
+      </c>
+      <c r="M80" t="str">
+        <v>2</v>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80">
+        <v>2100</v>
+      </c>
+      <c r="Q80" t="str">
+        <v>1</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B81" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C81" t="str">
+        <v>SELVA L 35 SZ</v>
+      </c>
+      <c r="D81" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E81">
+        <v>350</v>
+      </c>
+      <c r="F81">
+        <v>30</v>
+      </c>
+      <c r="G81">
+        <v>30</v>
+      </c>
+      <c r="H81" t="str">
+        <v>So</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>26</v>
+      </c>
+      <c r="L81">
+        <v>13</v>
+      </c>
+      <c r="M81" t="str">
+        <v>2</v>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81">
+        <v>420</v>
+      </c>
+      <c r="Q81" t="str">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B82" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C82" t="str">
+        <v>SELVA L 80 PR</v>
+      </c>
+      <c r="D82" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E82">
+        <v>800</v>
+      </c>
+      <c r="F82">
+        <v>25</v>
+      </c>
+      <c r="G82">
+        <v>40</v>
+      </c>
+      <c r="H82" t="str">
+        <v>So</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+      <c r="K82">
+        <v>26</v>
+      </c>
+      <c r="L82">
+        <v>14</v>
+      </c>
+      <c r="M82" t="str">
+        <v>203</v>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82">
+        <v>420</v>
+      </c>
+      <c r="Q82" t="str">
+        <v>1</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B83" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C83" t="str">
+        <v>SELVA L 156,5</v>
+      </c>
+      <c r="D83" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E83">
+        <v>1565</v>
+      </c>
+      <c r="F83">
+        <v>25</v>
+      </c>
+      <c r="G83">
+        <v>25</v>
+      </c>
+      <c r="H83" t="str">
+        <v>So</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="K83">
+        <v>26</v>
+      </c>
+      <c r="L83">
+        <v>15</v>
+      </c>
+      <c r="M83" t="str">
+        <v>607</v>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83">
+        <v>210</v>
+      </c>
+      <c r="Q83" t="str">
+        <v>3</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B84" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C84" t="str">
+        <v>SELVA L 136</v>
+      </c>
+      <c r="D84" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E84">
+        <v>1360</v>
+      </c>
+      <c r="F84">
+        <v>25</v>
+      </c>
+      <c r="G84">
+        <v>25</v>
+      </c>
+      <c r="H84" t="str">
+        <v>So</v>
+      </c>
+      <c r="I84">
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <v>2</v>
+      </c>
+      <c r="K84">
+        <v>26</v>
+      </c>
+      <c r="L84">
+        <v>16</v>
+      </c>
+      <c r="M84" t="str">
+        <v>405</v>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84">
+        <v>210</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>2</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B85" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C85" t="str">
+        <v>SELVA L 132</v>
+      </c>
+      <c r="D85" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E85">
+        <v>1320</v>
+      </c>
+      <c r="F85">
+        <v>25</v>
+      </c>
+      <c r="G85">
+        <v>25</v>
+      </c>
+      <c r="H85" t="str">
+        <v>So</v>
+      </c>
+      <c r="I85">
+        <v>2</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85">
+        <v>26</v>
+      </c>
+      <c r="L85">
+        <v>17</v>
+      </c>
+      <c r="M85" t="str">
+        <v>11110</v>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85">
+        <v>210</v>
+      </c>
+      <c r="Q85" t="str">
+        <v>5</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B86" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C86" t="str">
+        <v>SELVA L 134</v>
+      </c>
+      <c r="D86" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E86">
+        <v>1340</v>
+      </c>
+      <c r="F86">
+        <v>25</v>
+      </c>
+      <c r="G86">
+        <v>25</v>
+      </c>
+      <c r="H86" t="str">
+        <v>So</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="K86">
+        <v>26</v>
+      </c>
+      <c r="L86">
+        <v>18</v>
+      </c>
+      <c r="M86" t="str">
+        <v>203</v>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86">
+        <v>630</v>
+      </c>
+      <c r="Q86" t="str">
+        <v>1</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B87" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C87" t="str">
+        <v>SELVA L 125</v>
+      </c>
+      <c r="D87" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E87">
+        <v>1250</v>
+      </c>
+      <c r="F87">
+        <v>25</v>
+      </c>
+      <c r="G87">
+        <v>25</v>
+      </c>
+      <c r="H87" t="str">
+        <v>So</v>
+      </c>
+      <c r="I87">
+        <v>2</v>
+      </c>
+      <c r="J87">
+        <v>2</v>
+      </c>
+      <c r="K87">
+        <v>26</v>
+      </c>
+      <c r="L87">
+        <v>19</v>
+      </c>
+      <c r="M87" t="str">
+        <v>809</v>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87">
+        <v>210</v>
+      </c>
+      <c r="Q87" t="str">
+        <v>4</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B88" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C88" t="str">
+        <v>SELVA L 112 SZ</v>
+      </c>
+      <c r="D88" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E88">
+        <v>1120</v>
+      </c>
+      <c r="F88">
+        <v>25</v>
+      </c>
+      <c r="G88">
+        <v>25</v>
+      </c>
+      <c r="H88" t="str">
+        <v>So</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88">
+        <v>26</v>
+      </c>
+      <c r="L88">
+        <v>20</v>
+      </c>
+      <c r="M88" t="str">
+        <v>607</v>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88">
+        <v>210</v>
+      </c>
+      <c r="Q88" t="str">
+        <v>3</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B89" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C89" t="str">
+        <v>SELVA L 85,5</v>
+      </c>
+      <c r="D89" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E89">
+        <v>855</v>
+      </c>
+      <c r="F89">
+        <v>25</v>
+      </c>
+      <c r="G89">
+        <v>25</v>
+      </c>
+      <c r="H89" t="str">
+        <v>So</v>
+      </c>
+      <c r="I89">
+        <v>2</v>
+      </c>
+      <c r="J89">
+        <v>2</v>
+      </c>
+      <c r="K89">
+        <v>26</v>
+      </c>
+      <c r="L89">
+        <v>21</v>
+      </c>
+      <c r="M89" t="str">
+        <v>405</v>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89">
+        <v>210</v>
+      </c>
+      <c r="Q89" t="str">
+        <v>2</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B90" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C90" t="str">
+        <v>SELVA L 65</v>
+      </c>
+      <c r="D90" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E90">
+        <v>650</v>
+      </c>
+      <c r="F90">
+        <v>25</v>
+      </c>
+      <c r="G90">
+        <v>25</v>
+      </c>
+      <c r="H90" t="str">
+        <v>So</v>
+      </c>
+      <c r="I90">
+        <v>2</v>
+      </c>
+      <c r="J90">
+        <v>2</v>
+      </c>
+      <c r="K90">
+        <v>26</v>
+      </c>
+      <c r="L90">
+        <v>22</v>
+      </c>
+      <c r="M90" t="str">
+        <v>203</v>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90">
+        <v>210</v>
+      </c>
+      <c r="Q90" t="str">
+        <v>1</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B91" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C91" t="str">
+        <v>SELVA L 61</v>
+      </c>
+      <c r="D91" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E91">
+        <v>610</v>
+      </c>
+      <c r="F91">
+        <v>25</v>
+      </c>
+      <c r="G91">
+        <v>25</v>
+      </c>
+      <c r="H91" t="str">
+        <v>So</v>
+      </c>
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91">
+        <v>2</v>
+      </c>
+      <c r="K91">
+        <v>26</v>
+      </c>
+      <c r="L91">
+        <v>23</v>
+      </c>
+      <c r="M91" t="str">
+        <v>10</v>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91">
+        <v>210</v>
+      </c>
+      <c r="Q91" t="str">
+        <v>5</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B92" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C92" t="str">
+        <v>SELVA L 49</v>
+      </c>
+      <c r="D92" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E92">
+        <v>490</v>
+      </c>
+      <c r="F92">
+        <v>25</v>
+      </c>
+      <c r="G92">
+        <v>25</v>
+      </c>
+      <c r="H92" t="str">
+        <v>So</v>
+      </c>
+      <c r="I92">
+        <v>2</v>
+      </c>
+      <c r="J92">
+        <v>2</v>
+      </c>
+      <c r="K92">
+        <v>26</v>
+      </c>
+      <c r="L92">
+        <v>24</v>
+      </c>
+      <c r="M92" t="str">
+        <v>8</v>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92">
+        <v>210</v>
+      </c>
+      <c r="Q92" t="str">
+        <v>4</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B93" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C93" t="str">
+        <v>SELVA L 46,5</v>
+      </c>
+      <c r="D93" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E93">
+        <v>465</v>
+      </c>
+      <c r="F93">
+        <v>25</v>
+      </c>
+      <c r="G93">
+        <v>25</v>
+      </c>
+      <c r="H93" t="str">
+        <v>So</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93">
+        <v>26</v>
+      </c>
+      <c r="L93">
+        <v>25</v>
+      </c>
+      <c r="M93" t="str">
+        <v>6</v>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93">
+        <v>630</v>
+      </c>
+      <c r="Q93" t="str">
+        <v>3</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B94" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C94" t="str">
+        <v>SELVA L 15,5</v>
+      </c>
+      <c r="D94" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E94">
+        <v>155</v>
+      </c>
+      <c r="F94">
+        <v>25</v>
+      </c>
+      <c r="G94">
+        <v>25</v>
+      </c>
+      <c r="H94" t="str">
+        <v>So</v>
+      </c>
+      <c r="I94">
+        <v>2</v>
+      </c>
+      <c r="J94">
+        <v>2</v>
+      </c>
+      <c r="K94">
+        <v>26</v>
+      </c>
+      <c r="L94">
+        <v>26</v>
+      </c>
+      <c r="M94" t="str">
+        <v>2</v>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94">
+        <v>1470</v>
+      </c>
+      <c r="Q94" t="str">
+        <v>1</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B95" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C95" t="str">
+        <v>SELVA L 25,5</v>
+      </c>
+      <c r="D95" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E95">
+        <v>255</v>
+      </c>
+      <c r="F95">
+        <v>25</v>
+      </c>
+      <c r="G95">
+        <v>25</v>
+      </c>
+      <c r="H95" t="str">
+        <v>So</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>2</v>
+      </c>
+      <c r="K95">
+        <v>26</v>
+      </c>
+      <c r="L95">
+        <v>27</v>
+      </c>
+      <c r="M95" t="str">
+        <v>4</v>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95">
+        <v>420</v>
+      </c>
+      <c r="Q95" t="str">
+        <v>2</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B96" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C96" t="str">
+        <v>SELVA L 137 SZ</v>
+      </c>
+      <c r="D96" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E96">
+        <v>1370</v>
+      </c>
+      <c r="F96">
+        <v>25</v>
+      </c>
+      <c r="G96">
+        <v>50</v>
+      </c>
+      <c r="H96" t="str">
+        <v>So</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96">
+        <v>26</v>
+      </c>
+      <c r="L96">
+        <v>28</v>
+      </c>
+      <c r="M96" t="str">
+        <v>405</v>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96">
+        <v>210</v>
+      </c>
+      <c r="Q96" t="str">
+        <v>2</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B97" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C97" t="str">
+        <v>SELVA L 112 SZ</v>
+      </c>
+      <c r="D97" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E97">
+        <v>1120</v>
+      </c>
+      <c r="F97">
+        <v>25</v>
+      </c>
+      <c r="G97">
+        <v>50</v>
+      </c>
+      <c r="H97" t="str">
+        <v>So</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>26</v>
+      </c>
+      <c r="L97">
+        <v>29</v>
+      </c>
+      <c r="M97" t="str">
+        <v>203</v>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97">
+        <v>210</v>
+      </c>
+      <c r="Q97" t="str">
+        <v>1</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B98" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C98" t="str">
+        <v>SELVA L 86,5 SZ</v>
+      </c>
+      <c r="D98" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E98">
+        <v>865</v>
+      </c>
+      <c r="F98">
+        <v>25</v>
+      </c>
+      <c r="G98">
+        <v>50</v>
+      </c>
+      <c r="H98" t="str">
+        <v>So</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98">
+        <v>26</v>
+      </c>
+      <c r="L98">
+        <v>30</v>
+      </c>
+      <c r="M98" t="str">
+        <v>11110</v>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98">
+        <v>210</v>
+      </c>
+      <c r="Q98" t="str">
+        <v>5</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B99" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C99" t="str">
+        <v>SELVA L 22</v>
+      </c>
+      <c r="D99" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E99">
+        <v>220</v>
+      </c>
+      <c r="F99">
+        <v>25</v>
+      </c>
+      <c r="G99">
+        <v>50</v>
+      </c>
+      <c r="H99" t="str">
+        <v>So</v>
+      </c>
+      <c r="I99">
+        <v>2</v>
+      </c>
+      <c r="J99">
+        <v>2</v>
+      </c>
+      <c r="K99">
+        <v>26</v>
+      </c>
+      <c r="L99">
+        <v>31</v>
+      </c>
+      <c r="M99" t="str">
+        <v>8</v>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99">
+        <v>1260</v>
+      </c>
+      <c r="Q99" t="str">
+        <v>4</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B100" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C100" t="str">
+        <v>SELVA L 7,5</v>
+      </c>
+      <c r="D100" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E100">
+        <v>75</v>
+      </c>
+      <c r="F100">
+        <v>25</v>
+      </c>
+      <c r="G100">
+        <v>50</v>
+      </c>
+      <c r="H100" t="str">
+        <v>So</v>
+      </c>
+      <c r="I100">
+        <v>2</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100">
+        <v>26</v>
+      </c>
+      <c r="L100">
+        <v>32</v>
+      </c>
+      <c r="M100" t="str">
+        <v>6</v>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100">
+        <v>210</v>
+      </c>
+      <c r="Q100" t="str">
+        <v>3</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B101" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C101" t="str">
+        <v>SELVA L 5,5</v>
+      </c>
+      <c r="D101" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E101">
+        <v>55</v>
+      </c>
+      <c r="F101">
+        <v>25</v>
+      </c>
+      <c r="G101">
+        <v>50</v>
+      </c>
+      <c r="H101" t="str">
+        <v>So</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101">
+        <v>2</v>
+      </c>
+      <c r="K101">
+        <v>26</v>
+      </c>
+      <c r="L101">
+        <v>33</v>
+      </c>
+      <c r="M101" t="str">
+        <v>4</v>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101">
+        <v>420</v>
+      </c>
+      <c r="Q101" t="str">
+        <v>2</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+      <c r="S101" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>selval</v>
+      </c>
+      <c r="B102" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C102" t="str">
+        <v>SELVA L 4</v>
+      </c>
+      <c r="D102" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E102">
+        <v>40</v>
+      </c>
+      <c r="F102">
+        <v>25</v>
+      </c>
+      <c r="G102">
+        <v>50</v>
+      </c>
+      <c r="H102" t="str">
+        <v>So</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="J102">
+        <v>2</v>
+      </c>
+      <c r="K102">
+        <v>26</v>
+      </c>
+      <c r="L102">
+        <v>34</v>
+      </c>
+      <c r="M102" t="str">
+        <v>2</v>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102">
+        <v>420</v>
+      </c>
+      <c r="Q102" t="str">
+        <v>1</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/receptury.xlsx
+++ b/receptury.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,7 +434,7 @@
         <v>2026-06-03 10:18:30</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-15 11:02:12</v>
+        <v>2026-06-26 06:59:52</v>
       </c>
       <c r="F2" t="str">
         <v>Default</v>
@@ -454,7 +454,7 @@
         <v>2026-06-09 07:42:59</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-06-09 07:43:54</v>
+        <v>2026-06-29 07:37:42</v>
       </c>
       <c r="F3" t="str">
         <v>Default</v>
@@ -474,22 +474,62 @@
         <v>2026-06-15 11:02:36</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-15 11:02:52</v>
+        <v>2026-06-24 13:29:30</v>
       </c>
       <c r="F4" t="str">
         <v>Default</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5">
+        <v>1781862748755</v>
+      </c>
+      <c r="B5" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-06-19 11:52:28</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-19 11:52:28</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-06-22 14:48:49</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Default</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1782300859277</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-06-24 13:34:19</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-24 13:34:19</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-06-24 13:35:11</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Default</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S102"/>
+  <dimension ref="A1:T172"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -532,21 +572,24 @@
         <v>wybijak</v>
       </c>
       <c r="N1" t="str">
+        <v>DzialanieWybijakow</v>
+      </c>
+      <c r="O1" t="str">
         <v>grupa</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>priorytet</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>ilosc</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>Stanowisko</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>iloscWykonana</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>Informacje</v>
       </c>
     </row>
@@ -596,16 +639,19 @@
       <c r="O2" t="str">
         <v/>
       </c>
-      <c r="P2">
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2">
         <v>300</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>4</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2" t="str">
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -655,16 +701,19 @@
       <c r="O3" t="str">
         <v/>
       </c>
-      <c r="P3">
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3">
         <v>150</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>3</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3" t="str">
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -714,16 +763,19 @@
       <c r="O4" t="str">
         <v/>
       </c>
-      <c r="P4">
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4">
         <v>300</v>
       </c>
-      <c r="Q4" t="str">
-        <v>2</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4" t="str">
+      <c r="R4" t="str">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -773,16 +825,19 @@
       <c r="O5" t="str">
         <v/>
       </c>
-      <c r="P5">
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5">
         <v>150</v>
       </c>
-      <c r="Q5" t="str">
-        <v>2</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5" t="str">
+      <c r="R5" t="str">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -832,16 +887,19 @@
       <c r="O6" t="str">
         <v/>
       </c>
-      <c r="P6">
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6">
         <v>300</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <v>4</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6" t="str">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -891,16 +949,19 @@
       <c r="O7" t="str">
         <v/>
       </c>
-      <c r="P7">
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7">
         <v>300</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="R7" t="str">
         <v>3</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7" t="str">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -950,16 +1011,19 @@
       <c r="O8" t="str">
         <v/>
       </c>
-      <c r="P8">
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8">
         <v>900</v>
       </c>
-      <c r="Q8" t="str">
-        <v>2</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8" t="str">
+      <c r="R8" t="str">
+        <v>2</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1009,16 +1073,19 @@
       <c r="O9" t="str">
         <v/>
       </c>
-      <c r="P9">
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9">
         <v>300</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="R9" t="str">
         <v>4</v>
       </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9" t="str">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1068,16 +1135,19 @@
       <c r="O10" t="str">
         <v/>
       </c>
-      <c r="P10">
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10">
         <v>150</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="R10" t="str">
         <v>3</v>
       </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10" t="str">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1127,16 +1197,19 @@
       <c r="O11" t="str">
         <v/>
       </c>
-      <c r="P11">
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11">
         <v>750</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="R11" t="str">
         <v>dysza</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11" t="str">
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1186,16 +1259,19 @@
       <c r="O12" t="str">
         <v/>
       </c>
-      <c r="P12">
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12">
         <v>900</v>
       </c>
-      <c r="Q12" t="str">
-        <v>2</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12" t="str">
+      <c r="R12" t="str">
+        <v>2</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1245,16 +1321,19 @@
       <c r="O13" t="str">
         <v/>
       </c>
-      <c r="P13">
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13">
         <v>300</v>
       </c>
-      <c r="Q13" t="str">
-        <v>2</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13" t="str">
+      <c r="R13" t="str">
+        <v>2</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1304,16 +1383,19 @@
       <c r="O14" t="str">
         <v/>
       </c>
-      <c r="P14">
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14">
         <v>300</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="R14" t="str">
         <v>4</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14" t="str">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1363,16 +1445,19 @@
       <c r="O15" t="str">
         <v/>
       </c>
-      <c r="P15">
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15">
         <v>150</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="R15" t="str">
         <v>3</v>
       </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15" t="str">
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1422,16 +1507,19 @@
       <c r="O16" t="str">
         <v/>
       </c>
-      <c r="P16">
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16">
         <v>300</v>
       </c>
-      <c r="Q16" t="str">
-        <v>2</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16" t="str">
+      <c r="R16" t="str">
+        <v>2</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1481,16 +1569,19 @@
       <c r="O17" t="str">
         <v/>
       </c>
-      <c r="P17">
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17">
         <v>450</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="R17" t="str">
         <v>4</v>
       </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17" t="str">
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1540,16 +1631,19 @@
       <c r="O18" t="str">
         <v/>
       </c>
-      <c r="P18">
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18">
         <v>150</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="R18" t="str">
         <v>3</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18" t="str">
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1599,16 +1693,19 @@
       <c r="O19" t="str">
         <v/>
       </c>
-      <c r="P19">
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19">
         <v>900</v>
       </c>
-      <c r="Q19" t="str">
-        <v>2</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19" t="str">
+      <c r="R19" t="str">
+        <v>2</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1658,16 +1755,19 @@
       <c r="O20" t="str">
         <v/>
       </c>
-      <c r="P20">
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20">
         <v>450</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="R20" t="str">
         <v>4</v>
       </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20" t="str">
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1717,16 +1817,19 @@
       <c r="O21" t="str">
         <v/>
       </c>
-      <c r="P21">
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21">
         <v>300</v>
       </c>
-      <c r="Q21" t="str">
+      <c r="R21" t="str">
         <v>3</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21" t="str">
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1776,16 +1879,19 @@
       <c r="O22" t="str">
         <v/>
       </c>
-      <c r="P22">
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22">
         <v>300</v>
       </c>
-      <c r="Q22" t="str">
-        <v>2</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22" t="str">
+      <c r="R22" t="str">
+        <v>2</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1835,16 +1941,19 @@
       <c r="O23" t="str">
         <v/>
       </c>
-      <c r="P23">
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23">
         <v>150</v>
       </c>
-      <c r="Q23" t="str">
+      <c r="R23" t="str">
         <v>4</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23" t="str">
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1894,16 +2003,19 @@
       <c r="O24" t="str">
         <v/>
       </c>
-      <c r="P24">
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24">
         <v>150</v>
       </c>
-      <c r="Q24" t="str">
+      <c r="R24" t="str">
         <v>3</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24" t="str">
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -1953,16 +2065,19 @@
       <c r="O25" t="str">
         <v/>
       </c>
-      <c r="P25">
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25">
         <v>450</v>
       </c>
-      <c r="Q25" t="str">
-        <v>2</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25" t="str">
+      <c r="R25" t="str">
+        <v>2</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2012,16 +2127,19 @@
       <c r="O26" t="str">
         <v/>
       </c>
-      <c r="P26">
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26">
         <v>450</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="R26" t="str">
         <v>3</v>
       </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26" t="str">
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2071,16 +2189,19 @@
       <c r="O27" t="str">
         <v/>
       </c>
-      <c r="P27">
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27">
         <v>600</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="R27" t="str">
         <v>4</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27" t="str">
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2130,16 +2251,19 @@
       <c r="O28" t="str">
         <v/>
       </c>
-      <c r="P28">
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28">
         <v>300</v>
       </c>
-      <c r="Q28" t="str">
-        <v>2</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28" t="str">
+      <c r="R28" t="str">
+        <v>2</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2189,16 +2313,19 @@
       <c r="O29" t="str">
         <v/>
       </c>
-      <c r="P29">
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29">
         <v>150</v>
       </c>
-      <c r="Q29" t="str">
+      <c r="R29" t="str">
         <v>4</v>
       </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29" t="str">
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2248,16 +2375,19 @@
       <c r="O30" t="str">
         <v/>
       </c>
-      <c r="P30">
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30">
         <v>1050</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="R30" t="str">
         <v>3</v>
       </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30" t="str">
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2307,16 +2437,19 @@
       <c r="O31" t="str">
         <v/>
       </c>
-      <c r="P31">
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31">
         <v>600</v>
       </c>
-      <c r="Q31" t="str">
-        <v>2</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31" t="str">
+      <c r="R31" t="str">
+        <v>2</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2366,16 +2499,19 @@
       <c r="O32" t="str">
         <v/>
       </c>
-      <c r="P32">
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32">
         <v>300</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="R32" t="str">
         <v>4</v>
       </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32" t="str">
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2425,16 +2561,19 @@
       <c r="O33" t="str">
         <v/>
       </c>
-      <c r="P33">
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33">
         <v>900</v>
       </c>
-      <c r="Q33" t="str">
+      <c r="R33" t="str">
         <v>3</v>
       </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33" t="str">
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2484,16 +2623,19 @@
       <c r="O34" t="str">
         <v/>
       </c>
-      <c r="P34">
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34">
         <v>1050</v>
       </c>
-      <c r="Q34" t="str">
-        <v>2</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34" t="str">
+      <c r="R34" t="str">
+        <v>2</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2543,16 +2685,19 @@
       <c r="O35" t="str">
         <v/>
       </c>
-      <c r="P35">
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35">
         <v>300</v>
       </c>
-      <c r="Q35" t="str">
-        <v>2</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35" t="str">
+      <c r="R35" t="str">
+        <v>2</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2602,16 +2747,19 @@
       <c r="O36" t="str">
         <v/>
       </c>
-      <c r="P36">
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36">
         <v>150</v>
       </c>
-      <c r="Q36" t="str">
+      <c r="R36" t="str">
         <v>4</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36" t="str">
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2661,16 +2809,19 @@
       <c r="O37" t="str">
         <v/>
       </c>
-      <c r="P37">
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37">
         <v>300</v>
       </c>
-      <c r="Q37" t="str">
-        <v>2</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37" t="str">
+      <c r="R37" t="str">
+        <v>2</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2720,16 +2871,19 @@
       <c r="O38" t="str">
         <v/>
       </c>
-      <c r="P38">
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38">
         <v>150</v>
       </c>
-      <c r="Q38" t="str">
+      <c r="R38" t="str">
         <v>3</v>
       </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38" t="str">
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2779,16 +2933,19 @@
       <c r="O39" t="str">
         <v/>
       </c>
-      <c r="P39">
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39">
         <v>300</v>
       </c>
-      <c r="Q39" t="str">
+      <c r="R39" t="str">
         <v>4</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39" t="str">
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2838,16 +2995,19 @@
       <c r="O40" t="str">
         <v/>
       </c>
-      <c r="P40">
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40">
         <v>300</v>
       </c>
-      <c r="Q40" t="str">
+      <c r="R40" t="str">
         <v>3</v>
       </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40" t="str">
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2897,16 +3057,19 @@
       <c r="O41" t="str">
         <v/>
       </c>
-      <c r="P41">
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41">
         <v>900</v>
       </c>
-      <c r="Q41" t="str">
-        <v>2</v>
-      </c>
-      <c r="R41">
-        <v>0</v>
-      </c>
-      <c r="S41" t="str">
+      <c r="R41" t="str">
+        <v>2</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -2956,16 +3119,19 @@
       <c r="O42" t="str">
         <v/>
       </c>
-      <c r="P42">
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42">
         <v>300</v>
       </c>
-      <c r="Q42" t="str">
+      <c r="R42" t="str">
         <v>4</v>
       </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42" t="str">
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3015,16 +3181,19 @@
       <c r="O43" t="str">
         <v/>
       </c>
-      <c r="P43">
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43">
         <v>150</v>
       </c>
-      <c r="Q43" t="str">
+      <c r="R43" t="str">
         <v>3</v>
       </c>
-      <c r="R43">
-        <v>0</v>
-      </c>
-      <c r="S43" t="str">
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3074,16 +3243,19 @@
       <c r="O44" t="str">
         <v/>
       </c>
-      <c r="P44">
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44">
         <v>750</v>
       </c>
-      <c r="Q44" t="str">
-        <v>2</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44" t="str">
+      <c r="R44" t="str">
+        <v>2</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3133,16 +3305,19 @@
       <c r="O45" t="str">
         <v/>
       </c>
-      <c r="P45">
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45">
         <v>900</v>
       </c>
-      <c r="Q45" t="str">
-        <v>2</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45" t="str">
+      <c r="R45" t="str">
+        <v>2</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3192,16 +3367,19 @@
       <c r="O46" t="str">
         <v/>
       </c>
-      <c r="P46">
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46">
         <v>300</v>
       </c>
-      <c r="Q46" t="str">
-        <v>2</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46" t="str">
+      <c r="R46" t="str">
+        <v>2</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3251,16 +3429,19 @@
       <c r="O47" t="str">
         <v/>
       </c>
-      <c r="P47">
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47">
         <v>300</v>
       </c>
-      <c r="Q47" t="str">
+      <c r="R47" t="str">
         <v>4</v>
       </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47" t="str">
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3310,16 +3491,19 @@
       <c r="O48" t="str">
         <v/>
       </c>
-      <c r="P48">
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48">
         <v>150</v>
       </c>
-      <c r="Q48" t="str">
+      <c r="R48" t="str">
         <v>3</v>
       </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48" t="str">
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3369,16 +3553,19 @@
       <c r="O49" t="str">
         <v/>
       </c>
-      <c r="P49">
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49">
         <v>300</v>
       </c>
-      <c r="Q49" t="str">
-        <v>2</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49" t="str">
+      <c r="R49" t="str">
+        <v>2</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3428,16 +3615,19 @@
       <c r="O50" t="str">
         <v/>
       </c>
-      <c r="P50">
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50">
         <v>450</v>
       </c>
-      <c r="Q50" t="str">
+      <c r="R50" t="str">
         <v>4</v>
       </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50" t="str">
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3487,16 +3677,19 @@
       <c r="O51" t="str">
         <v/>
       </c>
-      <c r="P51">
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51">
         <v>150</v>
       </c>
-      <c r="Q51" t="str">
+      <c r="R51" t="str">
         <v>3</v>
       </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51" t="str">
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3546,16 +3739,19 @@
       <c r="O52" t="str">
         <v/>
       </c>
-      <c r="P52">
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52">
         <v>900</v>
       </c>
-      <c r="Q52" t="str">
-        <v>2</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52" t="str">
+      <c r="R52" t="str">
+        <v>2</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3605,16 +3801,19 @@
       <c r="O53" t="str">
         <v/>
       </c>
-      <c r="P53">
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53">
         <v>450</v>
       </c>
-      <c r="Q53" t="str">
+      <c r="R53" t="str">
         <v>4</v>
       </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53" t="str">
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3664,16 +3863,19 @@
       <c r="O54" t="str">
         <v/>
       </c>
-      <c r="P54">
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54">
         <v>300</v>
       </c>
-      <c r="Q54" t="str">
+      <c r="R54" t="str">
         <v>3</v>
       </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54" t="str">
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3723,16 +3925,19 @@
       <c r="O55" t="str">
         <v/>
       </c>
-      <c r="P55">
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55">
         <v>300</v>
       </c>
-      <c r="Q55" t="str">
-        <v>2</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55" t="str">
+      <c r="R55" t="str">
+        <v>2</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3782,16 +3987,19 @@
       <c r="O56" t="str">
         <v/>
       </c>
-      <c r="P56">
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56">
         <v>150</v>
       </c>
-      <c r="Q56" t="str">
+      <c r="R56" t="str">
         <v>4</v>
       </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56" t="str">
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3841,16 +4049,19 @@
       <c r="O57" t="str">
         <v/>
       </c>
-      <c r="P57">
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57">
         <v>150</v>
       </c>
-      <c r="Q57" t="str">
+      <c r="R57" t="str">
         <v>3</v>
       </c>
-      <c r="R57">
-        <v>0</v>
-      </c>
-      <c r="S57" t="str">
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3900,16 +4111,19 @@
       <c r="O58" t="str">
         <v/>
       </c>
-      <c r="P58">
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58">
         <v>450</v>
       </c>
-      <c r="Q58" t="str">
-        <v>2</v>
-      </c>
-      <c r="R58">
-        <v>0</v>
-      </c>
-      <c r="S58" t="str">
+      <c r="R58" t="str">
+        <v>2</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -3959,16 +4173,19 @@
       <c r="O59" t="str">
         <v/>
       </c>
-      <c r="P59">
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59">
         <v>450</v>
       </c>
-      <c r="Q59" t="str">
+      <c r="R59" t="str">
         <v>3</v>
       </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59" t="str">
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4018,16 +4235,19 @@
       <c r="O60" t="str">
         <v/>
       </c>
-      <c r="P60">
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60">
         <v>600</v>
       </c>
-      <c r="Q60" t="str">
+      <c r="R60" t="str">
         <v>4</v>
       </c>
-      <c r="R60">
-        <v>0</v>
-      </c>
-      <c r="S60" t="str">
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4077,16 +4297,19 @@
       <c r="O61" t="str">
         <v/>
       </c>
-      <c r="P61">
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61">
         <v>300</v>
       </c>
-      <c r="Q61" t="str">
-        <v>2</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61" t="str">
+      <c r="R61" t="str">
+        <v>2</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4136,16 +4359,19 @@
       <c r="O62" t="str">
         <v/>
       </c>
-      <c r="P62">
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62">
         <v>150</v>
       </c>
-      <c r="Q62" t="str">
+      <c r="R62" t="str">
         <v>4</v>
       </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62" t="str">
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4195,16 +4421,19 @@
       <c r="O63" t="str">
         <v/>
       </c>
-      <c r="P63">
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63">
         <v>1050</v>
       </c>
-      <c r="Q63" t="str">
+      <c r="R63" t="str">
         <v>3</v>
       </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63" t="str">
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4254,16 +4483,19 @@
       <c r="O64" t="str">
         <v/>
       </c>
-      <c r="P64">
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64">
         <v>600</v>
       </c>
-      <c r="Q64" t="str">
-        <v>2</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64" t="str">
+      <c r="R64" t="str">
+        <v>2</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4313,16 +4545,19 @@
       <c r="O65" t="str">
         <v/>
       </c>
-      <c r="P65">
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65">
         <v>300</v>
       </c>
-      <c r="Q65" t="str">
+      <c r="R65" t="str">
         <v>4</v>
       </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65" t="str">
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4372,16 +4607,19 @@
       <c r="O66" t="str">
         <v/>
       </c>
-      <c r="P66">
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66">
         <v>900</v>
       </c>
-      <c r="Q66" t="str">
+      <c r="R66" t="str">
         <v>3</v>
       </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66" t="str">
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4431,16 +4669,19 @@
       <c r="O67" t="str">
         <v/>
       </c>
-      <c r="P67">
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67">
         <v>1050</v>
       </c>
-      <c r="Q67" t="str">
-        <v>2</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67" t="str">
+      <c r="R67" t="str">
+        <v>2</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4490,16 +4731,19 @@
       <c r="O68" t="str">
         <v/>
       </c>
-      <c r="P68">
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68">
         <v>210</v>
       </c>
-      <c r="Q68" t="str">
+      <c r="R68" t="str">
         <v>1</v>
       </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68" t="str">
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4549,16 +4793,19 @@
       <c r="O69" t="str">
         <v/>
       </c>
-      <c r="P69">
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69">
         <v>210</v>
       </c>
-      <c r="Q69" t="str">
-        <v>2</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69" t="str">
+      <c r="R69" t="str">
+        <v>2</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+      <c r="T69" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4608,16 +4855,19 @@
       <c r="O70" t="str">
         <v/>
       </c>
-      <c r="P70">
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70">
         <v>210</v>
       </c>
-      <c r="Q70" t="str">
+      <c r="R70" t="str">
         <v>5</v>
       </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70" t="str">
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4667,16 +4917,19 @@
       <c r="O71" t="str">
         <v/>
       </c>
-      <c r="P71">
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71">
         <v>210</v>
       </c>
-      <c r="Q71" t="str">
+      <c r="R71" t="str">
         <v>3</v>
       </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71" t="str">
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4726,16 +4979,19 @@
       <c r="O72" t="str">
         <v/>
       </c>
-      <c r="P72">
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72">
         <v>420</v>
       </c>
-      <c r="Q72" t="str">
+      <c r="R72" t="str">
         <v>4</v>
       </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
-      <c r="S72" t="str">
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4785,16 +5041,19 @@
       <c r="O73" t="str">
         <v/>
       </c>
-      <c r="P73">
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73">
         <v>420</v>
       </c>
-      <c r="Q73" t="str">
-        <v>2</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73" t="str">
+      <c r="R73" t="str">
+        <v>2</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4844,16 +5103,19 @@
       <c r="O74" t="str">
         <v/>
       </c>
-      <c r="P74">
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74">
         <v>420</v>
       </c>
-      <c r="Q74" t="str">
+      <c r="R74" t="str">
         <v>5</v>
       </c>
-      <c r="R74">
-        <v>0</v>
-      </c>
-      <c r="S74" t="str">
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4903,16 +5165,19 @@
       <c r="O75" t="str">
         <v/>
       </c>
-      <c r="P75">
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75">
         <v>1050</v>
       </c>
-      <c r="Q75" t="str">
+      <c r="R75" t="str">
         <v>4</v>
       </c>
-      <c r="R75">
-        <v>0</v>
-      </c>
-      <c r="S75" t="str">
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -4962,16 +5227,19 @@
       <c r="O76" t="str">
         <v/>
       </c>
-      <c r="P76">
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76">
         <v>1260</v>
       </c>
-      <c r="Q76" t="str">
-        <v>2</v>
-      </c>
-      <c r="R76">
-        <v>0</v>
-      </c>
-      <c r="S76" t="str">
+      <c r="R76" t="str">
+        <v>2</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5021,16 +5289,19 @@
       <c r="O77" t="str">
         <v/>
       </c>
-      <c r="P77">
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77">
         <v>420</v>
       </c>
-      <c r="Q77" t="str">
+      <c r="R77" t="str">
         <v>1</v>
       </c>
-      <c r="R77">
-        <v>0</v>
-      </c>
-      <c r="S77" t="str">
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5080,16 +5351,19 @@
       <c r="O78" t="str">
         <v/>
       </c>
-      <c r="P78">
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78">
         <v>1260</v>
       </c>
-      <c r="Q78" t="str">
+      <c r="R78" t="str">
         <v>1</v>
       </c>
-      <c r="R78">
-        <v>0</v>
-      </c>
-      <c r="S78" t="str">
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5139,16 +5413,19 @@
       <c r="O79" t="str">
         <v/>
       </c>
-      <c r="P79">
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79">
         <v>630</v>
       </c>
-      <c r="Q79" t="str">
+      <c r="R79" t="str">
         <v>3</v>
       </c>
-      <c r="R79">
-        <v>0</v>
-      </c>
-      <c r="S79" t="str">
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5198,16 +5475,19 @@
       <c r="O80" t="str">
         <v/>
       </c>
-      <c r="P80">
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80">
         <v>2100</v>
       </c>
-      <c r="Q80" t="str">
+      <c r="R80" t="str">
         <v>1</v>
       </c>
-      <c r="R80">
-        <v>0</v>
-      </c>
-      <c r="S80" t="str">
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5257,16 +5537,19 @@
       <c r="O81" t="str">
         <v/>
       </c>
-      <c r="P81">
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81">
         <v>420</v>
       </c>
-      <c r="Q81" t="str">
+      <c r="R81" t="str">
         <v>1</v>
       </c>
-      <c r="R81">
-        <v>0</v>
-      </c>
-      <c r="S81" t="str">
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5316,16 +5599,19 @@
       <c r="O82" t="str">
         <v/>
       </c>
-      <c r="P82">
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82">
         <v>420</v>
       </c>
-      <c r="Q82" t="str">
+      <c r="R82" t="str">
         <v>1</v>
       </c>
-      <c r="R82">
-        <v>0</v>
-      </c>
-      <c r="S82" t="str">
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5375,16 +5661,19 @@
       <c r="O83" t="str">
         <v/>
       </c>
-      <c r="P83">
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83">
         <v>210</v>
       </c>
-      <c r="Q83" t="str">
+      <c r="R83" t="str">
         <v>3</v>
       </c>
-      <c r="R83">
-        <v>0</v>
-      </c>
-      <c r="S83" t="str">
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5434,16 +5723,19 @@
       <c r="O84" t="str">
         <v/>
       </c>
-      <c r="P84">
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84">
         <v>210</v>
       </c>
-      <c r="Q84" t="str">
-        <v>2</v>
-      </c>
-      <c r="R84">
-        <v>0</v>
-      </c>
-      <c r="S84" t="str">
+      <c r="R84" t="str">
+        <v>2</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5493,16 +5785,19 @@
       <c r="O85" t="str">
         <v/>
       </c>
-      <c r="P85">
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85">
         <v>210</v>
       </c>
-      <c r="Q85" t="str">
+      <c r="R85" t="str">
         <v>5</v>
       </c>
-      <c r="R85">
-        <v>0</v>
-      </c>
-      <c r="S85" t="str">
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5552,16 +5847,19 @@
       <c r="O86" t="str">
         <v/>
       </c>
-      <c r="P86">
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86">
         <v>630</v>
       </c>
-      <c r="Q86" t="str">
+      <c r="R86" t="str">
         <v>1</v>
       </c>
-      <c r="R86">
-        <v>0</v>
-      </c>
-      <c r="S86" t="str">
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5611,16 +5909,19 @@
       <c r="O87" t="str">
         <v/>
       </c>
-      <c r="P87">
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87">
         <v>210</v>
       </c>
-      <c r="Q87" t="str">
+      <c r="R87" t="str">
         <v>4</v>
       </c>
-      <c r="R87">
-        <v>0</v>
-      </c>
-      <c r="S87" t="str">
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5670,16 +5971,19 @@
       <c r="O88" t="str">
         <v/>
       </c>
-      <c r="P88">
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88">
         <v>210</v>
       </c>
-      <c r="Q88" t="str">
+      <c r="R88" t="str">
         <v>3</v>
       </c>
-      <c r="R88">
-        <v>0</v>
-      </c>
-      <c r="S88" t="str">
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5729,16 +6033,19 @@
       <c r="O89" t="str">
         <v/>
       </c>
-      <c r="P89">
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89">
         <v>210</v>
       </c>
-      <c r="Q89" t="str">
-        <v>2</v>
-      </c>
-      <c r="R89">
-        <v>0</v>
-      </c>
-      <c r="S89" t="str">
+      <c r="R89" t="str">
+        <v>2</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5788,16 +6095,19 @@
       <c r="O90" t="str">
         <v/>
       </c>
-      <c r="P90">
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90">
         <v>210</v>
       </c>
-      <c r="Q90" t="str">
+      <c r="R90" t="str">
         <v>1</v>
       </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90" t="str">
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5847,16 +6157,19 @@
       <c r="O91" t="str">
         <v/>
       </c>
-      <c r="P91">
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91">
         <v>210</v>
       </c>
-      <c r="Q91" t="str">
+      <c r="R91" t="str">
         <v>5</v>
       </c>
-      <c r="R91">
-        <v>0</v>
-      </c>
-      <c r="S91" t="str">
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5906,16 +6219,19 @@
       <c r="O92" t="str">
         <v/>
       </c>
-      <c r="P92">
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92">
         <v>210</v>
       </c>
-      <c r="Q92" t="str">
+      <c r="R92" t="str">
         <v>4</v>
       </c>
-      <c r="R92">
-        <v>0</v>
-      </c>
-      <c r="S92" t="str">
+      <c r="S92">
+        <v>0</v>
+      </c>
+      <c r="T92" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -5965,16 +6281,19 @@
       <c r="O93" t="str">
         <v/>
       </c>
-      <c r="P93">
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93">
         <v>630</v>
       </c>
-      <c r="Q93" t="str">
+      <c r="R93" t="str">
         <v>3</v>
       </c>
-      <c r="R93">
-        <v>0</v>
-      </c>
-      <c r="S93" t="str">
+      <c r="S93">
+        <v>0</v>
+      </c>
+      <c r="T93" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6024,16 +6343,19 @@
       <c r="O94" t="str">
         <v/>
       </c>
-      <c r="P94">
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94">
         <v>1470</v>
       </c>
-      <c r="Q94" t="str">
+      <c r="R94" t="str">
         <v>1</v>
       </c>
-      <c r="R94">
-        <v>0</v>
-      </c>
-      <c r="S94" t="str">
+      <c r="S94">
+        <v>0</v>
+      </c>
+      <c r="T94" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6083,16 +6405,19 @@
       <c r="O95" t="str">
         <v/>
       </c>
-      <c r="P95">
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95">
         <v>420</v>
       </c>
-      <c r="Q95" t="str">
-        <v>2</v>
-      </c>
-      <c r="R95">
-        <v>0</v>
-      </c>
-      <c r="S95" t="str">
+      <c r="R95" t="str">
+        <v>2</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+      <c r="T95" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6142,16 +6467,19 @@
       <c r="O96" t="str">
         <v/>
       </c>
-      <c r="P96">
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96">
         <v>210</v>
       </c>
-      <c r="Q96" t="str">
-        <v>2</v>
-      </c>
-      <c r="R96">
-        <v>0</v>
-      </c>
-      <c r="S96" t="str">
+      <c r="R96" t="str">
+        <v>2</v>
+      </c>
+      <c r="S96">
+        <v>0</v>
+      </c>
+      <c r="T96" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6201,16 +6529,19 @@
       <c r="O97" t="str">
         <v/>
       </c>
-      <c r="P97">
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97">
         <v>210</v>
       </c>
-      <c r="Q97" t="str">
+      <c r="R97" t="str">
         <v>1</v>
       </c>
-      <c r="R97">
-        <v>0</v>
-      </c>
-      <c r="S97" t="str">
+      <c r="S97">
+        <v>0</v>
+      </c>
+      <c r="T97" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6260,16 +6591,19 @@
       <c r="O98" t="str">
         <v/>
       </c>
-      <c r="P98">
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98">
         <v>210</v>
       </c>
-      <c r="Q98" t="str">
+      <c r="R98" t="str">
         <v>5</v>
       </c>
-      <c r="R98">
-        <v>0</v>
-      </c>
-      <c r="S98" t="str">
+      <c r="S98">
+        <v>0</v>
+      </c>
+      <c r="T98" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6319,16 +6653,19 @@
       <c r="O99" t="str">
         <v/>
       </c>
-      <c r="P99">
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99">
         <v>1260</v>
       </c>
-      <c r="Q99" t="str">
+      <c r="R99" t="str">
         <v>4</v>
       </c>
-      <c r="R99">
-        <v>0</v>
-      </c>
-      <c r="S99" t="str">
+      <c r="S99">
+        <v>0</v>
+      </c>
+      <c r="T99" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6378,16 +6715,19 @@
       <c r="O100" t="str">
         <v/>
       </c>
-      <c r="P100">
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100">
         <v>210</v>
       </c>
-      <c r="Q100" t="str">
+      <c r="R100" t="str">
         <v>3</v>
       </c>
-      <c r="R100">
-        <v>0</v>
-      </c>
-      <c r="S100" t="str">
+      <c r="S100">
+        <v>0</v>
+      </c>
+      <c r="T100" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6437,16 +6777,19 @@
       <c r="O101" t="str">
         <v/>
       </c>
-      <c r="P101">
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101">
         <v>420</v>
       </c>
-      <c r="Q101" t="str">
-        <v>2</v>
-      </c>
-      <c r="R101">
-        <v>0</v>
-      </c>
-      <c r="S101" t="str">
+      <c r="R101" t="str">
+        <v>2</v>
+      </c>
+      <c r="S101">
+        <v>0</v>
+      </c>
+      <c r="T101" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
@@ -6496,22 +6839,4365 @@
       <c r="O102" t="str">
         <v/>
       </c>
-      <c r="P102">
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102">
         <v>420</v>
       </c>
-      <c r="Q102" t="str">
+      <c r="R102" t="str">
         <v>1</v>
       </c>
-      <c r="R102">
-        <v>0</v>
-      </c>
-      <c r="S102" t="str">
+      <c r="S102">
+        <v>0</v>
+      </c>
+      <c r="T102" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B103" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C103" t="str">
+        <v>SELVA L 215,5 FR</v>
+      </c>
+      <c r="D103" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E103">
+        <v>2155</v>
+      </c>
+      <c r="F103">
+        <v>30</v>
+      </c>
+      <c r="G103">
+        <v>60</v>
+      </c>
+      <c r="H103" t="str">
+        <v>So</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
+      </c>
+      <c r="J103">
+        <v>2</v>
+      </c>
+      <c r="K103">
+        <v>26</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103" t="str">
+        <v>809</v>
+      </c>
+      <c r="N103" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103">
+        <v>90</v>
+      </c>
+      <c r="R103" t="str">
+        <v>4</v>
+      </c>
+      <c r="S103">
+        <v>0</v>
+      </c>
+      <c r="T103" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B104" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C104" t="str">
+        <v>SELVA L 215,5 FR+KL</v>
+      </c>
+      <c r="D104" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E104">
+        <v>2155</v>
+      </c>
+      <c r="F104">
+        <v>30</v>
+      </c>
+      <c r="G104">
+        <v>60</v>
+      </c>
+      <c r="H104" t="str">
+        <v>So</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="K104">
+        <v>26</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="M104" t="str">
+        <v>1011</v>
+      </c>
+      <c r="N104" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104">
+        <v>90</v>
+      </c>
+      <c r="R104" t="str">
+        <v>5</v>
+      </c>
+      <c r="S104">
+        <v>0</v>
+      </c>
+      <c r="T104" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B105" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C105" t="str">
+        <v>SELVA L 209,5 KL</v>
+      </c>
+      <c r="D105" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E105">
+        <v>2095</v>
+      </c>
+      <c r="F105">
+        <v>30</v>
+      </c>
+      <c r="G105">
+        <v>60</v>
+      </c>
+      <c r="H105" t="str">
+        <v>So</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105">
+        <v>2</v>
+      </c>
+      <c r="K105">
+        <v>26</v>
+      </c>
+      <c r="L105">
+        <v>2</v>
+      </c>
+      <c r="M105" t="str">
+        <v>607</v>
+      </c>
+      <c r="N105" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105">
+        <v>90</v>
+      </c>
+      <c r="R105" t="str">
+        <v>3</v>
+      </c>
+      <c r="S105">
+        <v>0</v>
+      </c>
+      <c r="T105" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B106" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C106" t="str">
+        <v>SELVA L 134</v>
+      </c>
+      <c r="D106" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E106">
+        <v>1340</v>
+      </c>
+      <c r="F106">
+        <v>30</v>
+      </c>
+      <c r="G106">
+        <v>60</v>
+      </c>
+      <c r="H106" t="str">
+        <v>So</v>
+      </c>
+      <c r="I106">
+        <v>2</v>
+      </c>
+      <c r="J106">
+        <v>2</v>
+      </c>
+      <c r="K106">
+        <v>26</v>
+      </c>
+      <c r="L106">
+        <v>3</v>
+      </c>
+      <c r="M106" t="str">
+        <v>1011</v>
+      </c>
+      <c r="N106" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106">
+        <v>90</v>
+      </c>
+      <c r="R106" t="str">
+        <v>5</v>
+      </c>
+      <c r="S106">
+        <v>0</v>
+      </c>
+      <c r="T106" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B107" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C107" t="str">
+        <v>SELVA L 134 FR+KL</v>
+      </c>
+      <c r="D107" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E107">
+        <v>1340</v>
+      </c>
+      <c r="F107">
+        <v>30</v>
+      </c>
+      <c r="G107">
+        <v>60</v>
+      </c>
+      <c r="H107" t="str">
+        <v>So</v>
+      </c>
+      <c r="I107">
+        <v>2</v>
+      </c>
+      <c r="J107">
+        <v>2</v>
+      </c>
+      <c r="K107">
+        <v>26</v>
+      </c>
+      <c r="L107">
+        <v>4</v>
+      </c>
+      <c r="M107" t="str">
+        <v>405</v>
+      </c>
+      <c r="N107" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107">
+        <v>180</v>
+      </c>
+      <c r="R107" t="str">
+        <v>2</v>
+      </c>
+      <c r="S107">
+        <v>0</v>
+      </c>
+      <c r="T107" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B108" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C108" t="str">
+        <v>SELVA L 88 FR</v>
+      </c>
+      <c r="D108" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E108">
+        <v>880</v>
+      </c>
+      <c r="F108">
+        <v>30</v>
+      </c>
+      <c r="G108">
+        <v>60</v>
+      </c>
+      <c r="H108" t="str">
+        <v>So</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108">
+        <v>26</v>
+      </c>
+      <c r="L108">
+        <v>5</v>
+      </c>
+      <c r="M108" t="str">
+        <v>809</v>
+      </c>
+      <c r="N108" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108">
+        <v>180</v>
+      </c>
+      <c r="R108" t="str">
+        <v>4</v>
+      </c>
+      <c r="S108">
+        <v>0</v>
+      </c>
+      <c r="T108" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B109" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C109" t="str">
+        <v>SELVA L 63 FR</v>
+      </c>
+      <c r="D109" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E109">
+        <v>630</v>
+      </c>
+      <c r="F109">
+        <v>30</v>
+      </c>
+      <c r="G109">
+        <v>60</v>
+      </c>
+      <c r="H109" t="str">
+        <v>So</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109">
+        <v>2</v>
+      </c>
+      <c r="K109">
+        <v>26</v>
+      </c>
+      <c r="L109">
+        <v>6</v>
+      </c>
+      <c r="M109" t="str">
+        <v>405</v>
+      </c>
+      <c r="N109" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109">
+        <v>180</v>
+      </c>
+      <c r="R109" t="str">
+        <v>2</v>
+      </c>
+      <c r="S109">
+        <v>0</v>
+      </c>
+      <c r="T109" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B110" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C110" t="str">
+        <v>SELVA L 57</v>
+      </c>
+      <c r="D110" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E110">
+        <v>570</v>
+      </c>
+      <c r="F110">
+        <v>30</v>
+      </c>
+      <c r="G110">
+        <v>60</v>
+      </c>
+      <c r="H110" t="str">
+        <v>So</v>
+      </c>
+      <c r="I110">
+        <v>2</v>
+      </c>
+      <c r="J110">
+        <v>2</v>
+      </c>
+      <c r="K110">
+        <v>26</v>
+      </c>
+      <c r="L110">
+        <v>7</v>
+      </c>
+      <c r="M110" t="str">
+        <v>11011</v>
+      </c>
+      <c r="N110" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110">
+        <v>450</v>
+      </c>
+      <c r="R110" t="str">
+        <v>5</v>
+      </c>
+      <c r="S110">
+        <v>0</v>
+      </c>
+      <c r="T110" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B111" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C111" t="str">
+        <v>SELVA L 22</v>
+      </c>
+      <c r="D111" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E111">
+        <v>220</v>
+      </c>
+      <c r="F111">
+        <v>30</v>
+      </c>
+      <c r="G111">
+        <v>60</v>
+      </c>
+      <c r="H111" t="str">
+        <v>So</v>
+      </c>
+      <c r="I111">
+        <v>2</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111">
+        <v>26</v>
+      </c>
+      <c r="L111">
+        <v>8</v>
+      </c>
+      <c r="M111" t="str">
+        <v>10607</v>
+      </c>
+      <c r="N111" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111">
+        <v>540</v>
+      </c>
+      <c r="R111" t="str">
+        <v>3</v>
+      </c>
+      <c r="S111">
+        <v>0</v>
+      </c>
+      <c r="T111" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B112" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C112" t="str">
+        <v>SELVA L 86,5 SZ</v>
+      </c>
+      <c r="D112" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E112">
+        <v>865</v>
+      </c>
+      <c r="F112">
+        <v>30</v>
+      </c>
+      <c r="G112">
+        <v>60</v>
+      </c>
+      <c r="H112" t="str">
+        <v>So</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>26</v>
+      </c>
+      <c r="L112">
+        <v>9</v>
+      </c>
+      <c r="M112" t="str">
+        <v>607</v>
+      </c>
+      <c r="N112" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112">
+        <v>180</v>
+      </c>
+      <c r="R112" t="str">
+        <v>3</v>
+      </c>
+      <c r="S112">
+        <v>0</v>
+      </c>
+      <c r="T112" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B113" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C113" t="str">
+        <v>SELVA L 11 SZ</v>
+      </c>
+      <c r="D113" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E113">
+        <v>110</v>
+      </c>
+      <c r="F113">
+        <v>30</v>
+      </c>
+      <c r="G113">
+        <v>60</v>
+      </c>
+      <c r="H113" t="str">
+        <v>So</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="K113">
+        <v>26</v>
+      </c>
+      <c r="L113">
+        <v>10</v>
+      </c>
+      <c r="M113" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N113" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113">
+        <v>540</v>
+      </c>
+      <c r="R113" t="str">
+        <v>2</v>
+      </c>
+      <c r="S113">
+        <v>0</v>
+      </c>
+      <c r="T113" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B114" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C114" t="str">
+        <v>SELVA L 23</v>
+      </c>
+      <c r="D114" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E114">
+        <v>230</v>
+      </c>
+      <c r="F114">
+        <v>30</v>
+      </c>
+      <c r="G114">
+        <v>60</v>
+      </c>
+      <c r="H114" t="str">
+        <v>So</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>26</v>
+      </c>
+      <c r="L114">
+        <v>11</v>
+      </c>
+      <c r="M114" t="str">
+        <v>10809</v>
+      </c>
+      <c r="N114" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114">
+        <v>270</v>
+      </c>
+      <c r="R114" t="str">
+        <v>4</v>
+      </c>
+      <c r="S114">
+        <v>0</v>
+      </c>
+      <c r="T114" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B115" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C115" t="str">
+        <v>SELVA L 17,9</v>
+      </c>
+      <c r="D115" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E115">
+        <v>179</v>
+      </c>
+      <c r="F115">
+        <v>30</v>
+      </c>
+      <c r="G115">
+        <v>80</v>
+      </c>
+      <c r="H115" t="str">
+        <v>So</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="K115">
+        <v>26</v>
+      </c>
+      <c r="L115">
+        <v>12</v>
+      </c>
+      <c r="M115" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N115" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115">
+        <v>900</v>
+      </c>
+      <c r="R115" t="str">
+        <v>2</v>
+      </c>
+      <c r="S115">
+        <v>0</v>
+      </c>
+      <c r="T115" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B116" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C116" t="str">
+        <v>SELVA L 35 SZ</v>
+      </c>
+      <c r="D116" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E116">
+        <v>350</v>
+      </c>
+      <c r="F116">
+        <v>30</v>
+      </c>
+      <c r="G116">
+        <v>30</v>
+      </c>
+      <c r="H116" t="str">
+        <v>So</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="K116">
+        <v>26</v>
+      </c>
+      <c r="L116">
+        <v>13</v>
+      </c>
+      <c r="M116" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N116" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116">
+        <v>180</v>
+      </c>
+      <c r="R116" t="str">
+        <v>2</v>
+      </c>
+      <c r="S116">
+        <v>0</v>
+      </c>
+      <c r="T116" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B117" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C117" t="str">
+        <v>SELVA L 80 PR</v>
+      </c>
+      <c r="D117" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E117">
+        <v>800</v>
+      </c>
+      <c r="F117">
+        <v>25</v>
+      </c>
+      <c r="G117">
+        <v>40</v>
+      </c>
+      <c r="H117" t="str">
+        <v>So</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117">
+        <v>26</v>
+      </c>
+      <c r="L117">
+        <v>14</v>
+      </c>
+      <c r="M117" t="str">
+        <v>405</v>
+      </c>
+      <c r="N117" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117">
+        <v>180</v>
+      </c>
+      <c r="R117" t="str">
+        <v>2</v>
+      </c>
+      <c r="S117">
+        <v>0</v>
+      </c>
+      <c r="T117" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B118" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C118" t="str">
+        <v>SELVA L 156,5</v>
+      </c>
+      <c r="D118" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E118">
+        <v>1565</v>
+      </c>
+      <c r="F118">
+        <v>25</v>
+      </c>
+      <c r="G118">
+        <v>25</v>
+      </c>
+      <c r="H118" t="str">
+        <v>So</v>
+      </c>
+      <c r="I118">
+        <v>2</v>
+      </c>
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="K118">
+        <v>26</v>
+      </c>
+      <c r="L118">
+        <v>15</v>
+      </c>
+      <c r="M118" t="str">
+        <v>405</v>
+      </c>
+      <c r="N118" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118">
+        <v>90</v>
+      </c>
+      <c r="R118" t="str">
+        <v>2</v>
+      </c>
+      <c r="S118">
+        <v>0</v>
+      </c>
+      <c r="T118" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B119" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C119" t="str">
+        <v>SELVA L 136</v>
+      </c>
+      <c r="D119" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E119">
+        <v>1360</v>
+      </c>
+      <c r="F119">
+        <v>25</v>
+      </c>
+      <c r="G119">
+        <v>25</v>
+      </c>
+      <c r="H119" t="str">
+        <v>So</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+      <c r="J119">
+        <v>2</v>
+      </c>
+      <c r="K119">
+        <v>26</v>
+      </c>
+      <c r="L119">
+        <v>16</v>
+      </c>
+      <c r="M119" t="str">
+        <v>1011</v>
+      </c>
+      <c r="N119" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119">
+        <v>90</v>
+      </c>
+      <c r="R119" t="str">
+        <v>5</v>
+      </c>
+      <c r="S119">
+        <v>0</v>
+      </c>
+      <c r="T119" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B120" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C120" t="str">
+        <v>SELVA L 132</v>
+      </c>
+      <c r="D120" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E120">
+        <v>1320</v>
+      </c>
+      <c r="F120">
+        <v>25</v>
+      </c>
+      <c r="G120">
+        <v>25</v>
+      </c>
+      <c r="H120" t="str">
+        <v>So</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120">
+        <v>2</v>
+      </c>
+      <c r="K120">
+        <v>26</v>
+      </c>
+      <c r="L120">
+        <v>17</v>
+      </c>
+      <c r="M120" t="str">
+        <v>607</v>
+      </c>
+      <c r="N120" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120">
+        <v>90</v>
+      </c>
+      <c r="R120" t="str">
+        <v>3</v>
+      </c>
+      <c r="S120">
+        <v>0</v>
+      </c>
+      <c r="T120" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B121" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C121" t="str">
+        <v>SELVA L 134</v>
+      </c>
+      <c r="D121" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E121">
+        <v>1340</v>
+      </c>
+      <c r="F121">
+        <v>25</v>
+      </c>
+      <c r="G121">
+        <v>25</v>
+      </c>
+      <c r="H121" t="str">
+        <v>So</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121">
+        <v>26</v>
+      </c>
+      <c r="L121">
+        <v>18</v>
+      </c>
+      <c r="M121" t="str">
+        <v>809</v>
+      </c>
+      <c r="N121" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121">
+        <v>270</v>
+      </c>
+      <c r="R121" t="str">
+        <v>4</v>
+      </c>
+      <c r="S121">
+        <v>0</v>
+      </c>
+      <c r="T121" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B122" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C122" t="str">
+        <v>SELVA L 125</v>
+      </c>
+      <c r="D122" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E122">
+        <v>1250</v>
+      </c>
+      <c r="F122">
+        <v>25</v>
+      </c>
+      <c r="G122">
+        <v>25</v>
+      </c>
+      <c r="H122" t="str">
+        <v>So</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>26</v>
+      </c>
+      <c r="L122">
+        <v>19</v>
+      </c>
+      <c r="M122" t="str">
+        <v>405</v>
+      </c>
+      <c r="N122" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122">
+        <v>90</v>
+      </c>
+      <c r="R122" t="str">
+        <v>2</v>
+      </c>
+      <c r="S122">
+        <v>0</v>
+      </c>
+      <c r="T122" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B123" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C123" t="str">
+        <v>SELVA L 112 SZ</v>
+      </c>
+      <c r="D123" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E123">
+        <v>1120</v>
+      </c>
+      <c r="F123">
+        <v>25</v>
+      </c>
+      <c r="G123">
+        <v>25</v>
+      </c>
+      <c r="H123" t="str">
+        <v>So</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123">
+        <v>1</v>
+      </c>
+      <c r="K123">
+        <v>26</v>
+      </c>
+      <c r="L123">
+        <v>20</v>
+      </c>
+      <c r="M123" t="str">
+        <v>1011</v>
+      </c>
+      <c r="N123" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123">
+        <v>90</v>
+      </c>
+      <c r="R123" t="str">
+        <v>5</v>
+      </c>
+      <c r="S123">
+        <v>0</v>
+      </c>
+      <c r="T123" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B124" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C124" t="str">
+        <v>SELVA L 85,5</v>
+      </c>
+      <c r="D124" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E124">
+        <v>855</v>
+      </c>
+      <c r="F124">
+        <v>25</v>
+      </c>
+      <c r="G124">
+        <v>25</v>
+      </c>
+      <c r="H124" t="str">
+        <v>So</v>
+      </c>
+      <c r="I124">
+        <v>2</v>
+      </c>
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="K124">
+        <v>26</v>
+      </c>
+      <c r="L124">
+        <v>21</v>
+      </c>
+      <c r="M124" t="str">
+        <v>809</v>
+      </c>
+      <c r="N124" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124">
+        <v>90</v>
+      </c>
+      <c r="R124" t="str">
+        <v>4</v>
+      </c>
+      <c r="S124">
+        <v>0</v>
+      </c>
+      <c r="T124" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B125" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C125" t="str">
+        <v>SELVA L 65</v>
+      </c>
+      <c r="D125" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E125">
+        <v>650</v>
+      </c>
+      <c r="F125">
+        <v>25</v>
+      </c>
+      <c r="G125">
+        <v>25</v>
+      </c>
+      <c r="H125" t="str">
+        <v>So</v>
+      </c>
+      <c r="I125">
+        <v>2</v>
+      </c>
+      <c r="J125">
+        <v>2</v>
+      </c>
+      <c r="K125">
+        <v>26</v>
+      </c>
+      <c r="L125">
+        <v>22</v>
+      </c>
+      <c r="M125" t="str">
+        <v>607</v>
+      </c>
+      <c r="N125" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125">
+        <v>90</v>
+      </c>
+      <c r="R125" t="str">
+        <v>3</v>
+      </c>
+      <c r="S125">
+        <v>0</v>
+      </c>
+      <c r="T125" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B126" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C126" t="str">
+        <v>SELVA L 61</v>
+      </c>
+      <c r="D126" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E126">
+        <v>610</v>
+      </c>
+      <c r="F126">
+        <v>25</v>
+      </c>
+      <c r="G126">
+        <v>25</v>
+      </c>
+      <c r="H126" t="str">
+        <v>So</v>
+      </c>
+      <c r="I126">
+        <v>2</v>
+      </c>
+      <c r="J126">
+        <v>2</v>
+      </c>
+      <c r="K126">
+        <v>26</v>
+      </c>
+      <c r="L126">
+        <v>23</v>
+      </c>
+      <c r="M126" t="str">
+        <v>405</v>
+      </c>
+      <c r="N126" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126">
+        <v>90</v>
+      </c>
+      <c r="R126" t="str">
+        <v>2</v>
+      </c>
+      <c r="S126">
+        <v>0</v>
+      </c>
+      <c r="T126" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B127" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C127" t="str">
+        <v>SELVA L 49</v>
+      </c>
+      <c r="D127" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E127">
+        <v>490</v>
+      </c>
+      <c r="F127">
+        <v>25</v>
+      </c>
+      <c r="G127">
+        <v>25</v>
+      </c>
+      <c r="H127" t="str">
+        <v>So</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+      <c r="J127">
+        <v>2</v>
+      </c>
+      <c r="K127">
+        <v>26</v>
+      </c>
+      <c r="L127">
+        <v>24</v>
+      </c>
+      <c r="M127" t="str">
+        <v>11011</v>
+      </c>
+      <c r="N127" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127">
+        <v>90</v>
+      </c>
+      <c r="R127" t="str">
+        <v>5</v>
+      </c>
+      <c r="S127">
+        <v>0</v>
+      </c>
+      <c r="T127" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B128" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C128" t="str">
+        <v>SELVA L 46,5</v>
+      </c>
+      <c r="D128" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E128">
+        <v>465</v>
+      </c>
+      <c r="F128">
+        <v>25</v>
+      </c>
+      <c r="G128">
+        <v>25</v>
+      </c>
+      <c r="H128" t="str">
+        <v>So</v>
+      </c>
+      <c r="I128">
+        <v>2</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128">
+        <v>26</v>
+      </c>
+      <c r="L128">
+        <v>25</v>
+      </c>
+      <c r="M128" t="str">
+        <v>10809</v>
+      </c>
+      <c r="N128" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128">
+        <v>270</v>
+      </c>
+      <c r="R128" t="str">
+        <v>4</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="T128" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B129" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C129" t="str">
+        <v>SELVA L 15,5</v>
+      </c>
+      <c r="D129" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E129">
+        <v>155</v>
+      </c>
+      <c r="F129">
+        <v>25</v>
+      </c>
+      <c r="G129">
+        <v>25</v>
+      </c>
+      <c r="H129" t="str">
+        <v>So</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="J129">
+        <v>2</v>
+      </c>
+      <c r="K129">
+        <v>26</v>
+      </c>
+      <c r="L129">
+        <v>26</v>
+      </c>
+      <c r="M129" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N129" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129">
+        <v>630</v>
+      </c>
+      <c r="R129" t="str">
+        <v>2</v>
+      </c>
+      <c r="S129">
+        <v>0</v>
+      </c>
+      <c r="T129" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B130" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C130" t="str">
+        <v>SELVA L 25,5</v>
+      </c>
+      <c r="D130" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E130">
+        <v>255</v>
+      </c>
+      <c r="F130">
+        <v>25</v>
+      </c>
+      <c r="G130">
+        <v>25</v>
+      </c>
+      <c r="H130" t="str">
+        <v>So</v>
+      </c>
+      <c r="I130">
+        <v>2</v>
+      </c>
+      <c r="J130">
+        <v>2</v>
+      </c>
+      <c r="K130">
+        <v>26</v>
+      </c>
+      <c r="L130">
+        <v>27</v>
+      </c>
+      <c r="M130" t="str">
+        <v>10607</v>
+      </c>
+      <c r="N130" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130">
+        <v>180</v>
+      </c>
+      <c r="R130" t="str">
+        <v>3</v>
+      </c>
+      <c r="S130">
+        <v>0</v>
+      </c>
+      <c r="T130" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B131" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C131" t="str">
+        <v>SELVA L 137 SZ</v>
+      </c>
+      <c r="D131" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E131">
+        <v>1370</v>
+      </c>
+      <c r="F131">
+        <v>25</v>
+      </c>
+      <c r="G131">
+        <v>50</v>
+      </c>
+      <c r="H131" t="str">
+        <v>So</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>26</v>
+      </c>
+      <c r="L131">
+        <v>28</v>
+      </c>
+      <c r="M131" t="str">
+        <v>809</v>
+      </c>
+      <c r="N131" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131">
+        <v>90</v>
+      </c>
+      <c r="R131" t="str">
+        <v>4</v>
+      </c>
+      <c r="S131">
+        <v>0</v>
+      </c>
+      <c r="T131" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B132" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C132" t="str">
+        <v>SELVA L 112 SZ</v>
+      </c>
+      <c r="D132" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E132">
+        <v>1120</v>
+      </c>
+      <c r="F132">
+        <v>25</v>
+      </c>
+      <c r="G132">
+        <v>50</v>
+      </c>
+      <c r="H132" t="str">
+        <v>So</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>26</v>
+      </c>
+      <c r="L132">
+        <v>29</v>
+      </c>
+      <c r="M132" t="str">
+        <v>607</v>
+      </c>
+      <c r="N132" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132">
+        <v>90</v>
+      </c>
+      <c r="R132" t="str">
+        <v>3</v>
+      </c>
+      <c r="S132">
+        <v>0</v>
+      </c>
+      <c r="T132" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B133" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C133" t="str">
+        <v>SELVA L 86,5 SZ</v>
+      </c>
+      <c r="D133" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E133">
+        <v>865</v>
+      </c>
+      <c r="F133">
+        <v>25</v>
+      </c>
+      <c r="G133">
+        <v>50</v>
+      </c>
+      <c r="H133" t="str">
+        <v>So</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>26</v>
+      </c>
+      <c r="L133">
+        <v>30</v>
+      </c>
+      <c r="M133" t="str">
+        <v>405</v>
+      </c>
+      <c r="N133" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133">
+        <v>90</v>
+      </c>
+      <c r="R133" t="str">
+        <v>2</v>
+      </c>
+      <c r="S133">
+        <v>0</v>
+      </c>
+      <c r="T133" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B134" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C134" t="str">
+        <v>SELVA L 22</v>
+      </c>
+      <c r="D134" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E134">
+        <v>220</v>
+      </c>
+      <c r="F134">
+        <v>25</v>
+      </c>
+      <c r="G134">
+        <v>50</v>
+      </c>
+      <c r="H134" t="str">
+        <v>So</v>
+      </c>
+      <c r="I134">
+        <v>2</v>
+      </c>
+      <c r="J134">
+        <v>2</v>
+      </c>
+      <c r="K134">
+        <v>26</v>
+      </c>
+      <c r="L134">
+        <v>31</v>
+      </c>
+      <c r="M134" t="str">
+        <v>11011</v>
+      </c>
+      <c r="N134" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134">
+        <v>540</v>
+      </c>
+      <c r="R134" t="str">
+        <v>5</v>
+      </c>
+      <c r="S134">
+        <v>0</v>
+      </c>
+      <c r="T134" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B135" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C135" t="str">
+        <v>SELVA L 7,5</v>
+      </c>
+      <c r="D135" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E135">
+        <v>75</v>
+      </c>
+      <c r="F135">
+        <v>25</v>
+      </c>
+      <c r="G135">
+        <v>50</v>
+      </c>
+      <c r="H135" t="str">
+        <v>So</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <v>2</v>
+      </c>
+      <c r="K135">
+        <v>26</v>
+      </c>
+      <c r="L135">
+        <v>32</v>
+      </c>
+      <c r="M135" t="str">
+        <v>10809</v>
+      </c>
+      <c r="N135" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135">
+        <v>90</v>
+      </c>
+      <c r="R135" t="str">
+        <v>4</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B136" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C136" t="str">
+        <v>SELVA L 5,5</v>
+      </c>
+      <c r="D136" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E136">
+        <v>55</v>
+      </c>
+      <c r="F136">
+        <v>25</v>
+      </c>
+      <c r="G136">
+        <v>50</v>
+      </c>
+      <c r="H136" t="str">
+        <v>So</v>
+      </c>
+      <c r="I136">
+        <v>2</v>
+      </c>
+      <c r="J136">
+        <v>2</v>
+      </c>
+      <c r="K136">
+        <v>26</v>
+      </c>
+      <c r="L136">
+        <v>33</v>
+      </c>
+      <c r="M136" t="str">
+        <v>10607</v>
+      </c>
+      <c r="N136" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136">
+        <v>180</v>
+      </c>
+      <c r="R136" t="str">
+        <v>3</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+      <c r="T136" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>selval90</v>
+      </c>
+      <c r="B137" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C137" t="str">
+        <v>SELVA L 4</v>
+      </c>
+      <c r="D137" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E137">
+        <v>40</v>
+      </c>
+      <c r="F137">
+        <v>25</v>
+      </c>
+      <c r="G137">
+        <v>50</v>
+      </c>
+      <c r="H137" t="str">
+        <v>So</v>
+      </c>
+      <c r="I137">
+        <v>2</v>
+      </c>
+      <c r="J137">
+        <v>2</v>
+      </c>
+      <c r="K137">
+        <v>26</v>
+      </c>
+      <c r="L137">
+        <v>34</v>
+      </c>
+      <c r="M137" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N137" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137">
+        <v>180</v>
+      </c>
+      <c r="R137" t="str">
+        <v>2</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B138" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C138" t="str">
+        <v>SELVA L 215,5 FR</v>
+      </c>
+      <c r="D138" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E138">
+        <v>2155</v>
+      </c>
+      <c r="F138">
+        <v>30</v>
+      </c>
+      <c r="G138">
+        <v>60</v>
+      </c>
+      <c r="H138" t="str">
+        <v>So</v>
+      </c>
+      <c r="I138">
+        <v>2</v>
+      </c>
+      <c r="J138">
+        <v>2</v>
+      </c>
+      <c r="K138">
+        <v>26</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="str">
+        <v>203</v>
+      </c>
+      <c r="N138" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138">
+        <v>180</v>
+      </c>
+      <c r="R138" t="str">
+        <v>1</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B139" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C139" t="str">
+        <v>SELVA L 215,5 FR+KL</v>
+      </c>
+      <c r="D139" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E139">
+        <v>2155</v>
+      </c>
+      <c r="F139">
+        <v>30</v>
+      </c>
+      <c r="G139">
+        <v>60</v>
+      </c>
+      <c r="H139" t="str">
+        <v>So</v>
+      </c>
+      <c r="I139">
+        <v>2</v>
+      </c>
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="K139">
+        <v>26</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139" t="str">
+        <v>405</v>
+      </c>
+      <c r="N139" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139">
+        <v>180</v>
+      </c>
+      <c r="R139" t="str">
+        <v>2</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B140" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C140" t="str">
+        <v>SELVA L 209,5 KL</v>
+      </c>
+      <c r="D140" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E140">
+        <v>2095</v>
+      </c>
+      <c r="F140">
+        <v>30</v>
+      </c>
+      <c r="G140">
+        <v>60</v>
+      </c>
+      <c r="H140" t="str">
+        <v>So</v>
+      </c>
+      <c r="I140">
+        <v>2</v>
+      </c>
+      <c r="J140">
+        <v>2</v>
+      </c>
+      <c r="K140">
+        <v>26</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140" t="str">
+        <v>1011</v>
+      </c>
+      <c r="N140" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140">
+        <v>180</v>
+      </c>
+      <c r="R140" t="str">
+        <v>5</v>
+      </c>
+      <c r="S140">
+        <v>0</v>
+      </c>
+      <c r="T140" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B141" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C141" t="str">
+        <v>SELVA L 134</v>
+      </c>
+      <c r="D141" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E141">
+        <v>1340</v>
+      </c>
+      <c r="F141">
+        <v>30</v>
+      </c>
+      <c r="G141">
+        <v>60</v>
+      </c>
+      <c r="H141" t="str">
+        <v>So</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="K141">
+        <v>26</v>
+      </c>
+      <c r="L141">
+        <v>3</v>
+      </c>
+      <c r="M141" t="str">
+        <v>607</v>
+      </c>
+      <c r="N141" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141">
+        <v>180</v>
+      </c>
+      <c r="R141" t="str">
+        <v>3</v>
+      </c>
+      <c r="S141">
+        <v>0</v>
+      </c>
+      <c r="T141" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B142" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C142" t="str">
+        <v>SELVA L 134 FR+KL</v>
+      </c>
+      <c r="D142" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E142">
+        <v>1340</v>
+      </c>
+      <c r="F142">
+        <v>30</v>
+      </c>
+      <c r="G142">
+        <v>60</v>
+      </c>
+      <c r="H142" t="str">
+        <v>So</v>
+      </c>
+      <c r="I142">
+        <v>2</v>
+      </c>
+      <c r="J142">
+        <v>2</v>
+      </c>
+      <c r="K142">
+        <v>26</v>
+      </c>
+      <c r="L142">
+        <v>4</v>
+      </c>
+      <c r="M142" t="str">
+        <v>809</v>
+      </c>
+      <c r="N142" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142">
+        <v>360</v>
+      </c>
+      <c r="R142" t="str">
+        <v>4</v>
+      </c>
+      <c r="S142">
+        <v>0</v>
+      </c>
+      <c r="T142" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B143" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C143" t="str">
+        <v>SELVA L 88 FR</v>
+      </c>
+      <c r="D143" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E143">
+        <v>880</v>
+      </c>
+      <c r="F143">
+        <v>30</v>
+      </c>
+      <c r="G143">
+        <v>60</v>
+      </c>
+      <c r="H143" t="str">
+        <v>So</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143">
+        <v>2</v>
+      </c>
+      <c r="K143">
+        <v>26</v>
+      </c>
+      <c r="L143">
+        <v>5</v>
+      </c>
+      <c r="M143" t="str">
+        <v>405</v>
+      </c>
+      <c r="N143" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143">
+        <v>360</v>
+      </c>
+      <c r="R143" t="str">
+        <v>2</v>
+      </c>
+      <c r="S143">
+        <v>0</v>
+      </c>
+      <c r="T143" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B144" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C144" t="str">
+        <v>SELVA L 63 FR</v>
+      </c>
+      <c r="D144" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E144">
+        <v>630</v>
+      </c>
+      <c r="F144">
+        <v>30</v>
+      </c>
+      <c r="G144">
+        <v>60</v>
+      </c>
+      <c r="H144" t="str">
+        <v>So</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
+      </c>
+      <c r="J144">
+        <v>2</v>
+      </c>
+      <c r="K144">
+        <v>26</v>
+      </c>
+      <c r="L144">
+        <v>6</v>
+      </c>
+      <c r="M144" t="str">
+        <v>11011</v>
+      </c>
+      <c r="N144" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144">
+        <v>360</v>
+      </c>
+      <c r="R144" t="str">
+        <v>5</v>
+      </c>
+      <c r="S144">
+        <v>0</v>
+      </c>
+      <c r="T144" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B145" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C145" t="str">
+        <v>SELVA L 57</v>
+      </c>
+      <c r="D145" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E145">
+        <v>570</v>
+      </c>
+      <c r="F145">
+        <v>30</v>
+      </c>
+      <c r="G145">
+        <v>60</v>
+      </c>
+      <c r="H145" t="str">
+        <v>So</v>
+      </c>
+      <c r="I145">
+        <v>2</v>
+      </c>
+      <c r="J145">
+        <v>2</v>
+      </c>
+      <c r="K145">
+        <v>26</v>
+      </c>
+      <c r="L145">
+        <v>7</v>
+      </c>
+      <c r="M145" t="str">
+        <v>809</v>
+      </c>
+      <c r="N145" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145">
+        <v>900</v>
+      </c>
+      <c r="R145" t="str">
+        <v>4</v>
+      </c>
+      <c r="S145">
+        <v>0</v>
+      </c>
+      <c r="T145" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B146" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C146" t="str">
+        <v>SELVA L 22</v>
+      </c>
+      <c r="D146" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E146">
+        <v>220</v>
+      </c>
+      <c r="F146">
+        <v>30</v>
+      </c>
+      <c r="G146">
+        <v>60</v>
+      </c>
+      <c r="H146" t="str">
+        <v>So</v>
+      </c>
+      <c r="I146">
+        <v>2</v>
+      </c>
+      <c r="J146">
+        <v>2</v>
+      </c>
+      <c r="K146">
+        <v>26</v>
+      </c>
+      <c r="L146">
+        <v>8</v>
+      </c>
+      <c r="M146" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N146" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146">
+        <v>1080</v>
+      </c>
+      <c r="R146" t="str">
+        <v>2</v>
+      </c>
+      <c r="S146">
+        <v>0</v>
+      </c>
+      <c r="T146" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B147" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C147" t="str">
+        <v>SELVA L 86,5 SZ</v>
+      </c>
+      <c r="D147" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E147">
+        <v>865</v>
+      </c>
+      <c r="F147">
+        <v>30</v>
+      </c>
+      <c r="G147">
+        <v>60</v>
+      </c>
+      <c r="H147" t="str">
+        <v>So</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>1</v>
+      </c>
+      <c r="K147">
+        <v>26</v>
+      </c>
+      <c r="L147">
+        <v>9</v>
+      </c>
+      <c r="M147" t="str">
+        <v>203</v>
+      </c>
+      <c r="N147" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147">
+        <v>360</v>
+      </c>
+      <c r="R147" t="str">
+        <v>1</v>
+      </c>
+      <c r="S147">
+        <v>0</v>
+      </c>
+      <c r="T147" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B148" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C148" t="str">
+        <v>SELVA L 11 SZ</v>
+      </c>
+      <c r="D148" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E148">
+        <v>110</v>
+      </c>
+      <c r="F148">
+        <v>30</v>
+      </c>
+      <c r="G148">
+        <v>60</v>
+      </c>
+      <c r="H148" t="str">
+        <v>So</v>
+      </c>
+      <c r="I148">
+        <v>1</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148">
+        <v>26</v>
+      </c>
+      <c r="L148">
+        <v>10</v>
+      </c>
+      <c r="M148" t="str">
+        <v>10203</v>
+      </c>
+      <c r="N148" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148">
+        <v>1080</v>
+      </c>
+      <c r="R148" t="str">
+        <v>1</v>
+      </c>
+      <c r="S148">
+        <v>0</v>
+      </c>
+      <c r="T148" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B149" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C149" t="str">
+        <v>SELVA L 23</v>
+      </c>
+      <c r="D149" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E149">
+        <v>230</v>
+      </c>
+      <c r="F149">
+        <v>30</v>
+      </c>
+      <c r="G149">
+        <v>60</v>
+      </c>
+      <c r="H149" t="str">
+        <v>So</v>
+      </c>
+      <c r="I149">
+        <v>2</v>
+      </c>
+      <c r="J149">
+        <v>2</v>
+      </c>
+      <c r="K149">
+        <v>26</v>
+      </c>
+      <c r="L149">
+        <v>11</v>
+      </c>
+      <c r="M149" t="str">
+        <v>10607</v>
+      </c>
+      <c r="N149" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149">
+        <v>540</v>
+      </c>
+      <c r="R149" t="str">
+        <v>3</v>
+      </c>
+      <c r="S149">
+        <v>0</v>
+      </c>
+      <c r="T149" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B150" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C150" t="str">
+        <v>SELVA L 17,9</v>
+      </c>
+      <c r="D150" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E150">
+        <v>179</v>
+      </c>
+      <c r="F150">
+        <v>30</v>
+      </c>
+      <c r="G150">
+        <v>80</v>
+      </c>
+      <c r="H150" t="str">
+        <v>So</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="J150">
+        <v>2</v>
+      </c>
+      <c r="K150">
+        <v>26</v>
+      </c>
+      <c r="L150">
+        <v>12</v>
+      </c>
+      <c r="M150" t="str">
+        <v>10203</v>
+      </c>
+      <c r="N150" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150">
+        <v>1800</v>
+      </c>
+      <c r="R150" t="str">
+        <v>1</v>
+      </c>
+      <c r="S150">
+        <v>0</v>
+      </c>
+      <c r="T150" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B151" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C151" t="str">
+        <v>SELVA L 35 SZ</v>
+      </c>
+      <c r="D151" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E151">
+        <v>350</v>
+      </c>
+      <c r="F151">
+        <v>30</v>
+      </c>
+      <c r="G151">
+        <v>30</v>
+      </c>
+      <c r="H151" t="str">
+        <v>So</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>26</v>
+      </c>
+      <c r="L151">
+        <v>13</v>
+      </c>
+      <c r="M151" t="str">
+        <v>10203</v>
+      </c>
+      <c r="N151" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151">
+        <v>360</v>
+      </c>
+      <c r="R151" t="str">
+        <v>1</v>
+      </c>
+      <c r="S151">
+        <v>0</v>
+      </c>
+      <c r="T151" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B152" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C152" t="str">
+        <v>SELVA L 80 PR</v>
+      </c>
+      <c r="D152" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E152">
+        <v>800</v>
+      </c>
+      <c r="F152">
+        <v>25</v>
+      </c>
+      <c r="G152">
+        <v>40</v>
+      </c>
+      <c r="H152" t="str">
+        <v>So</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>26</v>
+      </c>
+      <c r="L152">
+        <v>14</v>
+      </c>
+      <c r="M152" t="str">
+        <v>203</v>
+      </c>
+      <c r="N152" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152">
+        <v>360</v>
+      </c>
+      <c r="R152" t="str">
+        <v>1</v>
+      </c>
+      <c r="S152">
+        <v>0</v>
+      </c>
+      <c r="T152" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B153" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C153" t="str">
+        <v>SELVA L 156,5</v>
+      </c>
+      <c r="D153" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E153">
+        <v>1565</v>
+      </c>
+      <c r="F153">
+        <v>25</v>
+      </c>
+      <c r="G153">
+        <v>25</v>
+      </c>
+      <c r="H153" t="str">
+        <v>So</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
+      </c>
+      <c r="J153">
+        <v>2</v>
+      </c>
+      <c r="K153">
+        <v>26</v>
+      </c>
+      <c r="L153">
+        <v>15</v>
+      </c>
+      <c r="M153" t="str">
+        <v>607</v>
+      </c>
+      <c r="N153" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153">
+        <v>180</v>
+      </c>
+      <c r="R153" t="str">
+        <v>3</v>
+      </c>
+      <c r="S153">
+        <v>0</v>
+      </c>
+      <c r="T153" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B154" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C154" t="str">
+        <v>SELVA L 136</v>
+      </c>
+      <c r="D154" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E154">
+        <v>1360</v>
+      </c>
+      <c r="F154">
+        <v>25</v>
+      </c>
+      <c r="G154">
+        <v>25</v>
+      </c>
+      <c r="H154" t="str">
+        <v>So</v>
+      </c>
+      <c r="I154">
+        <v>2</v>
+      </c>
+      <c r="J154">
+        <v>2</v>
+      </c>
+      <c r="K154">
+        <v>26</v>
+      </c>
+      <c r="L154">
+        <v>16</v>
+      </c>
+      <c r="M154" t="str">
+        <v>405</v>
+      </c>
+      <c r="N154" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154">
+        <v>180</v>
+      </c>
+      <c r="R154" t="str">
+        <v>2</v>
+      </c>
+      <c r="S154">
+        <v>0</v>
+      </c>
+      <c r="T154" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B155" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C155" t="str">
+        <v>SELVA L 132</v>
+      </c>
+      <c r="D155" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E155">
+        <v>1320</v>
+      </c>
+      <c r="F155">
+        <v>25</v>
+      </c>
+      <c r="G155">
+        <v>25</v>
+      </c>
+      <c r="H155" t="str">
+        <v>So</v>
+      </c>
+      <c r="I155">
+        <v>2</v>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="K155">
+        <v>26</v>
+      </c>
+      <c r="L155">
+        <v>17</v>
+      </c>
+      <c r="M155" t="str">
+        <v>1011</v>
+      </c>
+      <c r="N155" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155">
+        <v>180</v>
+      </c>
+      <c r="R155" t="str">
+        <v>5</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="T155" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B156" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C156" t="str">
+        <v>SELVA L 134</v>
+      </c>
+      <c r="D156" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E156">
+        <v>1340</v>
+      </c>
+      <c r="F156">
+        <v>25</v>
+      </c>
+      <c r="G156">
+        <v>25</v>
+      </c>
+      <c r="H156" t="str">
+        <v>So</v>
+      </c>
+      <c r="I156">
+        <v>2</v>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+      <c r="K156">
+        <v>26</v>
+      </c>
+      <c r="L156">
+        <v>18</v>
+      </c>
+      <c r="M156" t="str">
+        <v>203</v>
+      </c>
+      <c r="N156" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156">
+        <v>540</v>
+      </c>
+      <c r="R156" t="str">
+        <v>1</v>
+      </c>
+      <c r="S156">
+        <v>0</v>
+      </c>
+      <c r="T156" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B157" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C157" t="str">
+        <v>SELVA L 125</v>
+      </c>
+      <c r="D157" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E157">
+        <v>1250</v>
+      </c>
+      <c r="F157">
+        <v>25</v>
+      </c>
+      <c r="G157">
+        <v>25</v>
+      </c>
+      <c r="H157" t="str">
+        <v>So</v>
+      </c>
+      <c r="I157">
+        <v>2</v>
+      </c>
+      <c r="J157">
+        <v>2</v>
+      </c>
+      <c r="K157">
+        <v>26</v>
+      </c>
+      <c r="L157">
+        <v>19</v>
+      </c>
+      <c r="M157" t="str">
+        <v>809</v>
+      </c>
+      <c r="N157" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157">
+        <v>180</v>
+      </c>
+      <c r="R157" t="str">
+        <v>4</v>
+      </c>
+      <c r="S157">
+        <v>0</v>
+      </c>
+      <c r="T157" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B158" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C158" t="str">
+        <v>SELVA L 112 SZ</v>
+      </c>
+      <c r="D158" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E158">
+        <v>1120</v>
+      </c>
+      <c r="F158">
+        <v>25</v>
+      </c>
+      <c r="G158">
+        <v>25</v>
+      </c>
+      <c r="H158" t="str">
+        <v>So</v>
+      </c>
+      <c r="I158">
+        <v>1</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>26</v>
+      </c>
+      <c r="L158">
+        <v>20</v>
+      </c>
+      <c r="M158" t="str">
+        <v>607</v>
+      </c>
+      <c r="N158" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158">
+        <v>180</v>
+      </c>
+      <c r="R158" t="str">
+        <v>3</v>
+      </c>
+      <c r="S158">
+        <v>0</v>
+      </c>
+      <c r="T158" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B159" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C159" t="str">
+        <v>SELVA L 85,5</v>
+      </c>
+      <c r="D159" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E159">
+        <v>855</v>
+      </c>
+      <c r="F159">
+        <v>25</v>
+      </c>
+      <c r="G159">
+        <v>25</v>
+      </c>
+      <c r="H159" t="str">
+        <v>So</v>
+      </c>
+      <c r="I159">
+        <v>2</v>
+      </c>
+      <c r="J159">
+        <v>2</v>
+      </c>
+      <c r="K159">
+        <v>26</v>
+      </c>
+      <c r="L159">
+        <v>21</v>
+      </c>
+      <c r="M159" t="str">
+        <v>405</v>
+      </c>
+      <c r="N159" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159">
+        <v>180</v>
+      </c>
+      <c r="R159" t="str">
+        <v>2</v>
+      </c>
+      <c r="S159">
+        <v>0</v>
+      </c>
+      <c r="T159" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B160" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C160" t="str">
+        <v>SELVA L 65</v>
+      </c>
+      <c r="D160" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E160">
+        <v>650</v>
+      </c>
+      <c r="F160">
+        <v>25</v>
+      </c>
+      <c r="G160">
+        <v>25</v>
+      </c>
+      <c r="H160" t="str">
+        <v>So</v>
+      </c>
+      <c r="I160">
+        <v>2</v>
+      </c>
+      <c r="J160">
+        <v>2</v>
+      </c>
+      <c r="K160">
+        <v>26</v>
+      </c>
+      <c r="L160">
+        <v>22</v>
+      </c>
+      <c r="M160" t="str">
+        <v>203</v>
+      </c>
+      <c r="N160" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160">
+        <v>180</v>
+      </c>
+      <c r="R160" t="str">
+        <v>1</v>
+      </c>
+      <c r="S160">
+        <v>0</v>
+      </c>
+      <c r="T160" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B161" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C161" t="str">
+        <v>SELVA L 61</v>
+      </c>
+      <c r="D161" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E161">
+        <v>610</v>
+      </c>
+      <c r="F161">
+        <v>25</v>
+      </c>
+      <c r="G161">
+        <v>25</v>
+      </c>
+      <c r="H161" t="str">
+        <v>So</v>
+      </c>
+      <c r="I161">
+        <v>2</v>
+      </c>
+      <c r="J161">
+        <v>2</v>
+      </c>
+      <c r="K161">
+        <v>26</v>
+      </c>
+      <c r="L161">
+        <v>23</v>
+      </c>
+      <c r="M161" t="str">
+        <v>11011</v>
+      </c>
+      <c r="N161" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161">
+        <v>180</v>
+      </c>
+      <c r="R161" t="str">
+        <v>5</v>
+      </c>
+      <c r="S161">
+        <v>0</v>
+      </c>
+      <c r="T161" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B162" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C162" t="str">
+        <v>SELVA L 49</v>
+      </c>
+      <c r="D162" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E162">
+        <v>490</v>
+      </c>
+      <c r="F162">
+        <v>25</v>
+      </c>
+      <c r="G162">
+        <v>25</v>
+      </c>
+      <c r="H162" t="str">
+        <v>So</v>
+      </c>
+      <c r="I162">
+        <v>2</v>
+      </c>
+      <c r="J162">
+        <v>2</v>
+      </c>
+      <c r="K162">
+        <v>26</v>
+      </c>
+      <c r="L162">
+        <v>24</v>
+      </c>
+      <c r="M162" t="str">
+        <v>10809</v>
+      </c>
+      <c r="N162" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162">
+        <v>180</v>
+      </c>
+      <c r="R162" t="str">
+        <v>4</v>
+      </c>
+      <c r="S162">
+        <v>0</v>
+      </c>
+      <c r="T162" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B163" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C163" t="str">
+        <v>SELVA L 46,5</v>
+      </c>
+      <c r="D163" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E163">
+        <v>465</v>
+      </c>
+      <c r="F163">
+        <v>25</v>
+      </c>
+      <c r="G163">
+        <v>25</v>
+      </c>
+      <c r="H163" t="str">
+        <v>So</v>
+      </c>
+      <c r="I163">
+        <v>2</v>
+      </c>
+      <c r="J163">
+        <v>2</v>
+      </c>
+      <c r="K163">
+        <v>26</v>
+      </c>
+      <c r="L163">
+        <v>25</v>
+      </c>
+      <c r="M163" t="str">
+        <v>10607</v>
+      </c>
+      <c r="N163" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163">
+        <v>540</v>
+      </c>
+      <c r="R163" t="str">
+        <v>3</v>
+      </c>
+      <c r="S163">
+        <v>0</v>
+      </c>
+      <c r="T163" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B164" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C164" t="str">
+        <v>SELVA L 15,5</v>
+      </c>
+      <c r="D164" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E164">
+        <v>155</v>
+      </c>
+      <c r="F164">
+        <v>25</v>
+      </c>
+      <c r="G164">
+        <v>25</v>
+      </c>
+      <c r="H164" t="str">
+        <v>So</v>
+      </c>
+      <c r="I164">
+        <v>2</v>
+      </c>
+      <c r="J164">
+        <v>2</v>
+      </c>
+      <c r="K164">
+        <v>26</v>
+      </c>
+      <c r="L164">
+        <v>26</v>
+      </c>
+      <c r="M164" t="str">
+        <v>10203</v>
+      </c>
+      <c r="N164" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164">
+        <v>1260</v>
+      </c>
+      <c r="R164" t="str">
+        <v>1</v>
+      </c>
+      <c r="S164">
+        <v>0</v>
+      </c>
+      <c r="T164" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B165" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C165" t="str">
+        <v>SELVA L 25,5</v>
+      </c>
+      <c r="D165" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E165">
+        <v>255</v>
+      </c>
+      <c r="F165">
+        <v>25</v>
+      </c>
+      <c r="G165">
+        <v>25</v>
+      </c>
+      <c r="H165" t="str">
+        <v>So</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
+      </c>
+      <c r="J165">
+        <v>2</v>
+      </c>
+      <c r="K165">
+        <v>26</v>
+      </c>
+      <c r="L165">
+        <v>27</v>
+      </c>
+      <c r="M165" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N165" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165">
+        <v>360</v>
+      </c>
+      <c r="R165" t="str">
+        <v>2</v>
+      </c>
+      <c r="S165">
+        <v>0</v>
+      </c>
+      <c r="T165" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B166" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C166" t="str">
+        <v>SELVA L 137 SZ</v>
+      </c>
+      <c r="D166" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E166">
+        <v>1370</v>
+      </c>
+      <c r="F166">
+        <v>25</v>
+      </c>
+      <c r="G166">
+        <v>50</v>
+      </c>
+      <c r="H166" t="str">
+        <v>So</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="J166">
+        <v>1</v>
+      </c>
+      <c r="K166">
+        <v>26</v>
+      </c>
+      <c r="L166">
+        <v>28</v>
+      </c>
+      <c r="M166" t="str">
+        <v>405</v>
+      </c>
+      <c r="N166" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166">
+        <v>180</v>
+      </c>
+      <c r="R166" t="str">
+        <v>2</v>
+      </c>
+      <c r="S166">
+        <v>0</v>
+      </c>
+      <c r="T166" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B167" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C167" t="str">
+        <v>SELVA L 112 SZ</v>
+      </c>
+      <c r="D167" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E167">
+        <v>1120</v>
+      </c>
+      <c r="F167">
+        <v>25</v>
+      </c>
+      <c r="G167">
+        <v>50</v>
+      </c>
+      <c r="H167" t="str">
+        <v>So</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>26</v>
+      </c>
+      <c r="L167">
+        <v>29</v>
+      </c>
+      <c r="M167" t="str">
+        <v>203</v>
+      </c>
+      <c r="N167" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167">
+        <v>180</v>
+      </c>
+      <c r="R167" t="str">
+        <v>1</v>
+      </c>
+      <c r="S167">
+        <v>0</v>
+      </c>
+      <c r="T167" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B168" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C168" t="str">
+        <v>SELVA L 86,5 SZ</v>
+      </c>
+      <c r="D168" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E168">
+        <v>865</v>
+      </c>
+      <c r="F168">
+        <v>25</v>
+      </c>
+      <c r="G168">
+        <v>50</v>
+      </c>
+      <c r="H168" t="str">
+        <v>So</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168">
+        <v>26</v>
+      </c>
+      <c r="L168">
+        <v>30</v>
+      </c>
+      <c r="M168" t="str">
+        <v>1011</v>
+      </c>
+      <c r="N168" t="str">
+        <v>synchronicznie</v>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168">
+        <v>180</v>
+      </c>
+      <c r="R168" t="str">
+        <v>5</v>
+      </c>
+      <c r="S168">
+        <v>0</v>
+      </c>
+      <c r="T168" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B169" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C169" t="str">
+        <v>SELVA L 22</v>
+      </c>
+      <c r="D169" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E169">
+        <v>220</v>
+      </c>
+      <c r="F169">
+        <v>25</v>
+      </c>
+      <c r="G169">
+        <v>50</v>
+      </c>
+      <c r="H169" t="str">
+        <v>So</v>
+      </c>
+      <c r="I169">
+        <v>2</v>
+      </c>
+      <c r="J169">
+        <v>2</v>
+      </c>
+      <c r="K169">
+        <v>26</v>
+      </c>
+      <c r="L169">
+        <v>31</v>
+      </c>
+      <c r="M169" t="str">
+        <v>10809</v>
+      </c>
+      <c r="N169" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169">
+        <v>1080</v>
+      </c>
+      <c r="R169" t="str">
+        <v>4</v>
+      </c>
+      <c r="S169">
+        <v>0</v>
+      </c>
+      <c r="T169" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B170" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C170" t="str">
+        <v>SELVA L 7,5</v>
+      </c>
+      <c r="D170" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E170">
+        <v>75</v>
+      </c>
+      <c r="F170">
+        <v>25</v>
+      </c>
+      <c r="G170">
+        <v>50</v>
+      </c>
+      <c r="H170" t="str">
+        <v>So</v>
+      </c>
+      <c r="I170">
+        <v>2</v>
+      </c>
+      <c r="J170">
+        <v>2</v>
+      </c>
+      <c r="K170">
+        <v>26</v>
+      </c>
+      <c r="L170">
+        <v>32</v>
+      </c>
+      <c r="M170" t="str">
+        <v>10607</v>
+      </c>
+      <c r="N170" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170">
+        <v>180</v>
+      </c>
+      <c r="R170" t="str">
+        <v>3</v>
+      </c>
+      <c r="S170">
+        <v>0</v>
+      </c>
+      <c r="T170" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B171" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C171" t="str">
+        <v>SELVA L 5,5</v>
+      </c>
+      <c r="D171" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E171">
+        <v>55</v>
+      </c>
+      <c r="F171">
+        <v>25</v>
+      </c>
+      <c r="G171">
+        <v>50</v>
+      </c>
+      <c r="H171" t="str">
+        <v>So</v>
+      </c>
+      <c r="I171">
+        <v>2</v>
+      </c>
+      <c r="J171">
+        <v>2</v>
+      </c>
+      <c r="K171">
+        <v>26</v>
+      </c>
+      <c r="L171">
+        <v>33</v>
+      </c>
+      <c r="M171" t="str">
+        <v>10405</v>
+      </c>
+      <c r="N171" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171">
+        <v>360</v>
+      </c>
+      <c r="R171" t="str">
+        <v>2</v>
+      </c>
+      <c r="S171">
+        <v>0</v>
+      </c>
+      <c r="T171" t="str">
+        <v>Kopia tymczasowa</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>SELVA L 180</v>
+      </c>
+      <c r="B172" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="C172" t="str">
+        <v>SELVA L 4</v>
+      </c>
+      <c r="D172" t="str">
+        <v>SELVA L</v>
+      </c>
+      <c r="E172">
+        <v>40</v>
+      </c>
+      <c r="F172">
+        <v>25</v>
+      </c>
+      <c r="G172">
+        <v>50</v>
+      </c>
+      <c r="H172" t="str">
+        <v>So</v>
+      </c>
+      <c r="I172">
+        <v>2</v>
+      </c>
+      <c r="J172">
+        <v>2</v>
+      </c>
+      <c r="K172">
+        <v>26</v>
+      </c>
+      <c r="L172">
+        <v>34</v>
+      </c>
+      <c r="M172" t="str">
+        <v>10203</v>
+      </c>
+      <c r="N172" t="str">
+        <v>naprzemiennie</v>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172">
+        <v>360</v>
+      </c>
+      <c r="R172" t="str">
+        <v>1</v>
+      </c>
+      <c r="S172">
+        <v>0</v>
+      </c>
+      <c r="T172" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T172"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/receptury.xlsx
+++ b/receptury.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -462,74 +462,34 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1781514156350</v>
+        <v>1782810915055</v>
       </c>
       <c r="B4" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-06-15 11:02:36</v>
+        <v>2026-06-30 11:15:15</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-15 11:02:36</v>
+        <v>2026-06-30 11:15:15</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-06-24 13:29:30</v>
+        <v>2026-06-30 11:15:58</v>
       </c>
       <c r="F4" t="str">
         <v>Default</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5">
-        <v>1781862748755</v>
-      </c>
-      <c r="B5" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2026-06-19 11:52:28</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-06-19 11:52:28</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-06-22 14:48:49</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Default</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>1782300859277</v>
-      </c>
-      <c r="B6" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2026-06-24 13:34:19</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-06-24 13:34:19</v>
-      </c>
-      <c r="E6" t="str">
-        <v>2026-06-24 13:35:11</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Default</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T172"/>
+  <dimension ref="A1:T102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4687,7 +4647,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B68" t="str">
         <v>SELVA L</v>
@@ -4723,10 +4683,10 @@
         <v>0</v>
       </c>
       <c r="M68" t="str">
-        <v>203</v>
+        <v>607</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -4735,10 +4695,10 @@
         <v/>
       </c>
       <c r="Q68">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R68" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -4749,7 +4709,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B69" t="str">
         <v>SELVA L</v>
@@ -4785,10 +4745,10 @@
         <v>1</v>
       </c>
       <c r="M69" t="str">
-        <v>405</v>
+        <v>809</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -4797,10 +4757,10 @@
         <v/>
       </c>
       <c r="Q69">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R69" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -4811,7 +4771,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B70" t="str">
         <v>SELVA L</v>
@@ -4847,10 +4807,10 @@
         <v>2</v>
       </c>
       <c r="M70" t="str">
-        <v>11110</v>
+        <v>405</v>
       </c>
       <c r="N70" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -4859,10 +4819,10 @@
         <v/>
       </c>
       <c r="Q70">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R70" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -4873,7 +4833,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B71" t="str">
         <v>SELVA L</v>
@@ -4912,7 +4872,7 @@
         <v>607</v>
       </c>
       <c r="N71" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O71" t="str">
         <v/>
@@ -4921,7 +4881,7 @@
         <v/>
       </c>
       <c r="Q71">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R71" t="str">
         <v>3</v>
@@ -4935,7 +4895,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B72" t="str">
         <v>SELVA L</v>
@@ -4974,7 +4934,7 @@
         <v>809</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -4983,7 +4943,7 @@
         <v/>
       </c>
       <c r="Q72">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R72" t="str">
         <v>4</v>
@@ -4997,7 +4957,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B73" t="str">
         <v>SELVA L</v>
@@ -5036,7 +4996,7 @@
         <v>405</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -5045,7 +5005,7 @@
         <v/>
       </c>
       <c r="Q73">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R73" t="str">
         <v>2</v>
@@ -5059,7 +5019,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B74" t="str">
         <v>SELVA L</v>
@@ -5095,10 +5055,10 @@
         <v>6</v>
       </c>
       <c r="M74" t="str">
-        <v>10</v>
+        <v>607</v>
       </c>
       <c r="N74" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O74" t="str">
         <v/>
@@ -5107,10 +5067,10 @@
         <v/>
       </c>
       <c r="Q74">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R74" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -5121,7 +5081,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B75" t="str">
         <v>SELVA L</v>
@@ -5157,10 +5117,10 @@
         <v>7</v>
       </c>
       <c r="M75" t="str">
-        <v>809</v>
+        <v>405</v>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -5169,10 +5129,10 @@
         <v/>
       </c>
       <c r="Q75">
-        <v>1050</v>
+        <v>600</v>
       </c>
       <c r="R75" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -5183,7 +5143,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B76" t="str">
         <v>SELVA L</v>
@@ -5219,10 +5179,10 @@
         <v>8</v>
       </c>
       <c r="M76" t="str">
-        <v>4</v>
+        <v>10607</v>
       </c>
       <c r="N76" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -5231,10 +5191,10 @@
         <v/>
       </c>
       <c r="Q76">
-        <v>1260</v>
+        <v>720</v>
       </c>
       <c r="R76" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -5245,7 +5205,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B77" t="str">
         <v>SELVA L</v>
@@ -5281,10 +5241,10 @@
         <v>9</v>
       </c>
       <c r="M77" t="str">
-        <v>203</v>
+        <v>809</v>
       </c>
       <c r="N77" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -5293,10 +5253,10 @@
         <v/>
       </c>
       <c r="Q77">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R77" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -5307,7 +5267,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B78" t="str">
         <v>SELVA L</v>
@@ -5343,10 +5303,10 @@
         <v>10</v>
       </c>
       <c r="M78" t="str">
-        <v>2</v>
+        <v>10405</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O78" t="str">
         <v/>
@@ -5355,10 +5315,10 @@
         <v/>
       </c>
       <c r="Q78">
-        <v>1260</v>
+        <v>720</v>
       </c>
       <c r="R78" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -5369,7 +5329,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B79" t="str">
         <v>SELVA L</v>
@@ -5405,10 +5365,10 @@
         <v>11</v>
       </c>
       <c r="M79" t="str">
-        <v>6</v>
+        <v>10809</v>
       </c>
       <c r="N79" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O79" t="str">
         <v/>
@@ -5417,10 +5377,10 @@
         <v/>
       </c>
       <c r="Q79">
-        <v>630</v>
+        <v>360</v>
       </c>
       <c r="R79" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -5431,7 +5391,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B80" t="str">
         <v>SELVA L</v>
@@ -5467,10 +5427,10 @@
         <v>12</v>
       </c>
       <c r="M80" t="str">
-        <v>2</v>
+        <v>10405</v>
       </c>
       <c r="N80" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O80" t="str">
         <v/>
@@ -5479,10 +5439,10 @@
         <v/>
       </c>
       <c r="Q80">
-        <v>2100</v>
+        <v>1200</v>
       </c>
       <c r="R80" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -5493,7 +5453,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B81" t="str">
         <v>SELVA L</v>
@@ -5529,10 +5489,10 @@
         <v>13</v>
       </c>
       <c r="M81" t="str">
-        <v>2</v>
+        <v>10405</v>
       </c>
       <c r="N81" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -5541,10 +5501,10 @@
         <v/>
       </c>
       <c r="Q81">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R81" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -5555,7 +5515,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B82" t="str">
         <v>SELVA L</v>
@@ -5591,10 +5551,10 @@
         <v>14</v>
       </c>
       <c r="M82" t="str">
-        <v>203</v>
+        <v>405</v>
       </c>
       <c r="N82" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O82" t="str">
         <v/>
@@ -5603,10 +5563,10 @@
         <v/>
       </c>
       <c r="Q82">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R82" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -5617,7 +5577,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B83" t="str">
         <v>SELVA L</v>
@@ -5653,10 +5613,10 @@
         <v>15</v>
       </c>
       <c r="M83" t="str">
-        <v>607</v>
+        <v>405</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O83" t="str">
         <v/>
@@ -5665,10 +5625,10 @@
         <v/>
       </c>
       <c r="Q83">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R83" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S83">
         <v>0</v>
@@ -5679,7 +5639,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B84" t="str">
         <v>SELVA L</v>
@@ -5715,10 +5675,10 @@
         <v>16</v>
       </c>
       <c r="M84" t="str">
-        <v>405</v>
+        <v>809</v>
       </c>
       <c r="N84" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O84" t="str">
         <v/>
@@ -5727,10 +5687,10 @@
         <v/>
       </c>
       <c r="Q84">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R84" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -5741,7 +5701,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B85" t="str">
         <v>SELVA L</v>
@@ -5777,10 +5737,10 @@
         <v>17</v>
       </c>
       <c r="M85" t="str">
-        <v>11110</v>
+        <v>405</v>
       </c>
       <c r="N85" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O85" t="str">
         <v/>
@@ -5789,10 +5749,10 @@
         <v/>
       </c>
       <c r="Q85">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R85" t="str">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S85">
         <v>0</v>
@@ -5803,7 +5763,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B86" t="str">
         <v>SELVA L</v>
@@ -5839,10 +5799,10 @@
         <v>18</v>
       </c>
       <c r="M86" t="str">
-        <v>203</v>
+        <v>607</v>
       </c>
       <c r="N86" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O86" t="str">
         <v/>
@@ -5851,10 +5811,10 @@
         <v/>
       </c>
       <c r="Q86">
-        <v>630</v>
+        <v>360</v>
       </c>
       <c r="R86" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S86">
         <v>0</v>
@@ -5865,7 +5825,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B87" t="str">
         <v>SELVA L</v>
@@ -5904,7 +5864,7 @@
         <v>809</v>
       </c>
       <c r="N87" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O87" t="str">
         <v/>
@@ -5913,7 +5873,7 @@
         <v/>
       </c>
       <c r="Q87">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R87" t="str">
         <v>4</v>
@@ -5927,7 +5887,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B88" t="str">
         <v>SELVA L</v>
@@ -5966,7 +5926,7 @@
         <v>607</v>
       </c>
       <c r="N88" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O88" t="str">
         <v/>
@@ -5975,7 +5935,7 @@
         <v/>
       </c>
       <c r="Q88">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R88" t="str">
         <v>3</v>
@@ -5989,7 +5949,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B89" t="str">
         <v>SELVA L</v>
@@ -6028,7 +5988,7 @@
         <v>405</v>
       </c>
       <c r="N89" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O89" t="str">
         <v/>
@@ -6037,7 +5997,7 @@
         <v/>
       </c>
       <c r="Q89">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R89" t="str">
         <v>2</v>
@@ -6051,7 +6011,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B90" t="str">
         <v>SELVA L</v>
@@ -6087,10 +6047,10 @@
         <v>22</v>
       </c>
       <c r="M90" t="str">
-        <v>203</v>
+        <v>809</v>
       </c>
       <c r="N90" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O90" t="str">
         <v/>
@@ -6099,10 +6059,10 @@
         <v/>
       </c>
       <c r="Q90">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R90" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S90">
         <v>0</v>
@@ -6113,7 +6073,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B91" t="str">
         <v>SELVA L</v>
@@ -6149,10 +6109,10 @@
         <v>23</v>
       </c>
       <c r="M91" t="str">
-        <v>10</v>
+        <v>607</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O91" t="str">
         <v/>
@@ -6161,10 +6121,10 @@
         <v/>
       </c>
       <c r="Q91">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R91" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -6175,7 +6135,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B92" t="str">
         <v>SELVA L</v>
@@ -6211,10 +6171,10 @@
         <v>24</v>
       </c>
       <c r="M92" t="str">
-        <v>8</v>
+        <v>10405</v>
       </c>
       <c r="N92" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O92" t="str">
         <v/>
@@ -6223,10 +6183,10 @@
         <v/>
       </c>
       <c r="Q92">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R92" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -6237,7 +6197,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B93" t="str">
         <v>SELVA L</v>
@@ -6273,10 +6233,10 @@
         <v>25</v>
       </c>
       <c r="M93" t="str">
-        <v>6</v>
+        <v>10809</v>
       </c>
       <c r="N93" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O93" t="str">
         <v/>
@@ -6285,10 +6245,10 @@
         <v/>
       </c>
       <c r="Q93">
-        <v>630</v>
+        <v>360</v>
       </c>
       <c r="R93" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -6299,7 +6259,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B94" t="str">
         <v>SELVA L</v>
@@ -6335,10 +6295,10 @@
         <v>26</v>
       </c>
       <c r="M94" t="str">
-        <v>2</v>
+        <v>10405</v>
       </c>
       <c r="N94" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O94" t="str">
         <v/>
@@ -6347,10 +6307,10 @@
         <v/>
       </c>
       <c r="Q94">
-        <v>1470</v>
+        <v>840</v>
       </c>
       <c r="R94" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -6361,7 +6321,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B95" t="str">
         <v>SELVA L</v>
@@ -6397,10 +6357,10 @@
         <v>27</v>
       </c>
       <c r="M95" t="str">
-        <v>4</v>
+        <v>10607</v>
       </c>
       <c r="N95" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -6409,10 +6369,10 @@
         <v/>
       </c>
       <c r="Q95">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R95" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -6423,7 +6383,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B96" t="str">
         <v>SELVA L</v>
@@ -6462,7 +6422,7 @@
         <v>405</v>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -6471,7 +6431,7 @@
         <v/>
       </c>
       <c r="Q96">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R96" t="str">
         <v>2</v>
@@ -6485,7 +6445,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B97" t="str">
         <v>SELVA L</v>
@@ -6521,10 +6481,10 @@
         <v>29</v>
       </c>
       <c r="M97" t="str">
-        <v>203</v>
+        <v>809</v>
       </c>
       <c r="N97" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -6533,10 +6493,10 @@
         <v/>
       </c>
       <c r="Q97">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R97" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S97">
         <v>0</v>
@@ -6547,7 +6507,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B98" t="str">
         <v>SELVA L</v>
@@ -6583,10 +6543,10 @@
         <v>30</v>
       </c>
       <c r="M98" t="str">
-        <v>11110</v>
+        <v>607</v>
       </c>
       <c r="N98" t="str">
-        <v/>
+        <v>synchronicznie</v>
       </c>
       <c r="O98" t="str">
         <v/>
@@ -6595,10 +6555,10 @@
         <v/>
       </c>
       <c r="Q98">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R98" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S98">
         <v>0</v>
@@ -6609,7 +6569,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B99" t="str">
         <v>SELVA L</v>
@@ -6645,10 +6605,10 @@
         <v>31</v>
       </c>
       <c r="M99" t="str">
-        <v>8</v>
+        <v>10405</v>
       </c>
       <c r="N99" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -6657,10 +6617,10 @@
         <v/>
       </c>
       <c r="Q99">
-        <v>1260</v>
+        <v>720</v>
       </c>
       <c r="R99" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S99">
         <v>0</v>
@@ -6671,7 +6631,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B100" t="str">
         <v>SELVA L</v>
@@ -6707,10 +6667,10 @@
         <v>32</v>
       </c>
       <c r="M100" t="str">
-        <v>6</v>
+        <v>10809</v>
       </c>
       <c r="N100" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O100" t="str">
         <v/>
@@ -6719,10 +6679,10 @@
         <v/>
       </c>
       <c r="Q100">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="R100" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S100">
         <v>0</v>
@@ -6733,7 +6693,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B101" t="str">
         <v>SELVA L</v>
@@ -6769,10 +6729,10 @@
         <v>33</v>
       </c>
       <c r="M101" t="str">
-        <v>4</v>
+        <v>10607</v>
       </c>
       <c r="N101" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -6781,10 +6741,10 @@
         <v/>
       </c>
       <c r="Q101">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R101" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S101">
         <v>0</v>
@@ -6795,7 +6755,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>selval</v>
+        <v>selval120</v>
       </c>
       <c r="B102" t="str">
         <v>SELVA L</v>
@@ -6831,10 +6791,10 @@
         <v>34</v>
       </c>
       <c r="M102" t="str">
-        <v>2</v>
+        <v>10405</v>
       </c>
       <c r="N102" t="str">
-        <v/>
+        <v>naprzemiennie</v>
       </c>
       <c r="O102" t="str">
         <v/>
@@ -6843,4361 +6803,21 @@
         <v/>
       </c>
       <c r="Q102">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="R102" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S102">
         <v>0</v>
       </c>
       <c r="T102" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B103" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C103" t="str">
-        <v>SELVA L 215,5 FR</v>
-      </c>
-      <c r="D103" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E103">
-        <v>2155</v>
-      </c>
-      <c r="F103">
-        <v>30</v>
-      </c>
-      <c r="G103">
-        <v>60</v>
-      </c>
-      <c r="H103" t="str">
-        <v>So</v>
-      </c>
-      <c r="I103">
-        <v>2</v>
-      </c>
-      <c r="J103">
-        <v>2</v>
-      </c>
-      <c r="K103">
-        <v>26</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103" t="str">
-        <v>809</v>
-      </c>
-      <c r="N103" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O103" t="str">
-        <v/>
-      </c>
-      <c r="P103" t="str">
-        <v/>
-      </c>
-      <c r="Q103">
-        <v>90</v>
-      </c>
-      <c r="R103" t="str">
-        <v>4</v>
-      </c>
-      <c r="S103">
-        <v>0</v>
-      </c>
-      <c r="T103" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B104" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C104" t="str">
-        <v>SELVA L 215,5 FR+KL</v>
-      </c>
-      <c r="D104" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E104">
-        <v>2155</v>
-      </c>
-      <c r="F104">
-        <v>30</v>
-      </c>
-      <c r="G104">
-        <v>60</v>
-      </c>
-      <c r="H104" t="str">
-        <v>So</v>
-      </c>
-      <c r="I104">
-        <v>2</v>
-      </c>
-      <c r="J104">
-        <v>2</v>
-      </c>
-      <c r="K104">
-        <v>26</v>
-      </c>
-      <c r="L104">
-        <v>1</v>
-      </c>
-      <c r="M104" t="str">
-        <v>1011</v>
-      </c>
-      <c r="N104" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O104" t="str">
-        <v/>
-      </c>
-      <c r="P104" t="str">
-        <v/>
-      </c>
-      <c r="Q104">
-        <v>90</v>
-      </c>
-      <c r="R104" t="str">
-        <v>5</v>
-      </c>
-      <c r="S104">
-        <v>0</v>
-      </c>
-      <c r="T104" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B105" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C105" t="str">
-        <v>SELVA L 209,5 KL</v>
-      </c>
-      <c r="D105" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E105">
-        <v>2095</v>
-      </c>
-      <c r="F105">
-        <v>30</v>
-      </c>
-      <c r="G105">
-        <v>60</v>
-      </c>
-      <c r="H105" t="str">
-        <v>So</v>
-      </c>
-      <c r="I105">
-        <v>2</v>
-      </c>
-      <c r="J105">
-        <v>2</v>
-      </c>
-      <c r="K105">
-        <v>26</v>
-      </c>
-      <c r="L105">
-        <v>2</v>
-      </c>
-      <c r="M105" t="str">
-        <v>607</v>
-      </c>
-      <c r="N105" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O105" t="str">
-        <v/>
-      </c>
-      <c r="P105" t="str">
-        <v/>
-      </c>
-      <c r="Q105">
-        <v>90</v>
-      </c>
-      <c r="R105" t="str">
-        <v>3</v>
-      </c>
-      <c r="S105">
-        <v>0</v>
-      </c>
-      <c r="T105" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B106" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C106" t="str">
-        <v>SELVA L 134</v>
-      </c>
-      <c r="D106" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E106">
-        <v>1340</v>
-      </c>
-      <c r="F106">
-        <v>30</v>
-      </c>
-      <c r="G106">
-        <v>60</v>
-      </c>
-      <c r="H106" t="str">
-        <v>So</v>
-      </c>
-      <c r="I106">
-        <v>2</v>
-      </c>
-      <c r="J106">
-        <v>2</v>
-      </c>
-      <c r="K106">
-        <v>26</v>
-      </c>
-      <c r="L106">
-        <v>3</v>
-      </c>
-      <c r="M106" t="str">
-        <v>1011</v>
-      </c>
-      <c r="N106" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O106" t="str">
-        <v/>
-      </c>
-      <c r="P106" t="str">
-        <v/>
-      </c>
-      <c r="Q106">
-        <v>90</v>
-      </c>
-      <c r="R106" t="str">
-        <v>5</v>
-      </c>
-      <c r="S106">
-        <v>0</v>
-      </c>
-      <c r="T106" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B107" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C107" t="str">
-        <v>SELVA L 134 FR+KL</v>
-      </c>
-      <c r="D107" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E107">
-        <v>1340</v>
-      </c>
-      <c r="F107">
-        <v>30</v>
-      </c>
-      <c r="G107">
-        <v>60</v>
-      </c>
-      <c r="H107" t="str">
-        <v>So</v>
-      </c>
-      <c r="I107">
-        <v>2</v>
-      </c>
-      <c r="J107">
-        <v>2</v>
-      </c>
-      <c r="K107">
-        <v>26</v>
-      </c>
-      <c r="L107">
-        <v>4</v>
-      </c>
-      <c r="M107" t="str">
-        <v>405</v>
-      </c>
-      <c r="N107" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O107" t="str">
-        <v/>
-      </c>
-      <c r="P107" t="str">
-        <v/>
-      </c>
-      <c r="Q107">
-        <v>180</v>
-      </c>
-      <c r="R107" t="str">
-        <v>2</v>
-      </c>
-      <c r="S107">
-        <v>0</v>
-      </c>
-      <c r="T107" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B108" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C108" t="str">
-        <v>SELVA L 88 FR</v>
-      </c>
-      <c r="D108" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E108">
-        <v>880</v>
-      </c>
-      <c r="F108">
-        <v>30</v>
-      </c>
-      <c r="G108">
-        <v>60</v>
-      </c>
-      <c r="H108" t="str">
-        <v>So</v>
-      </c>
-      <c r="I108">
-        <v>2</v>
-      </c>
-      <c r="J108">
-        <v>2</v>
-      </c>
-      <c r="K108">
-        <v>26</v>
-      </c>
-      <c r="L108">
-        <v>5</v>
-      </c>
-      <c r="M108" t="str">
-        <v>809</v>
-      </c>
-      <c r="N108" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O108" t="str">
-        <v/>
-      </c>
-      <c r="P108" t="str">
-        <v/>
-      </c>
-      <c r="Q108">
-        <v>180</v>
-      </c>
-      <c r="R108" t="str">
-        <v>4</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
-      <c r="T108" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B109" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C109" t="str">
-        <v>SELVA L 63 FR</v>
-      </c>
-      <c r="D109" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E109">
-        <v>630</v>
-      </c>
-      <c r="F109">
-        <v>30</v>
-      </c>
-      <c r="G109">
-        <v>60</v>
-      </c>
-      <c r="H109" t="str">
-        <v>So</v>
-      </c>
-      <c r="I109">
-        <v>2</v>
-      </c>
-      <c r="J109">
-        <v>2</v>
-      </c>
-      <c r="K109">
-        <v>26</v>
-      </c>
-      <c r="L109">
-        <v>6</v>
-      </c>
-      <c r="M109" t="str">
-        <v>405</v>
-      </c>
-      <c r="N109" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O109" t="str">
-        <v/>
-      </c>
-      <c r="P109" t="str">
-        <v/>
-      </c>
-      <c r="Q109">
-        <v>180</v>
-      </c>
-      <c r="R109" t="str">
-        <v>2</v>
-      </c>
-      <c r="S109">
-        <v>0</v>
-      </c>
-      <c r="T109" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B110" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C110" t="str">
-        <v>SELVA L 57</v>
-      </c>
-      <c r="D110" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E110">
-        <v>570</v>
-      </c>
-      <c r="F110">
-        <v>30</v>
-      </c>
-      <c r="G110">
-        <v>60</v>
-      </c>
-      <c r="H110" t="str">
-        <v>So</v>
-      </c>
-      <c r="I110">
-        <v>2</v>
-      </c>
-      <c r="J110">
-        <v>2</v>
-      </c>
-      <c r="K110">
-        <v>26</v>
-      </c>
-      <c r="L110">
-        <v>7</v>
-      </c>
-      <c r="M110" t="str">
-        <v>11011</v>
-      </c>
-      <c r="N110" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O110" t="str">
-        <v/>
-      </c>
-      <c r="P110" t="str">
-        <v/>
-      </c>
-      <c r="Q110">
-        <v>450</v>
-      </c>
-      <c r="R110" t="str">
-        <v>5</v>
-      </c>
-      <c r="S110">
-        <v>0</v>
-      </c>
-      <c r="T110" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B111" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C111" t="str">
-        <v>SELVA L 22</v>
-      </c>
-      <c r="D111" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E111">
-        <v>220</v>
-      </c>
-      <c r="F111">
-        <v>30</v>
-      </c>
-      <c r="G111">
-        <v>60</v>
-      </c>
-      <c r="H111" t="str">
-        <v>So</v>
-      </c>
-      <c r="I111">
-        <v>2</v>
-      </c>
-      <c r="J111">
-        <v>2</v>
-      </c>
-      <c r="K111">
-        <v>26</v>
-      </c>
-      <c r="L111">
-        <v>8</v>
-      </c>
-      <c r="M111" t="str">
-        <v>10607</v>
-      </c>
-      <c r="N111" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O111" t="str">
-        <v/>
-      </c>
-      <c r="P111" t="str">
-        <v/>
-      </c>
-      <c r="Q111">
-        <v>540</v>
-      </c>
-      <c r="R111" t="str">
-        <v>3</v>
-      </c>
-      <c r="S111">
-        <v>0</v>
-      </c>
-      <c r="T111" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B112" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C112" t="str">
-        <v>SELVA L 86,5 SZ</v>
-      </c>
-      <c r="D112" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E112">
-        <v>865</v>
-      </c>
-      <c r="F112">
-        <v>30</v>
-      </c>
-      <c r="G112">
-        <v>60</v>
-      </c>
-      <c r="H112" t="str">
-        <v>So</v>
-      </c>
-      <c r="I112">
-        <v>1</v>
-      </c>
-      <c r="J112">
-        <v>1</v>
-      </c>
-      <c r="K112">
-        <v>26</v>
-      </c>
-      <c r="L112">
-        <v>9</v>
-      </c>
-      <c r="M112" t="str">
-        <v>607</v>
-      </c>
-      <c r="N112" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O112" t="str">
-        <v/>
-      </c>
-      <c r="P112" t="str">
-        <v/>
-      </c>
-      <c r="Q112">
-        <v>180</v>
-      </c>
-      <c r="R112" t="str">
-        <v>3</v>
-      </c>
-      <c r="S112">
-        <v>0</v>
-      </c>
-      <c r="T112" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B113" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C113" t="str">
-        <v>SELVA L 11 SZ</v>
-      </c>
-      <c r="D113" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E113">
-        <v>110</v>
-      </c>
-      <c r="F113">
-        <v>30</v>
-      </c>
-      <c r="G113">
-        <v>60</v>
-      </c>
-      <c r="H113" t="str">
-        <v>So</v>
-      </c>
-      <c r="I113">
-        <v>1</v>
-      </c>
-      <c r="J113">
-        <v>1</v>
-      </c>
-      <c r="K113">
-        <v>26</v>
-      </c>
-      <c r="L113">
-        <v>10</v>
-      </c>
-      <c r="M113" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N113" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O113" t="str">
-        <v/>
-      </c>
-      <c r="P113" t="str">
-        <v/>
-      </c>
-      <c r="Q113">
-        <v>540</v>
-      </c>
-      <c r="R113" t="str">
-        <v>2</v>
-      </c>
-      <c r="S113">
-        <v>0</v>
-      </c>
-      <c r="T113" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B114" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C114" t="str">
-        <v>SELVA L 23</v>
-      </c>
-      <c r="D114" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E114">
-        <v>230</v>
-      </c>
-      <c r="F114">
-        <v>30</v>
-      </c>
-      <c r="G114">
-        <v>60</v>
-      </c>
-      <c r="H114" t="str">
-        <v>So</v>
-      </c>
-      <c r="I114">
-        <v>2</v>
-      </c>
-      <c r="J114">
-        <v>2</v>
-      </c>
-      <c r="K114">
-        <v>26</v>
-      </c>
-      <c r="L114">
-        <v>11</v>
-      </c>
-      <c r="M114" t="str">
-        <v>10809</v>
-      </c>
-      <c r="N114" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O114" t="str">
-        <v/>
-      </c>
-      <c r="P114" t="str">
-        <v/>
-      </c>
-      <c r="Q114">
-        <v>270</v>
-      </c>
-      <c r="R114" t="str">
-        <v>4</v>
-      </c>
-      <c r="S114">
-        <v>0</v>
-      </c>
-      <c r="T114" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B115" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C115" t="str">
-        <v>SELVA L 17,9</v>
-      </c>
-      <c r="D115" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E115">
-        <v>179</v>
-      </c>
-      <c r="F115">
-        <v>30</v>
-      </c>
-      <c r="G115">
-        <v>80</v>
-      </c>
-      <c r="H115" t="str">
-        <v>So</v>
-      </c>
-      <c r="I115">
-        <v>2</v>
-      </c>
-      <c r="J115">
-        <v>2</v>
-      </c>
-      <c r="K115">
-        <v>26</v>
-      </c>
-      <c r="L115">
-        <v>12</v>
-      </c>
-      <c r="M115" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N115" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O115" t="str">
-        <v/>
-      </c>
-      <c r="P115" t="str">
-        <v/>
-      </c>
-      <c r="Q115">
-        <v>900</v>
-      </c>
-      <c r="R115" t="str">
-        <v>2</v>
-      </c>
-      <c r="S115">
-        <v>0</v>
-      </c>
-      <c r="T115" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B116" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C116" t="str">
-        <v>SELVA L 35 SZ</v>
-      </c>
-      <c r="D116" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E116">
-        <v>350</v>
-      </c>
-      <c r="F116">
-        <v>30</v>
-      </c>
-      <c r="G116">
-        <v>30</v>
-      </c>
-      <c r="H116" t="str">
-        <v>So</v>
-      </c>
-      <c r="I116">
-        <v>1</v>
-      </c>
-      <c r="J116">
-        <v>1</v>
-      </c>
-      <c r="K116">
-        <v>26</v>
-      </c>
-      <c r="L116">
-        <v>13</v>
-      </c>
-      <c r="M116" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N116" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O116" t="str">
-        <v/>
-      </c>
-      <c r="P116" t="str">
-        <v/>
-      </c>
-      <c r="Q116">
-        <v>180</v>
-      </c>
-      <c r="R116" t="str">
-        <v>2</v>
-      </c>
-      <c r="S116">
-        <v>0</v>
-      </c>
-      <c r="T116" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B117" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C117" t="str">
-        <v>SELVA L 80 PR</v>
-      </c>
-      <c r="D117" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E117">
-        <v>800</v>
-      </c>
-      <c r="F117">
-        <v>25</v>
-      </c>
-      <c r="G117">
-        <v>40</v>
-      </c>
-      <c r="H117" t="str">
-        <v>So</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117">
-        <v>1</v>
-      </c>
-      <c r="K117">
-        <v>26</v>
-      </c>
-      <c r="L117">
-        <v>14</v>
-      </c>
-      <c r="M117" t="str">
-        <v>405</v>
-      </c>
-      <c r="N117" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O117" t="str">
-        <v/>
-      </c>
-      <c r="P117" t="str">
-        <v/>
-      </c>
-      <c r="Q117">
-        <v>180</v>
-      </c>
-      <c r="R117" t="str">
-        <v>2</v>
-      </c>
-      <c r="S117">
-        <v>0</v>
-      </c>
-      <c r="T117" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B118" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C118" t="str">
-        <v>SELVA L 156,5</v>
-      </c>
-      <c r="D118" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E118">
-        <v>1565</v>
-      </c>
-      <c r="F118">
-        <v>25</v>
-      </c>
-      <c r="G118">
-        <v>25</v>
-      </c>
-      <c r="H118" t="str">
-        <v>So</v>
-      </c>
-      <c r="I118">
-        <v>2</v>
-      </c>
-      <c r="J118">
-        <v>2</v>
-      </c>
-      <c r="K118">
-        <v>26</v>
-      </c>
-      <c r="L118">
-        <v>15</v>
-      </c>
-      <c r="M118" t="str">
-        <v>405</v>
-      </c>
-      <c r="N118" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O118" t="str">
-        <v/>
-      </c>
-      <c r="P118" t="str">
-        <v/>
-      </c>
-      <c r="Q118">
-        <v>90</v>
-      </c>
-      <c r="R118" t="str">
-        <v>2</v>
-      </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
-      <c r="T118" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B119" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C119" t="str">
-        <v>SELVA L 136</v>
-      </c>
-      <c r="D119" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E119">
-        <v>1360</v>
-      </c>
-      <c r="F119">
-        <v>25</v>
-      </c>
-      <c r="G119">
-        <v>25</v>
-      </c>
-      <c r="H119" t="str">
-        <v>So</v>
-      </c>
-      <c r="I119">
-        <v>2</v>
-      </c>
-      <c r="J119">
-        <v>2</v>
-      </c>
-      <c r="K119">
-        <v>26</v>
-      </c>
-      <c r="L119">
-        <v>16</v>
-      </c>
-      <c r="M119" t="str">
-        <v>1011</v>
-      </c>
-      <c r="N119" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O119" t="str">
-        <v/>
-      </c>
-      <c r="P119" t="str">
-        <v/>
-      </c>
-      <c r="Q119">
-        <v>90</v>
-      </c>
-      <c r="R119" t="str">
-        <v>5</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B120" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C120" t="str">
-        <v>SELVA L 132</v>
-      </c>
-      <c r="D120" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E120">
-        <v>1320</v>
-      </c>
-      <c r="F120">
-        <v>25</v>
-      </c>
-      <c r="G120">
-        <v>25</v>
-      </c>
-      <c r="H120" t="str">
-        <v>So</v>
-      </c>
-      <c r="I120">
-        <v>2</v>
-      </c>
-      <c r="J120">
-        <v>2</v>
-      </c>
-      <c r="K120">
-        <v>26</v>
-      </c>
-      <c r="L120">
-        <v>17</v>
-      </c>
-      <c r="M120" t="str">
-        <v>607</v>
-      </c>
-      <c r="N120" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O120" t="str">
-        <v/>
-      </c>
-      <c r="P120" t="str">
-        <v/>
-      </c>
-      <c r="Q120">
-        <v>90</v>
-      </c>
-      <c r="R120" t="str">
-        <v>3</v>
-      </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
-      <c r="T120" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B121" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C121" t="str">
-        <v>SELVA L 134</v>
-      </c>
-      <c r="D121" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E121">
-        <v>1340</v>
-      </c>
-      <c r="F121">
-        <v>25</v>
-      </c>
-      <c r="G121">
-        <v>25</v>
-      </c>
-      <c r="H121" t="str">
-        <v>So</v>
-      </c>
-      <c r="I121">
-        <v>2</v>
-      </c>
-      <c r="J121">
-        <v>2</v>
-      </c>
-      <c r="K121">
-        <v>26</v>
-      </c>
-      <c r="L121">
-        <v>18</v>
-      </c>
-      <c r="M121" t="str">
-        <v>809</v>
-      </c>
-      <c r="N121" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O121" t="str">
-        <v/>
-      </c>
-      <c r="P121" t="str">
-        <v/>
-      </c>
-      <c r="Q121">
-        <v>270</v>
-      </c>
-      <c r="R121" t="str">
-        <v>4</v>
-      </c>
-      <c r="S121">
-        <v>0</v>
-      </c>
-      <c r="T121" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B122" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C122" t="str">
-        <v>SELVA L 125</v>
-      </c>
-      <c r="D122" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E122">
-        <v>1250</v>
-      </c>
-      <c r="F122">
-        <v>25</v>
-      </c>
-      <c r="G122">
-        <v>25</v>
-      </c>
-      <c r="H122" t="str">
-        <v>So</v>
-      </c>
-      <c r="I122">
-        <v>2</v>
-      </c>
-      <c r="J122">
-        <v>2</v>
-      </c>
-      <c r="K122">
-        <v>26</v>
-      </c>
-      <c r="L122">
-        <v>19</v>
-      </c>
-      <c r="M122" t="str">
-        <v>405</v>
-      </c>
-      <c r="N122" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O122" t="str">
-        <v/>
-      </c>
-      <c r="P122" t="str">
-        <v/>
-      </c>
-      <c r="Q122">
-        <v>90</v>
-      </c>
-      <c r="R122" t="str">
-        <v>2</v>
-      </c>
-      <c r="S122">
-        <v>0</v>
-      </c>
-      <c r="T122" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B123" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C123" t="str">
-        <v>SELVA L 112 SZ</v>
-      </c>
-      <c r="D123" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E123">
-        <v>1120</v>
-      </c>
-      <c r="F123">
-        <v>25</v>
-      </c>
-      <c r="G123">
-        <v>25</v>
-      </c>
-      <c r="H123" t="str">
-        <v>So</v>
-      </c>
-      <c r="I123">
-        <v>1</v>
-      </c>
-      <c r="J123">
-        <v>1</v>
-      </c>
-      <c r="K123">
-        <v>26</v>
-      </c>
-      <c r="L123">
-        <v>20</v>
-      </c>
-      <c r="M123" t="str">
-        <v>1011</v>
-      </c>
-      <c r="N123" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O123" t="str">
-        <v/>
-      </c>
-      <c r="P123" t="str">
-        <v/>
-      </c>
-      <c r="Q123">
-        <v>90</v>
-      </c>
-      <c r="R123" t="str">
-        <v>5</v>
-      </c>
-      <c r="S123">
-        <v>0</v>
-      </c>
-      <c r="T123" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B124" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C124" t="str">
-        <v>SELVA L 85,5</v>
-      </c>
-      <c r="D124" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E124">
-        <v>855</v>
-      </c>
-      <c r="F124">
-        <v>25</v>
-      </c>
-      <c r="G124">
-        <v>25</v>
-      </c>
-      <c r="H124" t="str">
-        <v>So</v>
-      </c>
-      <c r="I124">
-        <v>2</v>
-      </c>
-      <c r="J124">
-        <v>2</v>
-      </c>
-      <c r="K124">
-        <v>26</v>
-      </c>
-      <c r="L124">
-        <v>21</v>
-      </c>
-      <c r="M124" t="str">
-        <v>809</v>
-      </c>
-      <c r="N124" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O124" t="str">
-        <v/>
-      </c>
-      <c r="P124" t="str">
-        <v/>
-      </c>
-      <c r="Q124">
-        <v>90</v>
-      </c>
-      <c r="R124" t="str">
-        <v>4</v>
-      </c>
-      <c r="S124">
-        <v>0</v>
-      </c>
-      <c r="T124" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B125" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C125" t="str">
-        <v>SELVA L 65</v>
-      </c>
-      <c r="D125" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E125">
-        <v>650</v>
-      </c>
-      <c r="F125">
-        <v>25</v>
-      </c>
-      <c r="G125">
-        <v>25</v>
-      </c>
-      <c r="H125" t="str">
-        <v>So</v>
-      </c>
-      <c r="I125">
-        <v>2</v>
-      </c>
-      <c r="J125">
-        <v>2</v>
-      </c>
-      <c r="K125">
-        <v>26</v>
-      </c>
-      <c r="L125">
-        <v>22</v>
-      </c>
-      <c r="M125" t="str">
-        <v>607</v>
-      </c>
-      <c r="N125" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O125" t="str">
-        <v/>
-      </c>
-      <c r="P125" t="str">
-        <v/>
-      </c>
-      <c r="Q125">
-        <v>90</v>
-      </c>
-      <c r="R125" t="str">
-        <v>3</v>
-      </c>
-      <c r="S125">
-        <v>0</v>
-      </c>
-      <c r="T125" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B126" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C126" t="str">
-        <v>SELVA L 61</v>
-      </c>
-      <c r="D126" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E126">
-        <v>610</v>
-      </c>
-      <c r="F126">
-        <v>25</v>
-      </c>
-      <c r="G126">
-        <v>25</v>
-      </c>
-      <c r="H126" t="str">
-        <v>So</v>
-      </c>
-      <c r="I126">
-        <v>2</v>
-      </c>
-      <c r="J126">
-        <v>2</v>
-      </c>
-      <c r="K126">
-        <v>26</v>
-      </c>
-      <c r="L126">
-        <v>23</v>
-      </c>
-      <c r="M126" t="str">
-        <v>405</v>
-      </c>
-      <c r="N126" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O126" t="str">
-        <v/>
-      </c>
-      <c r="P126" t="str">
-        <v/>
-      </c>
-      <c r="Q126">
-        <v>90</v>
-      </c>
-      <c r="R126" t="str">
-        <v>2</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B127" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C127" t="str">
-        <v>SELVA L 49</v>
-      </c>
-      <c r="D127" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E127">
-        <v>490</v>
-      </c>
-      <c r="F127">
-        <v>25</v>
-      </c>
-      <c r="G127">
-        <v>25</v>
-      </c>
-      <c r="H127" t="str">
-        <v>So</v>
-      </c>
-      <c r="I127">
-        <v>2</v>
-      </c>
-      <c r="J127">
-        <v>2</v>
-      </c>
-      <c r="K127">
-        <v>26</v>
-      </c>
-      <c r="L127">
-        <v>24</v>
-      </c>
-      <c r="M127" t="str">
-        <v>11011</v>
-      </c>
-      <c r="N127" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O127" t="str">
-        <v/>
-      </c>
-      <c r="P127" t="str">
-        <v/>
-      </c>
-      <c r="Q127">
-        <v>90</v>
-      </c>
-      <c r="R127" t="str">
-        <v>5</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B128" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C128" t="str">
-        <v>SELVA L 46,5</v>
-      </c>
-      <c r="D128" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E128">
-        <v>465</v>
-      </c>
-      <c r="F128">
-        <v>25</v>
-      </c>
-      <c r="G128">
-        <v>25</v>
-      </c>
-      <c r="H128" t="str">
-        <v>So</v>
-      </c>
-      <c r="I128">
-        <v>2</v>
-      </c>
-      <c r="J128">
-        <v>2</v>
-      </c>
-      <c r="K128">
-        <v>26</v>
-      </c>
-      <c r="L128">
-        <v>25</v>
-      </c>
-      <c r="M128" t="str">
-        <v>10809</v>
-      </c>
-      <c r="N128" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O128" t="str">
-        <v/>
-      </c>
-      <c r="P128" t="str">
-        <v/>
-      </c>
-      <c r="Q128">
-        <v>270</v>
-      </c>
-      <c r="R128" t="str">
-        <v>4</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B129" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C129" t="str">
-        <v>SELVA L 15,5</v>
-      </c>
-      <c r="D129" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E129">
-        <v>155</v>
-      </c>
-      <c r="F129">
-        <v>25</v>
-      </c>
-      <c r="G129">
-        <v>25</v>
-      </c>
-      <c r="H129" t="str">
-        <v>So</v>
-      </c>
-      <c r="I129">
-        <v>2</v>
-      </c>
-      <c r="J129">
-        <v>2</v>
-      </c>
-      <c r="K129">
-        <v>26</v>
-      </c>
-      <c r="L129">
-        <v>26</v>
-      </c>
-      <c r="M129" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N129" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O129" t="str">
-        <v/>
-      </c>
-      <c r="P129" t="str">
-        <v/>
-      </c>
-      <c r="Q129">
-        <v>630</v>
-      </c>
-      <c r="R129" t="str">
-        <v>2</v>
-      </c>
-      <c r="S129">
-        <v>0</v>
-      </c>
-      <c r="T129" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B130" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C130" t="str">
-        <v>SELVA L 25,5</v>
-      </c>
-      <c r="D130" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E130">
-        <v>255</v>
-      </c>
-      <c r="F130">
-        <v>25</v>
-      </c>
-      <c r="G130">
-        <v>25</v>
-      </c>
-      <c r="H130" t="str">
-        <v>So</v>
-      </c>
-      <c r="I130">
-        <v>2</v>
-      </c>
-      <c r="J130">
-        <v>2</v>
-      </c>
-      <c r="K130">
-        <v>26</v>
-      </c>
-      <c r="L130">
-        <v>27</v>
-      </c>
-      <c r="M130" t="str">
-        <v>10607</v>
-      </c>
-      <c r="N130" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O130" t="str">
-        <v/>
-      </c>
-      <c r="P130" t="str">
-        <v/>
-      </c>
-      <c r="Q130">
-        <v>180</v>
-      </c>
-      <c r="R130" t="str">
-        <v>3</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B131" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C131" t="str">
-        <v>SELVA L 137 SZ</v>
-      </c>
-      <c r="D131" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E131">
-        <v>1370</v>
-      </c>
-      <c r="F131">
-        <v>25</v>
-      </c>
-      <c r="G131">
-        <v>50</v>
-      </c>
-      <c r="H131" t="str">
-        <v>So</v>
-      </c>
-      <c r="I131">
-        <v>1</v>
-      </c>
-      <c r="J131">
-        <v>1</v>
-      </c>
-      <c r="K131">
-        <v>26</v>
-      </c>
-      <c r="L131">
-        <v>28</v>
-      </c>
-      <c r="M131" t="str">
-        <v>809</v>
-      </c>
-      <c r="N131" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O131" t="str">
-        <v/>
-      </c>
-      <c r="P131" t="str">
-        <v/>
-      </c>
-      <c r="Q131">
-        <v>90</v>
-      </c>
-      <c r="R131" t="str">
-        <v>4</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B132" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C132" t="str">
-        <v>SELVA L 112 SZ</v>
-      </c>
-      <c r="D132" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E132">
-        <v>1120</v>
-      </c>
-      <c r="F132">
-        <v>25</v>
-      </c>
-      <c r="G132">
-        <v>50</v>
-      </c>
-      <c r="H132" t="str">
-        <v>So</v>
-      </c>
-      <c r="I132">
-        <v>1</v>
-      </c>
-      <c r="J132">
-        <v>1</v>
-      </c>
-      <c r="K132">
-        <v>26</v>
-      </c>
-      <c r="L132">
-        <v>29</v>
-      </c>
-      <c r="M132" t="str">
-        <v>607</v>
-      </c>
-      <c r="N132" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O132" t="str">
-        <v/>
-      </c>
-      <c r="P132" t="str">
-        <v/>
-      </c>
-      <c r="Q132">
-        <v>90</v>
-      </c>
-      <c r="R132" t="str">
-        <v>3</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B133" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C133" t="str">
-        <v>SELVA L 86,5 SZ</v>
-      </c>
-      <c r="D133" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E133">
-        <v>865</v>
-      </c>
-      <c r="F133">
-        <v>25</v>
-      </c>
-      <c r="G133">
-        <v>50</v>
-      </c>
-      <c r="H133" t="str">
-        <v>So</v>
-      </c>
-      <c r="I133">
-        <v>1</v>
-      </c>
-      <c r="J133">
-        <v>1</v>
-      </c>
-      <c r="K133">
-        <v>26</v>
-      </c>
-      <c r="L133">
-        <v>30</v>
-      </c>
-      <c r="M133" t="str">
-        <v>405</v>
-      </c>
-      <c r="N133" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O133" t="str">
-        <v/>
-      </c>
-      <c r="P133" t="str">
-        <v/>
-      </c>
-      <c r="Q133">
-        <v>90</v>
-      </c>
-      <c r="R133" t="str">
-        <v>2</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B134" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C134" t="str">
-        <v>SELVA L 22</v>
-      </c>
-      <c r="D134" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E134">
-        <v>220</v>
-      </c>
-      <c r="F134">
-        <v>25</v>
-      </c>
-      <c r="G134">
-        <v>50</v>
-      </c>
-      <c r="H134" t="str">
-        <v>So</v>
-      </c>
-      <c r="I134">
-        <v>2</v>
-      </c>
-      <c r="J134">
-        <v>2</v>
-      </c>
-      <c r="K134">
-        <v>26</v>
-      </c>
-      <c r="L134">
-        <v>31</v>
-      </c>
-      <c r="M134" t="str">
-        <v>11011</v>
-      </c>
-      <c r="N134" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O134" t="str">
-        <v/>
-      </c>
-      <c r="P134" t="str">
-        <v/>
-      </c>
-      <c r="Q134">
-        <v>540</v>
-      </c>
-      <c r="R134" t="str">
-        <v>5</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B135" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C135" t="str">
-        <v>SELVA L 7,5</v>
-      </c>
-      <c r="D135" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E135">
-        <v>75</v>
-      </c>
-      <c r="F135">
-        <v>25</v>
-      </c>
-      <c r="G135">
-        <v>50</v>
-      </c>
-      <c r="H135" t="str">
-        <v>So</v>
-      </c>
-      <c r="I135">
-        <v>2</v>
-      </c>
-      <c r="J135">
-        <v>2</v>
-      </c>
-      <c r="K135">
-        <v>26</v>
-      </c>
-      <c r="L135">
-        <v>32</v>
-      </c>
-      <c r="M135" t="str">
-        <v>10809</v>
-      </c>
-      <c r="N135" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O135" t="str">
-        <v/>
-      </c>
-      <c r="P135" t="str">
-        <v/>
-      </c>
-      <c r="Q135">
-        <v>90</v>
-      </c>
-      <c r="R135" t="str">
-        <v>4</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B136" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C136" t="str">
-        <v>SELVA L 5,5</v>
-      </c>
-      <c r="D136" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E136">
-        <v>55</v>
-      </c>
-      <c r="F136">
-        <v>25</v>
-      </c>
-      <c r="G136">
-        <v>50</v>
-      </c>
-      <c r="H136" t="str">
-        <v>So</v>
-      </c>
-      <c r="I136">
-        <v>2</v>
-      </c>
-      <c r="J136">
-        <v>2</v>
-      </c>
-      <c r="K136">
-        <v>26</v>
-      </c>
-      <c r="L136">
-        <v>33</v>
-      </c>
-      <c r="M136" t="str">
-        <v>10607</v>
-      </c>
-      <c r="N136" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O136" t="str">
-        <v/>
-      </c>
-      <c r="P136" t="str">
-        <v/>
-      </c>
-      <c r="Q136">
-        <v>180</v>
-      </c>
-      <c r="R136" t="str">
-        <v>3</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>selval90</v>
-      </c>
-      <c r="B137" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C137" t="str">
-        <v>SELVA L 4</v>
-      </c>
-      <c r="D137" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E137">
-        <v>40</v>
-      </c>
-      <c r="F137">
-        <v>25</v>
-      </c>
-      <c r="G137">
-        <v>50</v>
-      </c>
-      <c r="H137" t="str">
-        <v>So</v>
-      </c>
-      <c r="I137">
-        <v>2</v>
-      </c>
-      <c r="J137">
-        <v>2</v>
-      </c>
-      <c r="K137">
-        <v>26</v>
-      </c>
-      <c r="L137">
-        <v>34</v>
-      </c>
-      <c r="M137" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N137" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O137" t="str">
-        <v/>
-      </c>
-      <c r="P137" t="str">
-        <v/>
-      </c>
-      <c r="Q137">
-        <v>180</v>
-      </c>
-      <c r="R137" t="str">
-        <v>2</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B138" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C138" t="str">
-        <v>SELVA L 215,5 FR</v>
-      </c>
-      <c r="D138" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E138">
-        <v>2155</v>
-      </c>
-      <c r="F138">
-        <v>30</v>
-      </c>
-      <c r="G138">
-        <v>60</v>
-      </c>
-      <c r="H138" t="str">
-        <v>So</v>
-      </c>
-      <c r="I138">
-        <v>2</v>
-      </c>
-      <c r="J138">
-        <v>2</v>
-      </c>
-      <c r="K138">
-        <v>26</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="str">
-        <v>203</v>
-      </c>
-      <c r="N138" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O138" t="str">
-        <v/>
-      </c>
-      <c r="P138" t="str">
-        <v/>
-      </c>
-      <c r="Q138">
-        <v>180</v>
-      </c>
-      <c r="R138" t="str">
-        <v>1</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B139" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C139" t="str">
-        <v>SELVA L 215,5 FR+KL</v>
-      </c>
-      <c r="D139" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E139">
-        <v>2155</v>
-      </c>
-      <c r="F139">
-        <v>30</v>
-      </c>
-      <c r="G139">
-        <v>60</v>
-      </c>
-      <c r="H139" t="str">
-        <v>So</v>
-      </c>
-      <c r="I139">
-        <v>2</v>
-      </c>
-      <c r="J139">
-        <v>2</v>
-      </c>
-      <c r="K139">
-        <v>26</v>
-      </c>
-      <c r="L139">
-        <v>1</v>
-      </c>
-      <c r="M139" t="str">
-        <v>405</v>
-      </c>
-      <c r="N139" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O139" t="str">
-        <v/>
-      </c>
-      <c r="P139" t="str">
-        <v/>
-      </c>
-      <c r="Q139">
-        <v>180</v>
-      </c>
-      <c r="R139" t="str">
-        <v>2</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B140" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C140" t="str">
-        <v>SELVA L 209,5 KL</v>
-      </c>
-      <c r="D140" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E140">
-        <v>2095</v>
-      </c>
-      <c r="F140">
-        <v>30</v>
-      </c>
-      <c r="G140">
-        <v>60</v>
-      </c>
-      <c r="H140" t="str">
-        <v>So</v>
-      </c>
-      <c r="I140">
-        <v>2</v>
-      </c>
-      <c r="J140">
-        <v>2</v>
-      </c>
-      <c r="K140">
-        <v>26</v>
-      </c>
-      <c r="L140">
-        <v>2</v>
-      </c>
-      <c r="M140" t="str">
-        <v>1011</v>
-      </c>
-      <c r="N140" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O140" t="str">
-        <v/>
-      </c>
-      <c r="P140" t="str">
-        <v/>
-      </c>
-      <c r="Q140">
-        <v>180</v>
-      </c>
-      <c r="R140" t="str">
-        <v>5</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B141" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C141" t="str">
-        <v>SELVA L 134</v>
-      </c>
-      <c r="D141" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E141">
-        <v>1340</v>
-      </c>
-      <c r="F141">
-        <v>30</v>
-      </c>
-      <c r="G141">
-        <v>60</v>
-      </c>
-      <c r="H141" t="str">
-        <v>So</v>
-      </c>
-      <c r="I141">
-        <v>2</v>
-      </c>
-      <c r="J141">
-        <v>2</v>
-      </c>
-      <c r="K141">
-        <v>26</v>
-      </c>
-      <c r="L141">
-        <v>3</v>
-      </c>
-      <c r="M141" t="str">
-        <v>607</v>
-      </c>
-      <c r="N141" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O141" t="str">
-        <v/>
-      </c>
-      <c r="P141" t="str">
-        <v/>
-      </c>
-      <c r="Q141">
-        <v>180</v>
-      </c>
-      <c r="R141" t="str">
-        <v>3</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B142" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C142" t="str">
-        <v>SELVA L 134 FR+KL</v>
-      </c>
-      <c r="D142" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E142">
-        <v>1340</v>
-      </c>
-      <c r="F142">
-        <v>30</v>
-      </c>
-      <c r="G142">
-        <v>60</v>
-      </c>
-      <c r="H142" t="str">
-        <v>So</v>
-      </c>
-      <c r="I142">
-        <v>2</v>
-      </c>
-      <c r="J142">
-        <v>2</v>
-      </c>
-      <c r="K142">
-        <v>26</v>
-      </c>
-      <c r="L142">
-        <v>4</v>
-      </c>
-      <c r="M142" t="str">
-        <v>809</v>
-      </c>
-      <c r="N142" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O142" t="str">
-        <v/>
-      </c>
-      <c r="P142" t="str">
-        <v/>
-      </c>
-      <c r="Q142">
-        <v>360</v>
-      </c>
-      <c r="R142" t="str">
-        <v>4</v>
-      </c>
-      <c r="S142">
-        <v>0</v>
-      </c>
-      <c r="T142" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B143" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C143" t="str">
-        <v>SELVA L 88 FR</v>
-      </c>
-      <c r="D143" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E143">
-        <v>880</v>
-      </c>
-      <c r="F143">
-        <v>30</v>
-      </c>
-      <c r="G143">
-        <v>60</v>
-      </c>
-      <c r="H143" t="str">
-        <v>So</v>
-      </c>
-      <c r="I143">
-        <v>2</v>
-      </c>
-      <c r="J143">
-        <v>2</v>
-      </c>
-      <c r="K143">
-        <v>26</v>
-      </c>
-      <c r="L143">
-        <v>5</v>
-      </c>
-      <c r="M143" t="str">
-        <v>405</v>
-      </c>
-      <c r="N143" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O143" t="str">
-        <v/>
-      </c>
-      <c r="P143" t="str">
-        <v/>
-      </c>
-      <c r="Q143">
-        <v>360</v>
-      </c>
-      <c r="R143" t="str">
-        <v>2</v>
-      </c>
-      <c r="S143">
-        <v>0</v>
-      </c>
-      <c r="T143" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B144" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C144" t="str">
-        <v>SELVA L 63 FR</v>
-      </c>
-      <c r="D144" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E144">
-        <v>630</v>
-      </c>
-      <c r="F144">
-        <v>30</v>
-      </c>
-      <c r="G144">
-        <v>60</v>
-      </c>
-      <c r="H144" t="str">
-        <v>So</v>
-      </c>
-      <c r="I144">
-        <v>2</v>
-      </c>
-      <c r="J144">
-        <v>2</v>
-      </c>
-      <c r="K144">
-        <v>26</v>
-      </c>
-      <c r="L144">
-        <v>6</v>
-      </c>
-      <c r="M144" t="str">
-        <v>11011</v>
-      </c>
-      <c r="N144" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O144" t="str">
-        <v/>
-      </c>
-      <c r="P144" t="str">
-        <v/>
-      </c>
-      <c r="Q144">
-        <v>360</v>
-      </c>
-      <c r="R144" t="str">
-        <v>5</v>
-      </c>
-      <c r="S144">
-        <v>0</v>
-      </c>
-      <c r="T144" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B145" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C145" t="str">
-        <v>SELVA L 57</v>
-      </c>
-      <c r="D145" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E145">
-        <v>570</v>
-      </c>
-      <c r="F145">
-        <v>30</v>
-      </c>
-      <c r="G145">
-        <v>60</v>
-      </c>
-      <c r="H145" t="str">
-        <v>So</v>
-      </c>
-      <c r="I145">
-        <v>2</v>
-      </c>
-      <c r="J145">
-        <v>2</v>
-      </c>
-      <c r="K145">
-        <v>26</v>
-      </c>
-      <c r="L145">
-        <v>7</v>
-      </c>
-      <c r="M145" t="str">
-        <v>809</v>
-      </c>
-      <c r="N145" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O145" t="str">
-        <v/>
-      </c>
-      <c r="P145" t="str">
-        <v/>
-      </c>
-      <c r="Q145">
-        <v>900</v>
-      </c>
-      <c r="R145" t="str">
-        <v>4</v>
-      </c>
-      <c r="S145">
-        <v>0</v>
-      </c>
-      <c r="T145" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B146" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C146" t="str">
-        <v>SELVA L 22</v>
-      </c>
-      <c r="D146" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E146">
-        <v>220</v>
-      </c>
-      <c r="F146">
-        <v>30</v>
-      </c>
-      <c r="G146">
-        <v>60</v>
-      </c>
-      <c r="H146" t="str">
-        <v>So</v>
-      </c>
-      <c r="I146">
-        <v>2</v>
-      </c>
-      <c r="J146">
-        <v>2</v>
-      </c>
-      <c r="K146">
-        <v>26</v>
-      </c>
-      <c r="L146">
-        <v>8</v>
-      </c>
-      <c r="M146" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N146" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O146" t="str">
-        <v/>
-      </c>
-      <c r="P146" t="str">
-        <v/>
-      </c>
-      <c r="Q146">
-        <v>1080</v>
-      </c>
-      <c r="R146" t="str">
-        <v>2</v>
-      </c>
-      <c r="S146">
-        <v>0</v>
-      </c>
-      <c r="T146" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B147" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C147" t="str">
-        <v>SELVA L 86,5 SZ</v>
-      </c>
-      <c r="D147" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E147">
-        <v>865</v>
-      </c>
-      <c r="F147">
-        <v>30</v>
-      </c>
-      <c r="G147">
-        <v>60</v>
-      </c>
-      <c r="H147" t="str">
-        <v>So</v>
-      </c>
-      <c r="I147">
-        <v>1</v>
-      </c>
-      <c r="J147">
-        <v>1</v>
-      </c>
-      <c r="K147">
-        <v>26</v>
-      </c>
-      <c r="L147">
-        <v>9</v>
-      </c>
-      <c r="M147" t="str">
-        <v>203</v>
-      </c>
-      <c r="N147" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O147" t="str">
-        <v/>
-      </c>
-      <c r="P147" t="str">
-        <v/>
-      </c>
-      <c r="Q147">
-        <v>360</v>
-      </c>
-      <c r="R147" t="str">
-        <v>1</v>
-      </c>
-      <c r="S147">
-        <v>0</v>
-      </c>
-      <c r="T147" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B148" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C148" t="str">
-        <v>SELVA L 11 SZ</v>
-      </c>
-      <c r="D148" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E148">
-        <v>110</v>
-      </c>
-      <c r="F148">
-        <v>30</v>
-      </c>
-      <c r="G148">
-        <v>60</v>
-      </c>
-      <c r="H148" t="str">
-        <v>So</v>
-      </c>
-      <c r="I148">
-        <v>1</v>
-      </c>
-      <c r="J148">
-        <v>1</v>
-      </c>
-      <c r="K148">
-        <v>26</v>
-      </c>
-      <c r="L148">
-        <v>10</v>
-      </c>
-      <c r="M148" t="str">
-        <v>10203</v>
-      </c>
-      <c r="N148" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O148" t="str">
-        <v/>
-      </c>
-      <c r="P148" t="str">
-        <v/>
-      </c>
-      <c r="Q148">
-        <v>1080</v>
-      </c>
-      <c r="R148" t="str">
-        <v>1</v>
-      </c>
-      <c r="S148">
-        <v>0</v>
-      </c>
-      <c r="T148" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B149" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C149" t="str">
-        <v>SELVA L 23</v>
-      </c>
-      <c r="D149" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E149">
-        <v>230</v>
-      </c>
-      <c r="F149">
-        <v>30</v>
-      </c>
-      <c r="G149">
-        <v>60</v>
-      </c>
-      <c r="H149" t="str">
-        <v>So</v>
-      </c>
-      <c r="I149">
-        <v>2</v>
-      </c>
-      <c r="J149">
-        <v>2</v>
-      </c>
-      <c r="K149">
-        <v>26</v>
-      </c>
-      <c r="L149">
-        <v>11</v>
-      </c>
-      <c r="M149" t="str">
-        <v>10607</v>
-      </c>
-      <c r="N149" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O149" t="str">
-        <v/>
-      </c>
-      <c r="P149" t="str">
-        <v/>
-      </c>
-      <c r="Q149">
-        <v>540</v>
-      </c>
-      <c r="R149" t="str">
-        <v>3</v>
-      </c>
-      <c r="S149">
-        <v>0</v>
-      </c>
-      <c r="T149" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B150" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C150" t="str">
-        <v>SELVA L 17,9</v>
-      </c>
-      <c r="D150" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E150">
-        <v>179</v>
-      </c>
-      <c r="F150">
-        <v>30</v>
-      </c>
-      <c r="G150">
-        <v>80</v>
-      </c>
-      <c r="H150" t="str">
-        <v>So</v>
-      </c>
-      <c r="I150">
-        <v>2</v>
-      </c>
-      <c r="J150">
-        <v>2</v>
-      </c>
-      <c r="K150">
-        <v>26</v>
-      </c>
-      <c r="L150">
-        <v>12</v>
-      </c>
-      <c r="M150" t="str">
-        <v>10203</v>
-      </c>
-      <c r="N150" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O150" t="str">
-        <v/>
-      </c>
-      <c r="P150" t="str">
-        <v/>
-      </c>
-      <c r="Q150">
-        <v>1800</v>
-      </c>
-      <c r="R150" t="str">
-        <v>1</v>
-      </c>
-      <c r="S150">
-        <v>0</v>
-      </c>
-      <c r="T150" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B151" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C151" t="str">
-        <v>SELVA L 35 SZ</v>
-      </c>
-      <c r="D151" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E151">
-        <v>350</v>
-      </c>
-      <c r="F151">
-        <v>30</v>
-      </c>
-      <c r="G151">
-        <v>30</v>
-      </c>
-      <c r="H151" t="str">
-        <v>So</v>
-      </c>
-      <c r="I151">
-        <v>1</v>
-      </c>
-      <c r="J151">
-        <v>1</v>
-      </c>
-      <c r="K151">
-        <v>26</v>
-      </c>
-      <c r="L151">
-        <v>13</v>
-      </c>
-      <c r="M151" t="str">
-        <v>10203</v>
-      </c>
-      <c r="N151" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O151" t="str">
-        <v/>
-      </c>
-      <c r="P151" t="str">
-        <v/>
-      </c>
-      <c r="Q151">
-        <v>360</v>
-      </c>
-      <c r="R151" t="str">
-        <v>1</v>
-      </c>
-      <c r="S151">
-        <v>0</v>
-      </c>
-      <c r="T151" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B152" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C152" t="str">
-        <v>SELVA L 80 PR</v>
-      </c>
-      <c r="D152" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E152">
-        <v>800</v>
-      </c>
-      <c r="F152">
-        <v>25</v>
-      </c>
-      <c r="G152">
-        <v>40</v>
-      </c>
-      <c r="H152" t="str">
-        <v>So</v>
-      </c>
-      <c r="I152">
-        <v>1</v>
-      </c>
-      <c r="J152">
-        <v>1</v>
-      </c>
-      <c r="K152">
-        <v>26</v>
-      </c>
-      <c r="L152">
-        <v>14</v>
-      </c>
-      <c r="M152" t="str">
-        <v>203</v>
-      </c>
-      <c r="N152" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O152" t="str">
-        <v/>
-      </c>
-      <c r="P152" t="str">
-        <v/>
-      </c>
-      <c r="Q152">
-        <v>360</v>
-      </c>
-      <c r="R152" t="str">
-        <v>1</v>
-      </c>
-      <c r="S152">
-        <v>0</v>
-      </c>
-      <c r="T152" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B153" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C153" t="str">
-        <v>SELVA L 156,5</v>
-      </c>
-      <c r="D153" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E153">
-        <v>1565</v>
-      </c>
-      <c r="F153">
-        <v>25</v>
-      </c>
-      <c r="G153">
-        <v>25</v>
-      </c>
-      <c r="H153" t="str">
-        <v>So</v>
-      </c>
-      <c r="I153">
-        <v>2</v>
-      </c>
-      <c r="J153">
-        <v>2</v>
-      </c>
-      <c r="K153">
-        <v>26</v>
-      </c>
-      <c r="L153">
-        <v>15</v>
-      </c>
-      <c r="M153" t="str">
-        <v>607</v>
-      </c>
-      <c r="N153" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O153" t="str">
-        <v/>
-      </c>
-      <c r="P153" t="str">
-        <v/>
-      </c>
-      <c r="Q153">
-        <v>180</v>
-      </c>
-      <c r="R153" t="str">
-        <v>3</v>
-      </c>
-      <c r="S153">
-        <v>0</v>
-      </c>
-      <c r="T153" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B154" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C154" t="str">
-        <v>SELVA L 136</v>
-      </c>
-      <c r="D154" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E154">
-        <v>1360</v>
-      </c>
-      <c r="F154">
-        <v>25</v>
-      </c>
-      <c r="G154">
-        <v>25</v>
-      </c>
-      <c r="H154" t="str">
-        <v>So</v>
-      </c>
-      <c r="I154">
-        <v>2</v>
-      </c>
-      <c r="J154">
-        <v>2</v>
-      </c>
-      <c r="K154">
-        <v>26</v>
-      </c>
-      <c r="L154">
-        <v>16</v>
-      </c>
-      <c r="M154" t="str">
-        <v>405</v>
-      </c>
-      <c r="N154" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O154" t="str">
-        <v/>
-      </c>
-      <c r="P154" t="str">
-        <v/>
-      </c>
-      <c r="Q154">
-        <v>180</v>
-      </c>
-      <c r="R154" t="str">
-        <v>2</v>
-      </c>
-      <c r="S154">
-        <v>0</v>
-      </c>
-      <c r="T154" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B155" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C155" t="str">
-        <v>SELVA L 132</v>
-      </c>
-      <c r="D155" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E155">
-        <v>1320</v>
-      </c>
-      <c r="F155">
-        <v>25</v>
-      </c>
-      <c r="G155">
-        <v>25</v>
-      </c>
-      <c r="H155" t="str">
-        <v>So</v>
-      </c>
-      <c r="I155">
-        <v>2</v>
-      </c>
-      <c r="J155">
-        <v>2</v>
-      </c>
-      <c r="K155">
-        <v>26</v>
-      </c>
-      <c r="L155">
-        <v>17</v>
-      </c>
-      <c r="M155" t="str">
-        <v>1011</v>
-      </c>
-      <c r="N155" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O155" t="str">
-        <v/>
-      </c>
-      <c r="P155" t="str">
-        <v/>
-      </c>
-      <c r="Q155">
-        <v>180</v>
-      </c>
-      <c r="R155" t="str">
-        <v>5</v>
-      </c>
-      <c r="S155">
-        <v>0</v>
-      </c>
-      <c r="T155" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B156" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C156" t="str">
-        <v>SELVA L 134</v>
-      </c>
-      <c r="D156" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E156">
-        <v>1340</v>
-      </c>
-      <c r="F156">
-        <v>25</v>
-      </c>
-      <c r="G156">
-        <v>25</v>
-      </c>
-      <c r="H156" t="str">
-        <v>So</v>
-      </c>
-      <c r="I156">
-        <v>2</v>
-      </c>
-      <c r="J156">
-        <v>2</v>
-      </c>
-      <c r="K156">
-        <v>26</v>
-      </c>
-      <c r="L156">
-        <v>18</v>
-      </c>
-      <c r="M156" t="str">
-        <v>203</v>
-      </c>
-      <c r="N156" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O156" t="str">
-        <v/>
-      </c>
-      <c r="P156" t="str">
-        <v/>
-      </c>
-      <c r="Q156">
-        <v>540</v>
-      </c>
-      <c r="R156" t="str">
-        <v>1</v>
-      </c>
-      <c r="S156">
-        <v>0</v>
-      </c>
-      <c r="T156" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B157" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C157" t="str">
-        <v>SELVA L 125</v>
-      </c>
-      <c r="D157" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E157">
-        <v>1250</v>
-      </c>
-      <c r="F157">
-        <v>25</v>
-      </c>
-      <c r="G157">
-        <v>25</v>
-      </c>
-      <c r="H157" t="str">
-        <v>So</v>
-      </c>
-      <c r="I157">
-        <v>2</v>
-      </c>
-      <c r="J157">
-        <v>2</v>
-      </c>
-      <c r="K157">
-        <v>26</v>
-      </c>
-      <c r="L157">
-        <v>19</v>
-      </c>
-      <c r="M157" t="str">
-        <v>809</v>
-      </c>
-      <c r="N157" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O157" t="str">
-        <v/>
-      </c>
-      <c r="P157" t="str">
-        <v/>
-      </c>
-      <c r="Q157">
-        <v>180</v>
-      </c>
-      <c r="R157" t="str">
-        <v>4</v>
-      </c>
-      <c r="S157">
-        <v>0</v>
-      </c>
-      <c r="T157" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B158" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C158" t="str">
-        <v>SELVA L 112 SZ</v>
-      </c>
-      <c r="D158" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E158">
-        <v>1120</v>
-      </c>
-      <c r="F158">
-        <v>25</v>
-      </c>
-      <c r="G158">
-        <v>25</v>
-      </c>
-      <c r="H158" t="str">
-        <v>So</v>
-      </c>
-      <c r="I158">
-        <v>1</v>
-      </c>
-      <c r="J158">
-        <v>1</v>
-      </c>
-      <c r="K158">
-        <v>26</v>
-      </c>
-      <c r="L158">
-        <v>20</v>
-      </c>
-      <c r="M158" t="str">
-        <v>607</v>
-      </c>
-      <c r="N158" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O158" t="str">
-        <v/>
-      </c>
-      <c r="P158" t="str">
-        <v/>
-      </c>
-      <c r="Q158">
-        <v>180</v>
-      </c>
-      <c r="R158" t="str">
-        <v>3</v>
-      </c>
-      <c r="S158">
-        <v>0</v>
-      </c>
-      <c r="T158" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B159" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C159" t="str">
-        <v>SELVA L 85,5</v>
-      </c>
-      <c r="D159" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E159">
-        <v>855</v>
-      </c>
-      <c r="F159">
-        <v>25</v>
-      </c>
-      <c r="G159">
-        <v>25</v>
-      </c>
-      <c r="H159" t="str">
-        <v>So</v>
-      </c>
-      <c r="I159">
-        <v>2</v>
-      </c>
-      <c r="J159">
-        <v>2</v>
-      </c>
-      <c r="K159">
-        <v>26</v>
-      </c>
-      <c r="L159">
-        <v>21</v>
-      </c>
-      <c r="M159" t="str">
-        <v>405</v>
-      </c>
-      <c r="N159" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O159" t="str">
-        <v/>
-      </c>
-      <c r="P159" t="str">
-        <v/>
-      </c>
-      <c r="Q159">
-        <v>180</v>
-      </c>
-      <c r="R159" t="str">
-        <v>2</v>
-      </c>
-      <c r="S159">
-        <v>0</v>
-      </c>
-      <c r="T159" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B160" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C160" t="str">
-        <v>SELVA L 65</v>
-      </c>
-      <c r="D160" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E160">
-        <v>650</v>
-      </c>
-      <c r="F160">
-        <v>25</v>
-      </c>
-      <c r="G160">
-        <v>25</v>
-      </c>
-      <c r="H160" t="str">
-        <v>So</v>
-      </c>
-      <c r="I160">
-        <v>2</v>
-      </c>
-      <c r="J160">
-        <v>2</v>
-      </c>
-      <c r="K160">
-        <v>26</v>
-      </c>
-      <c r="L160">
-        <v>22</v>
-      </c>
-      <c r="M160" t="str">
-        <v>203</v>
-      </c>
-      <c r="N160" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O160" t="str">
-        <v/>
-      </c>
-      <c r="P160" t="str">
-        <v/>
-      </c>
-      <c r="Q160">
-        <v>180</v>
-      </c>
-      <c r="R160" t="str">
-        <v>1</v>
-      </c>
-      <c r="S160">
-        <v>0</v>
-      </c>
-      <c r="T160" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B161" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C161" t="str">
-        <v>SELVA L 61</v>
-      </c>
-      <c r="D161" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E161">
-        <v>610</v>
-      </c>
-      <c r="F161">
-        <v>25</v>
-      </c>
-      <c r="G161">
-        <v>25</v>
-      </c>
-      <c r="H161" t="str">
-        <v>So</v>
-      </c>
-      <c r="I161">
-        <v>2</v>
-      </c>
-      <c r="J161">
-        <v>2</v>
-      </c>
-      <c r="K161">
-        <v>26</v>
-      </c>
-      <c r="L161">
-        <v>23</v>
-      </c>
-      <c r="M161" t="str">
-        <v>11011</v>
-      </c>
-      <c r="N161" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O161" t="str">
-        <v/>
-      </c>
-      <c r="P161" t="str">
-        <v/>
-      </c>
-      <c r="Q161">
-        <v>180</v>
-      </c>
-      <c r="R161" t="str">
-        <v>5</v>
-      </c>
-      <c r="S161">
-        <v>0</v>
-      </c>
-      <c r="T161" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B162" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C162" t="str">
-        <v>SELVA L 49</v>
-      </c>
-      <c r="D162" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E162">
-        <v>490</v>
-      </c>
-      <c r="F162">
-        <v>25</v>
-      </c>
-      <c r="G162">
-        <v>25</v>
-      </c>
-      <c r="H162" t="str">
-        <v>So</v>
-      </c>
-      <c r="I162">
-        <v>2</v>
-      </c>
-      <c r="J162">
-        <v>2</v>
-      </c>
-      <c r="K162">
-        <v>26</v>
-      </c>
-      <c r="L162">
-        <v>24</v>
-      </c>
-      <c r="M162" t="str">
-        <v>10809</v>
-      </c>
-      <c r="N162" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O162" t="str">
-        <v/>
-      </c>
-      <c r="P162" t="str">
-        <v/>
-      </c>
-      <c r="Q162">
-        <v>180</v>
-      </c>
-      <c r="R162" t="str">
-        <v>4</v>
-      </c>
-      <c r="S162">
-        <v>0</v>
-      </c>
-      <c r="T162" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B163" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C163" t="str">
-        <v>SELVA L 46,5</v>
-      </c>
-      <c r="D163" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E163">
-        <v>465</v>
-      </c>
-      <c r="F163">
-        <v>25</v>
-      </c>
-      <c r="G163">
-        <v>25</v>
-      </c>
-      <c r="H163" t="str">
-        <v>So</v>
-      </c>
-      <c r="I163">
-        <v>2</v>
-      </c>
-      <c r="J163">
-        <v>2</v>
-      </c>
-      <c r="K163">
-        <v>26</v>
-      </c>
-      <c r="L163">
-        <v>25</v>
-      </c>
-      <c r="M163" t="str">
-        <v>10607</v>
-      </c>
-      <c r="N163" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O163" t="str">
-        <v/>
-      </c>
-      <c r="P163" t="str">
-        <v/>
-      </c>
-      <c r="Q163">
-        <v>540</v>
-      </c>
-      <c r="R163" t="str">
-        <v>3</v>
-      </c>
-      <c r="S163">
-        <v>0</v>
-      </c>
-      <c r="T163" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B164" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C164" t="str">
-        <v>SELVA L 15,5</v>
-      </c>
-      <c r="D164" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E164">
-        <v>155</v>
-      </c>
-      <c r="F164">
-        <v>25</v>
-      </c>
-      <c r="G164">
-        <v>25</v>
-      </c>
-      <c r="H164" t="str">
-        <v>So</v>
-      </c>
-      <c r="I164">
-        <v>2</v>
-      </c>
-      <c r="J164">
-        <v>2</v>
-      </c>
-      <c r="K164">
-        <v>26</v>
-      </c>
-      <c r="L164">
-        <v>26</v>
-      </c>
-      <c r="M164" t="str">
-        <v>10203</v>
-      </c>
-      <c r="N164" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O164" t="str">
-        <v/>
-      </c>
-      <c r="P164" t="str">
-        <v/>
-      </c>
-      <c r="Q164">
-        <v>1260</v>
-      </c>
-      <c r="R164" t="str">
-        <v>1</v>
-      </c>
-      <c r="S164">
-        <v>0</v>
-      </c>
-      <c r="T164" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B165" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C165" t="str">
-        <v>SELVA L 25,5</v>
-      </c>
-      <c r="D165" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E165">
-        <v>255</v>
-      </c>
-      <c r="F165">
-        <v>25</v>
-      </c>
-      <c r="G165">
-        <v>25</v>
-      </c>
-      <c r="H165" t="str">
-        <v>So</v>
-      </c>
-      <c r="I165">
-        <v>2</v>
-      </c>
-      <c r="J165">
-        <v>2</v>
-      </c>
-      <c r="K165">
-        <v>26</v>
-      </c>
-      <c r="L165">
-        <v>27</v>
-      </c>
-      <c r="M165" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N165" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O165" t="str">
-        <v/>
-      </c>
-      <c r="P165" t="str">
-        <v/>
-      </c>
-      <c r="Q165">
-        <v>360</v>
-      </c>
-      <c r="R165" t="str">
-        <v>2</v>
-      </c>
-      <c r="S165">
-        <v>0</v>
-      </c>
-      <c r="T165" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B166" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C166" t="str">
-        <v>SELVA L 137 SZ</v>
-      </c>
-      <c r="D166" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E166">
-        <v>1370</v>
-      </c>
-      <c r="F166">
-        <v>25</v>
-      </c>
-      <c r="G166">
-        <v>50</v>
-      </c>
-      <c r="H166" t="str">
-        <v>So</v>
-      </c>
-      <c r="I166">
-        <v>1</v>
-      </c>
-      <c r="J166">
-        <v>1</v>
-      </c>
-      <c r="K166">
-        <v>26</v>
-      </c>
-      <c r="L166">
-        <v>28</v>
-      </c>
-      <c r="M166" t="str">
-        <v>405</v>
-      </c>
-      <c r="N166" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O166" t="str">
-        <v/>
-      </c>
-      <c r="P166" t="str">
-        <v/>
-      </c>
-      <c r="Q166">
-        <v>180</v>
-      </c>
-      <c r="R166" t="str">
-        <v>2</v>
-      </c>
-      <c r="S166">
-        <v>0</v>
-      </c>
-      <c r="T166" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B167" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C167" t="str">
-        <v>SELVA L 112 SZ</v>
-      </c>
-      <c r="D167" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E167">
-        <v>1120</v>
-      </c>
-      <c r="F167">
-        <v>25</v>
-      </c>
-      <c r="G167">
-        <v>50</v>
-      </c>
-      <c r="H167" t="str">
-        <v>So</v>
-      </c>
-      <c r="I167">
-        <v>1</v>
-      </c>
-      <c r="J167">
-        <v>1</v>
-      </c>
-      <c r="K167">
-        <v>26</v>
-      </c>
-      <c r="L167">
-        <v>29</v>
-      </c>
-      <c r="M167" t="str">
-        <v>203</v>
-      </c>
-      <c r="N167" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O167" t="str">
-        <v/>
-      </c>
-      <c r="P167" t="str">
-        <v/>
-      </c>
-      <c r="Q167">
-        <v>180</v>
-      </c>
-      <c r="R167" t="str">
-        <v>1</v>
-      </c>
-      <c r="S167">
-        <v>0</v>
-      </c>
-      <c r="T167" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B168" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C168" t="str">
-        <v>SELVA L 86,5 SZ</v>
-      </c>
-      <c r="D168" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E168">
-        <v>865</v>
-      </c>
-      <c r="F168">
-        <v>25</v>
-      </c>
-      <c r="G168">
-        <v>50</v>
-      </c>
-      <c r="H168" t="str">
-        <v>So</v>
-      </c>
-      <c r="I168">
-        <v>1</v>
-      </c>
-      <c r="J168">
-        <v>1</v>
-      </c>
-      <c r="K168">
-        <v>26</v>
-      </c>
-      <c r="L168">
-        <v>30</v>
-      </c>
-      <c r="M168" t="str">
-        <v>1011</v>
-      </c>
-      <c r="N168" t="str">
-        <v>synchronicznie</v>
-      </c>
-      <c r="O168" t="str">
-        <v/>
-      </c>
-      <c r="P168" t="str">
-        <v/>
-      </c>
-      <c r="Q168">
-        <v>180</v>
-      </c>
-      <c r="R168" t="str">
-        <v>5</v>
-      </c>
-      <c r="S168">
-        <v>0</v>
-      </c>
-      <c r="T168" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B169" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C169" t="str">
-        <v>SELVA L 22</v>
-      </c>
-      <c r="D169" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E169">
-        <v>220</v>
-      </c>
-      <c r="F169">
-        <v>25</v>
-      </c>
-      <c r="G169">
-        <v>50</v>
-      </c>
-      <c r="H169" t="str">
-        <v>So</v>
-      </c>
-      <c r="I169">
-        <v>2</v>
-      </c>
-      <c r="J169">
-        <v>2</v>
-      </c>
-      <c r="K169">
-        <v>26</v>
-      </c>
-      <c r="L169">
-        <v>31</v>
-      </c>
-      <c r="M169" t="str">
-        <v>10809</v>
-      </c>
-      <c r="N169" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O169" t="str">
-        <v/>
-      </c>
-      <c r="P169" t="str">
-        <v/>
-      </c>
-      <c r="Q169">
-        <v>1080</v>
-      </c>
-      <c r="R169" t="str">
-        <v>4</v>
-      </c>
-      <c r="S169">
-        <v>0</v>
-      </c>
-      <c r="T169" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B170" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C170" t="str">
-        <v>SELVA L 7,5</v>
-      </c>
-      <c r="D170" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E170">
-        <v>75</v>
-      </c>
-      <c r="F170">
-        <v>25</v>
-      </c>
-      <c r="G170">
-        <v>50</v>
-      </c>
-      <c r="H170" t="str">
-        <v>So</v>
-      </c>
-      <c r="I170">
-        <v>2</v>
-      </c>
-      <c r="J170">
-        <v>2</v>
-      </c>
-      <c r="K170">
-        <v>26</v>
-      </c>
-      <c r="L170">
-        <v>32</v>
-      </c>
-      <c r="M170" t="str">
-        <v>10607</v>
-      </c>
-      <c r="N170" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O170" t="str">
-        <v/>
-      </c>
-      <c r="P170" t="str">
-        <v/>
-      </c>
-      <c r="Q170">
-        <v>180</v>
-      </c>
-      <c r="R170" t="str">
-        <v>3</v>
-      </c>
-      <c r="S170">
-        <v>0</v>
-      </c>
-      <c r="T170" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B171" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C171" t="str">
-        <v>SELVA L 5,5</v>
-      </c>
-      <c r="D171" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E171">
-        <v>55</v>
-      </c>
-      <c r="F171">
-        <v>25</v>
-      </c>
-      <c r="G171">
-        <v>50</v>
-      </c>
-      <c r="H171" t="str">
-        <v>So</v>
-      </c>
-      <c r="I171">
-        <v>2</v>
-      </c>
-      <c r="J171">
-        <v>2</v>
-      </c>
-      <c r="K171">
-        <v>26</v>
-      </c>
-      <c r="L171">
-        <v>33</v>
-      </c>
-      <c r="M171" t="str">
-        <v>10405</v>
-      </c>
-      <c r="N171" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O171" t="str">
-        <v/>
-      </c>
-      <c r="P171" t="str">
-        <v/>
-      </c>
-      <c r="Q171">
-        <v>360</v>
-      </c>
-      <c r="R171" t="str">
-        <v>2</v>
-      </c>
-      <c r="S171">
-        <v>0</v>
-      </c>
-      <c r="T171" t="str">
-        <v>Kopia tymczasowa</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>SELVA L 180</v>
-      </c>
-      <c r="B172" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="C172" t="str">
-        <v>SELVA L 4</v>
-      </c>
-      <c r="D172" t="str">
-        <v>SELVA L</v>
-      </c>
-      <c r="E172">
-        <v>40</v>
-      </c>
-      <c r="F172">
-        <v>25</v>
-      </c>
-      <c r="G172">
-        <v>50</v>
-      </c>
-      <c r="H172" t="str">
-        <v>So</v>
-      </c>
-      <c r="I172">
-        <v>2</v>
-      </c>
-      <c r="J172">
-        <v>2</v>
-      </c>
-      <c r="K172">
-        <v>26</v>
-      </c>
-      <c r="L172">
-        <v>34</v>
-      </c>
-      <c r="M172" t="str">
-        <v>10203</v>
-      </c>
-      <c r="N172" t="str">
-        <v>naprzemiennie</v>
-      </c>
-      <c r="O172" t="str">
-        <v/>
-      </c>
-      <c r="P172" t="str">
-        <v/>
-      </c>
-      <c r="Q172">
-        <v>360</v>
-      </c>
-      <c r="R172" t="str">
-        <v>1</v>
-      </c>
-      <c r="S172">
-        <v>0</v>
-      </c>
-      <c r="T172" t="str">
         <v>Kopia tymczasowa</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T172"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T102"/>
   </ignoredErrors>
 </worksheet>
 </file>